--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.9%</t>
+          <t>421.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.2%</t>
+          <t>-682.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-154.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.5%</t>
+          <t>587.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
     </row>
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.627485154849547</v>
+        <v>3.585543183948654</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.276490286491615</v>
+        <v>-5.210050808304612</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.187189291737912</v>
+        <v>2.213765083012713</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.561656008944627</v>
+        <v>0.5697902969127311</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.635135436015082</v>
+        <v>4.640016008795944</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>52.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.6%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.6%</t>
+          <t>-690.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-154.8%</t>
+          <t>-158.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-14.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.6%</t>
+          <t>181.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.9%</t>
+          <t>-304.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-169.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.81229228416808</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.3346615225627163</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.314373103356599</v>
+        <v>-0.32874664559976</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.871310998529737</v>
+        <v>2.86268687318384</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.72732761743876</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.3815537304781031</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2294084366272794</v>
+        <v>-0.2437819788704404</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.935196139790988</v>
+        <v>2.926572014445091</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.832917607211865</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>0.2113418049696429</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3349984264003837</v>
+        <v>-0.3493719686435448</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.743866216327906</v>
+        <v>2.735242090982009</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.764683022586437</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.2871799806969002</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3165831035278477</v>
+        <v>-0.3309566457710088</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803459751928514</v>
+        <v>2.794835626582617</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.616742981178838</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.2297351886215329</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2962621876192902</v>
+        <v>-0.3106357298624512</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.699031492835242</v>
+        <v>2.690407367489345</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.56377345892485</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.24220901126965</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2576662076084623</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.722099219934157</v>
+        <v>2.71347509458826</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.397985262964559</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.301563677558673</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2576662076084623</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.715138607839064</v>
+        <v>2.706514482493167</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.36462205648579</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.3293713145313237</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2576662076084623</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.729600962220207</v>
+        <v>2.72097683687431</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.256362919363268</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.3672070898395274</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2576662076084623</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.724133082679402</v>
+        <v>2.715508957333505</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-6.133071784546138</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.4140216377769566</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1200015305481708</v>
+        <v>-0.1343750727913318</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.795605857580257</v>
+        <v>2.78698173223436</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-6.080374917414846</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.4428013628667982</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08167820566004064</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.834924956096357</v>
+        <v>2.82630083075046</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.836609475431402</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.5360882480072267</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08167820566004064</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.830705664443407</v>
+        <v>2.822081539097511</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.74683380305493</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.5741228308778319</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02007876074573062</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.86978964531201</v>
+        <v>2.861165519966113</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.496983409105855</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.6668050634411635</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02007876074573062</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.862531720295712</v>
+        <v>2.853907594949815</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.321091316638423</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.7407610239487852</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02007876074573062</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.86613084381636</v>
+        <v>2.857506718470463</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.14964485361596</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.8226671152123242</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1657412445198935</v>
+        <v>0.1513677022767325</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.982326227684392</v>
+        <v>2.973702102338495</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-5.069622566506839</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.8536965076722698</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2457635316290145</v>
+        <v>0.2313899893858535</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.029360077566162</v>
+        <v>3.020735952220265</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-5.005986824272904</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.8838456056201607</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.309399273862949</v>
+        <v>0.295025731619788</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.072236323960839</v>
+        <v>3.063612198614943</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.912289506056509</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.9025187916905144</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.309399273862949</v>
+        <v>0.295025731619788</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.053430582744635</v>
+        <v>3.044806457398738</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.922792129121798</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.9000608190892763</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2845231085544991</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>3.040247960184443</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.850549560950603</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9328871601925743</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2845231085544991</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>3.044177274019263</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.832835874072738</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9406512188610605</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2877044374514159</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>3.046764655274753</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.70936160275972</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>0.9870389986062613</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2877044374514159</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>3.043762726494746</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.489340804722709</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.07662635483168</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4289242825193962</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.130073670546149</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.356473115659432</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.145667613258814</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4289242825193962</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.145967853347972</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.236300032294933</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.194882691044915</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5490973658838951</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.219217547806973</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.101046670964956</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.259072138138346</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6843507272138722</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.310457667166399</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.160921498322648</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.221159698596695</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6244758998561801</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.26057026215321</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-4.041101267411811</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.284376960195238</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6244758998561801</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.275859431387418</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-4.043570973873617</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.191033276932957</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.6220061933943739</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.182021806832776</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.111941160197627</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.082947063888655</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6312818924305889</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.106849087739807</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.223813439823778</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.028634860670086</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6312818924305889</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.097285796371698</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.279333515716368</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.143457667005252</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6312818924305889</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.2343166330639</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.103859255923899</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.218214602914028</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6312818924305889</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.238883865055688</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.095934881338985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.1971263815092</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6312818924305889</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.214625893816895</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.089656678769136</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.12817597593859</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6375600950004379</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.146931128760254</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-4.029804059565413</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.162289410052211</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6375600950004379</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.157103515192387</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.943560596539035</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.191733065836623</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6375600950004379</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.152049785766247</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.988867415938015</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.165386113521556</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5967499319912071</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.119339463405234</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-4.017900520640316</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.154324744673737</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5967499319912071</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.119891336438335</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.925090039189457</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.120721629145447</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6895604134420664</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.104850317200217</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.969479508518884</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.104839317338277</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.6451709441126388</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.080090111527161</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.086021113624227</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.053298383807862</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.528629339007296</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>3.005240856975679</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.125945208206799</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.042820041805501</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.528629339007296</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>3.010732152806346</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.153725606108152</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.043205084413499</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.5008489411059429</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>3.005561115834073</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.27210627883829</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8342085353220967</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4336310889549667</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.80358612454414</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.380720357281621</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.91091256466397</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4336310889549667</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.923735785263346</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.345311319033478</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.93958920606555</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4336310889549667</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.938248811365669</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.306927656475327</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9523621124311792</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4720147515131179</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.958698450242928</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.129811326440161</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.019937673290547</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4720147515131179</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.95542747908823</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.174903571273707</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.002584167119042</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.4101187083437281</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.91897324494851</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.995528150034939</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.068121310920964</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.5668954665144468</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>3.006826275157355</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-4.040542363555545</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.030923080844311</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.5365465711998422</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.969424393300182</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.30754687382798</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.929812839074283</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.3421835331568936</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.858498132813359</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.408744655265153</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.8885376483959153</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2737747196115744</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.816656766582669</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.40223368865084</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.8887419965959571</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2737747196115744</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.814256728136985</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.383195560943543</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.8928819668871208</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2155911082803799</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.775871280546514</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.435711363218363</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>0.9911700476113832</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2155911082803799</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.895165682180704</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.449578124552281</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>0.9864566720639494</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1777331915465569</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.873284261126543</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.409095132629936</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>1.008658399229813</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1777331915465569</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.879292791523469</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.261352162394934</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.965705808601014</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3455405487814401</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.877927427141599</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.345173383669632</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.9349709416226155</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3455405487814401</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.88072104867308</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.339020677616848</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9380943724353876</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.3516932548342244</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.885075020696409</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.35582997576735</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9304511299152971</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.3348839566837227</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.874069918546218</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.293531976991227</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>1.021705883222567</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.3801782209581648</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.967582030907704</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.091741779326069</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.9047139640027573</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.5781964131273192</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.888684947923324</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.142628492012264</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.9546495112504545</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.5273097004411247</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.928443152633783</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-4.056017749362457</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>1.003921544426421</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.6059354316462829</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.990246327472921</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.116227047367742</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>0.9783738060489786</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5457261336409984</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.952656729494422</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.067040398683391</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>0.9965400835626477</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5457261336409984</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.951148347534351</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-4.022667267044822</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.014152203653511</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.590099265279567</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.977635093952928</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.045147617903707</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>0.9995538574485479</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.590099265279567</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.972028888091518</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-3.997491887342651</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.024997906700775</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.6377549958406227</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.007004083455957</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.896973728843896</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.070097543475002</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.7382731543393772</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.072207351929934</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.881068399411544</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.063214347723815</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.6591604936301383</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.011494427980263</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.836229997803146</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.085247410977803</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.6637039265750078</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.018318190357813</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.855728454045154</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.081608968112077</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.6156192852951035</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.993628345220948</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.811525616959254</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.105169705474275</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.6598221223810039</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.026029650000326</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.8190852827963</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.100555839608703</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7146255263908232</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.057321692875465</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.660793865257028</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.215120171807452</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7146255263908232</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.108569458058505</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.453151861622552</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.296617677855496</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.9222675300252994</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.231595364833443</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.402119768900024</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.311978743182777</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.9732996227478273</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.257162848705231</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.336895587772818</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.355255819726364</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.038523803875033</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.313484761474259</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.299468567701684</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.366187600054098</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.043775341904214</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.312596656591048</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.319580223736393</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.359399729971455</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.054802686901634</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.32046985592074</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.291166960636509</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.531322806232619</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>0.9958271241552048</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.445642289294093</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.216384699611496</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.681348619860441</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.070609385180217</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.610624555126918</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.190300615347688</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.683490229579824</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.070609385180217</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.602332531140777</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.102422702238568</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.716834590407251</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.186535027603568</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.670081112178567</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.093530240845284</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.737945980691356</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.186535027603568</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.687635517905358</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.262006357815162</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.662410581307989</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.158587191886988</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.662721863879994</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.815750165185722</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.822182755547627</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.063868522217355</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.587160359266076</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.79302906150257</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.821935219517792</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.063868522217355</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.577824381762981</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.922230874796612</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.929160620051344</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.9346667089233127</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.659209419637724</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.948105273270638</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.955888683155381</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>0.9795783176350539</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.723234207358415</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.941050583055465</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.955385915230995</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9866330078502277</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.724142377477065</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.914099358728977</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.976172558606332</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.001513353877947</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.743076738738438</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.935643586559764</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.151657999618977</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.001513353877947</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.927179870883398</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.958051704364636</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.134811447400021</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.001513353877947</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.919296565786391</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-2.986275939942236</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.125575752718619</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.019490106329255</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.932136616806813</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-2.995716865830766</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.178053100085053</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.141917223872647</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.061846605054695</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.070219954756078</v>
+        <v>-3.08459349699924</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.15114295906023</v>
+        <v>2.145393542162965</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.067414134947334</v>
+        <v>1.053040592704173</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.020035846244808</v>
+        <v>4.011411720898912</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.146549932356984</v>
+        <v>-3.160923474600146</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118722780913642</v>
+        <v>2.112973364016378</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.067414134947334</v>
+        <v>1.053040592704173</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.018147659138584</v>
+        <v>4.009523533792687</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.240213877034526</v>
+        <v>-3.254587419277687</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076077432645488</v>
+        <v>2.070328015748224</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>0.9593766480266316</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.948145396589025</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.401782302561781</v>
+        <v>-3.416155844804942</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009884072644738</v>
+        <v>2.004134655747474</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8325937242287522</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.870509652520449</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5100829644319</v>
+        <v>-3.524456506675062</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.979637214762609</v>
+        <v>1.973887797865345</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8325937242287522</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.883583059386368</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.603230435735267</v>
+        <v>-3.617603977978428</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934383423024203</v>
+        <v>1.928634006126938</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7241380551893805</v>
+        <v>0.7097645129462195</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810514854745685</v>
+        <v>3.801890729399788</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.63113122284474</v>
+        <v>-3.645504765087901</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.921747149307415</v>
+        <v>1.915997732410151</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6895411310464457</v>
+        <v>0.6751675888032846</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788280741386926</v>
+        <v>3.779656616041029</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.753657325547634</v>
+        <v>-3.768030867790795</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869501152203457</v>
+        <v>1.863751735306192</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5670150283435518</v>
+        <v>0.5526414861003908</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711529523742389</v>
+        <v>3.702905398396492</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.984171821733223</v>
+        <v>-3.998545363976384</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.844001313319725</v>
+        <v>1.83825189642246</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3365005321579631</v>
+        <v>0.322126989914802</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639926785621539</v>
+        <v>3.631302660275642</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.332916906957666</v>
+        <v>-4.347290449200828</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844814998231794</v>
+        <v>1.83906558133453</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2133790359959042</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714989732272048</v>
+        <v>3.706365606926151</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.486903324733807</v>
+        <v>-4.501276866976968</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852200700266978</v>
+        <v>1.846451283369713</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2133790359959042</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783970001417687</v>
+        <v>3.775345876071791</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.436381420906141</v>
+        <v>-4.450754963149302</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858460663918165</v>
+        <v>1.8527112470209</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2133790359959042</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770021203537808</v>
+        <v>3.761397078191912</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.688856574913865</v>
+        <v>-4.703230117157027</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769341091370489</v>
+        <v>1.763591674473225</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2133790359959042</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781891692593222</v>
+        <v>3.773267567247326</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.981752331393277</v>
+        <v>-4.996125873636439</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653393323297668</v>
+        <v>1.647643906400404</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2133790359959042</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783102227112166</v>
+        <v>3.774478101766269</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.168416459528085</v>
+        <v>-5.182790001771247</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582849414271066</v>
+        <v>1.577099997373802</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2010136074145054</v>
+        <v>0.1866400651713443</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771180586844751</v>
+        <v>3.762556461498855</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.314437146442048</v>
+        <v>-5.328810688685209</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519518992241671</v>
+        <v>1.513769575344406</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.1775569733774874</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760808584504626</v>
+        <v>3.75218445915873</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.406151155551633</v>
+        <v>-5.420524697794795</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645037445296881</v>
+        <v>1.639288028399616</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.1775569733774874</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923012641203671</v>
+        <v>3.914388515857774</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.437802814611603</v>
+        <v>-5.452176356854764</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627223419636707</v>
+        <v>1.621474002739443</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1867620583762082</v>
+        <v>0.1723885161330472</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914758204820821</v>
+        <v>3.906134079474924</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.519737632880486</v>
+        <v>-5.534111175123647</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604678909897645</v>
+        <v>1.598929493000381</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.176827312789128</v>
+        <v>0.162453770545967</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919026775037064</v>
+        <v>3.910402649691167</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.621713755128893</v>
+        <v>-5.636087297372055</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572814099454185</v>
+        <v>1.56706468255692</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07485119054072042</v>
+        <v>0.06047764829755942</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866766740143922</v>
+        <v>3.858142614798025</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.511707471651672</v>
+        <v>-5.526081013894833</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608969500089248</v>
+        <v>1.603220083191984</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09805576245799563</v>
+        <v>0.08368222021483462</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872842370538462</v>
+        <v>3.864218245192566</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.368647895910746</v>
+        <v>-5.383021438153907</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670443341107593</v>
+        <v>1.664693924210328</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1060691890479749</v>
+        <v>0.0916956468048139</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881900437214424</v>
+        <v>3.873276311868528</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.067201170438908</v>
+        <v>-5.08157471268207</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798282914178864</v>
+        <v>1.7925334972816</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.3931423722766512</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070029355380062</v>
+        <v>4.061405230034166</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.091791414674092</v>
+        <v>-5.106164956917254</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789417994237501</v>
+        <v>1.783668577340237</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.3931423722766512</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071000533132773</v>
+        <v>4.062376407786877</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.040753038667572</v>
+        <v>-5.055126580910733</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810676249019865</v>
+        <v>1.8049268321226</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.3931423722766512</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071843437512529</v>
+        <v>4.063219312166632</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.999613743800941</v>
+        <v>-5.013987286044102</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846170065840663</v>
+        <v>1.840420648943398</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.448655209386443</v>
+        <v>0.434281667143282</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115565113306652</v>
+        <v>4.106940987960756</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.902978831782301</v>
+        <v>-4.917352374025462</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701008026772053</v>
+        <v>1.695258609874789</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5452901214050829</v>
+        <v>0.5309165791619219</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989730056641771</v>
+        <v>3.981105931295875</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.033559566313143</v>
+        <v>-5.047933108556305</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65227777703368</v>
+        <v>1.646528360136416</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4147093868742404</v>
+        <v>0.4003358446310794</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488365999723</v>
+        <v>3.906259534651333</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.869063232122182</v>
+        <v>-4.883436774365343</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702503129786148</v>
+        <v>1.696753712888883</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5648321788220413</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998008279587889</v>
+        <v>3.989384154241993</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.896433164806614</v>
+        <v>-4.910806707049775</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690742867148805</v>
+        <v>1.68499345025154</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5648321788220413</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997195990024319</v>
+        <v>3.988571864678423</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.906818359696503</v>
+        <v>-4.921191901939665</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696457568317921</v>
+        <v>1.690708151420657</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.568820526175313</v>
+        <v>0.554446983932152</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000833652215458</v>
+        <v>3.992209526869561</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.925406518418728</v>
+        <v>-4.93978006066189</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759859310605457</v>
+        <v>1.754109893708192</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5502323674530876</v>
+        <v>0.5358588252099266</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060517762758548</v>
+        <v>4.051893637412651</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.925705065114764</v>
+        <v>-4.940078607357925</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756608902745341</v>
+        <v>1.750859485848076</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5499338207570517</v>
+        <v>0.5355602785138907</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057207645559225</v>
+        <v>4.048583520213328</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.824881931424336</v>
+        <v>-4.839255473667498</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801469051160903</v>
+        <v>1.795719634263639</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5623980362414055</v>
+        <v>0.5480244939982445</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069217069789229</v>
+        <v>4.060592944443332</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.634100570671929</v>
+        <v>-4.648474112915091</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877910848940409</v>
+        <v>1.872161432043145</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7531793969938129</v>
+        <v>0.7388058547506519</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183815139719216</v>
+        <v>4.175191014373319</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527137212822508</v>
+        <v>-4.541510755065669</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900533037817774</v>
+        <v>1.89478362092051</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8116440049536143</v>
+        <v>0.7972704627104533</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198730750232693</v>
+        <v>4.190106624886797</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471806624920745</v>
+        <v>-4.486180167163907</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.957632209590538</v>
+        <v>1.951882792693273</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8669745928553765</v>
+        <v>0.8526010506122155</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266896039585809</v>
+        <v>4.258271914239913</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459752498007783</v>
+        <v>-4.474126040250944</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.956140428257161</v>
+        <v>1.950391011359896</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8790287197683393</v>
+        <v>0.8646551775251783</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267815083635025</v>
+        <v>4.259190958289128</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.500907617576003</v>
+        <v>-4.515281159819165</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.941559010614008</v>
+        <v>1.935809593716743</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8378736002001184</v>
+        <v>0.8235000579569574</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245002642078228</v>
+        <v>4.236378516732332</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.432859054884474</v>
+        <v>-4.447232597127635</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981629461568502</v>
+        <v>1.975880044671238</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.8915486206484872</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298682805571028</v>
+        <v>4.290058680225131</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.664459448053974</v>
+        <v>-4.678832990297136</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909191974474296</v>
+        <v>1.903442557577032</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.8915486206484872</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318885475744622</v>
+        <v>4.310261350398726</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.682531956345586</v>
+        <v>-4.696905498588747</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901962971157652</v>
+        <v>1.896213554260387</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.8915486206484872</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318885475744622</v>
+        <v>4.310261350398726</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.857638788922031</v>
+        <v>-4.872012331165193</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79217215172054</v>
+        <v>1.786422734823276</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.8915486206484872</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.279137389338089</v>
+        <v>4.270513263992193</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.826352768381576</v>
+        <v>-4.840726310624738</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.811709178933662</v>
+        <v>1.805959762036398</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9372081834321035</v>
+        <v>0.9228346411889425</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.304931620659302</v>
+        <v>4.296307495313406</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.673327376268292</v>
+        <v>-4.687700918511453</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.972090335351881</v>
+        <v>1.966340918454616</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.090233575545388</v>
+        <v>1.075860033302227</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.495917855500178</v>
+        <v>4.487293730154281</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.701634690141562</v>
+        <v>-4.716008232384723</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.148233634710865</v>
+        <v>2.1424842178136</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.090233575545388</v>
+        <v>1.075860033302227</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.683384080408469</v>
+        <v>4.674759955062573</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.868227915255084</v>
+        <v>-4.882601457498246</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.050999296019538</v>
+        <v>2.045249879122273</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9092668081887043</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.552831096694439</v>
+        <v>4.544206971348542</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.845192121893518</v>
+        <v>-4.85956566413668</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.063890016025882</v>
+        <v>2.058140599128618</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9092668081887043</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.556507499356156</v>
+        <v>4.54788337401026</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.815946141437822</v>
+        <v>-4.830319683680983</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.073206463331656</v>
+        <v>2.067457046434392</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9092668081887043</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.554125554479652</v>
+        <v>4.545501429133755</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.922871689315673</v>
+        <v>-4.937245231558834</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.027729483338151</v>
+        <v>2.021980066440886</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.816714802554014</v>
+        <v>0.802341260310853</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.487263464910575</v>
+        <v>4.478639339564679</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.067890247822922</v>
+        <v>-5.082263790066083</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.971150862078485</v>
+        <v>1.965401445181221</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6716962440467654</v>
+        <v>0.6573227018036044</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.40168113194946</v>
+        <v>4.393057006603564</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.186232013607639</v>
+        <v>-5.2006055558508</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.023745395022351</v>
+        <v>2.017995978125087</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.6680087403664945</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.508023994344947</v>
+        <v>4.499399868999051</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.237642435928347</v>
+        <v>-5.252015978171508</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.000966923220007</v>
+        <v>1.995217506322742</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.6680087403664945</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.505809691470886</v>
+        <v>4.49718556612499</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.317061887136099</v>
+        <v>-5.33143542937926</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.969102270811196</v>
+        <v>1.963352853913931</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.6680087403664945</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.505712819545176</v>
+        <v>4.497088694199279</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.412524885053316</v>
+        <v>-5.426898427296478</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.930910965202352</v>
+        <v>1.925161548305087</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.6680087403664945</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.505706713103219</v>
+        <v>4.497082587757323</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.4525448830971</v>
+        <v>-5.466918425340261</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.912999362547449</v>
+        <v>1.907249945650185</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.6279887423227106</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.479791110839559</v>
+        <v>4.471166985493663</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.507914045229294</v>
+        <v>-5.522287587472455</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.896585515442298</v>
+        <v>1.890836098545034</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.6279887423227106</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.485524928587286</v>
+        <v>4.47690080324139</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.553351825060121</v>
+        <v>-5.567725367303282</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.8779487668529</v>
+        <v>1.872199349955636</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.599517293887712</v>
+        <v>0.585143751644551</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.459356297523323</v>
+        <v>4.450732172177426</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.465144990912543</v>
+        <v>-5.479518533155704</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.933105893362251</v>
+        <v>1.927356476464986</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.599517293887712</v>
+        <v>0.585143751644551</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.479230690373642</v>
+        <v>4.470606565027746</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.359109995707233</v>
+        <v>-5.373483537950395</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.959220591969102</v>
+        <v>1.953471175071838</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.599517293887712</v>
+        <v>0.585143751644551</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.462931390898371</v>
+        <v>4.454307265552473</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.175898332574138</v>
+        <v>-5.1902718748173</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.034936206686386</v>
+        <v>2.029186789789121</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.599517293887712</v>
+        <v>0.585143751644551</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.465362340362416</v>
+        <v>4.456738215016519</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.104176885560287</v>
+        <v>-5.118550427803449</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.029415971339815</v>
+        <v>2.023666554442551</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6712387409015627</v>
+        <v>0.6568651986584017</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.474186394418616</v>
+        <v>4.465562269072719</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.081803859952581</v>
+        <v>-5.096177402195742</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.98528092750407</v>
+        <v>1.979531510606805</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6824944920144642</v>
+        <v>0.6681209497713032</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.427855591007528</v>
+        <v>4.419231465661632</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.114820155863326</v>
+        <v>-5.129193698106487</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.157272614025127</v>
+        <v>2.151523197127863</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6130571153477127</v>
+        <v>0.5986835731045517</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.571391369892833</v>
+        <v>4.562767244546936</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.103292520213717</v>
+        <v>-5.117666062456879</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.15380489411322</v>
+        <v>2.148055477215955</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6720577735490751</v>
+        <v>0.6576842313059141</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.598712990641899</v>
+        <v>4.590088865296003</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.200634021556086</v>
+        <v>-5.215007563799247</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.118536406098061</v>
+        <v>2.112786989200796</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6276375913835868</v>
+        <v>0.6132640491404258</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.575728993864395</v>
+        <v>4.567104868518499</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.286490050896052</v>
+        <v>-5.300863593139214</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.085445076554913</v>
+        <v>2.079695659657648</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5852615221574518</v>
+        <v>0.5708879799142907</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.551554434521552</v>
+        <v>4.542930309175656</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.295326848312172</v>
+        <v>-5.309700390555333</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.064329559408967</v>
+        <v>2.058580142511702</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.577819349516101</v>
+        <v>0.56344580727294</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.529508332757244</v>
+        <v>4.520884207411346</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.38670941087763</v>
+        <v>-5.401082953120792</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.037941045427833</v>
+        <v>2.032191628530568</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4864367869506428</v>
+        <v>0.4720632447074818</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.484843306263018</v>
+        <v>4.476219180917122</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.375002692890624</v>
+        <v>-5.389376235133786</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.144751990446903</v>
+        <v>2.139002573549639</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4981435049376493</v>
+        <v>0.4837699626944882</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.59399559487949</v>
+        <v>4.585371469533594</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.585543183948654</v>
+        <v>3.802282022642979</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.210050808304612</v>
+        <v>-5.289712731050123</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.213765083012713</v>
+        <v>2.181900313914508</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5697902969127311</v>
+        <v>0.5469570458981747</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.640016008795944</v>
+        <v>4.62631605818721</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>57.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.5%</t>
+          <t>-683.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.0%</t>
+          <t>-155.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.1%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>181.1%</t>
+          <t>589.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.5%</t>
+          <t>-305.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.3%</t>
+          <t>-162.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.81229228416808</v>
+        <v>-6.797918741924919</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3346615225627163</v>
+        <v>0.3404109394599812</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.32874664559976</v>
+        <v>-0.314373103356599</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.86268687318384</v>
+        <v>2.871310998529737</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.72732761743876</v>
+        <v>-6.712954075195599</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3815537304781031</v>
+        <v>0.3873031473753676</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2437819788704404</v>
+        <v>-0.2294084366272794</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.926572014445091</v>
+        <v>2.935196139790988</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.832917607211865</v>
+        <v>-6.818544064968703</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2113418049696429</v>
+        <v>0.2170912218669074</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3493719686435448</v>
+        <v>-0.3349984264003837</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.735242090982009</v>
+        <v>2.743866216327906</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.764683022586437</v>
+        <v>-6.750309480343276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2871799806969002</v>
+        <v>0.2929293975941647</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3309566457710088</v>
+        <v>-0.3165831035278477</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.794835626582617</v>
+        <v>2.803459751928514</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.616742981178838</v>
+        <v>-6.602369438935677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2297351886215329</v>
+        <v>0.2354846055187974</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3106357298624512</v>
+        <v>-0.2962621876192902</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.690407367489345</v>
+        <v>2.699031492835242</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.56377345892485</v>
+        <v>-6.549399916681688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.24220901126965</v>
+        <v>0.2479584281669145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2576662076084623</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.71347509458826</v>
+        <v>2.722099219934157</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.397985262964559</v>
+        <v>-6.383611720721397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.301563677558673</v>
+        <v>0.3073130944559379</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2576662076084623</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.706514482493167</v>
+        <v>2.715138607839064</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.36462205648579</v>
+        <v>-6.350248514242629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3293713145313237</v>
+        <v>0.3351207314285882</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2576662076084623</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.72097683687431</v>
+        <v>2.729600962220207</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.256362919363268</v>
+        <v>-6.241989377120107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3672070898395274</v>
+        <v>0.3729565067367919</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2576662076084623</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.715508957333505</v>
+        <v>2.724133082679402</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.133071784546138</v>
+        <v>-6.118698242302976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4140216377769566</v>
+        <v>0.419771054674221</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1343750727913318</v>
+        <v>-0.1200015305481708</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.78698173223436</v>
+        <v>2.795605857580257</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.080374917414846</v>
+        <v>-6.066001375171685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4428013628667982</v>
+        <v>0.4485507797640631</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08167820566004064</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.82630083075046</v>
+        <v>2.834924956096357</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.836609475431402</v>
+        <v>-5.822235933188241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5360882480072267</v>
+        <v>0.5418376649044916</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08167820566004064</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.822081539097511</v>
+        <v>2.830705664443407</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.74683380305493</v>
+        <v>-5.732460260811768</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5741228308778319</v>
+        <v>0.5798722477750964</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.02007876074573062</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.861165519966113</v>
+        <v>2.86978964531201</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.496983409105855</v>
+        <v>-5.482609866862694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6668050634411635</v>
+        <v>0.6725544803384285</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.02007876074573062</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.853907594949815</v>
+        <v>2.862531720295712</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.321091316638423</v>
+        <v>-5.306717774395262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7407610239487852</v>
+        <v>0.7465104408460497</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.02007876074573062</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.857506718470463</v>
+        <v>2.86613084381636</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.14964485361596</v>
+        <v>-5.135271311372798</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8226671152123242</v>
+        <v>0.8284165321095891</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1513677022767325</v>
+        <v>0.1657412445198935</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.973702102338495</v>
+        <v>2.982326227684392</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.069622566506839</v>
+        <v>-5.055249024263677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8536965076722698</v>
+        <v>0.8594459245695343</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2313899893858535</v>
+        <v>0.2457635316290145</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.020735952220265</v>
+        <v>3.029360077566162</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.005986824272904</v>
+        <v>-4.991613282029743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8838456056201607</v>
+        <v>0.8895950225174254</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.295025731619788</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.063612198614943</v>
+        <v>3.072236323960839</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.912289506056509</v>
+        <v>-4.897915963813348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9025187916905144</v>
+        <v>0.9082682085877791</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.295025731619788</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.044806457398738</v>
+        <v>3.053430582744635</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.922792129121798</v>
+        <v>-4.908418586878637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9000608190892763</v>
+        <v>0.9058102359865408</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2845231085544991</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.040247960184443</v>
+        <v>3.048872085530339</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.850549560950603</v>
+        <v>-4.836176018707442</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9328871601925743</v>
+        <v>0.9386365770898388</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2845231085544991</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.044177274019263</v>
+        <v>3.052801399365159</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.832835874072738</v>
+        <v>-4.818462331829577</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9406512188610605</v>
+        <v>0.946400635758325</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2877044374514159</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.046764655274753</v>
+        <v>3.055388780620649</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.70936160275972</v>
+        <v>-4.694988060516558</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9870389986062613</v>
+        <v>0.9927884155035258</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2877044374514159</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.043762726494746</v>
+        <v>3.052386851840643</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.489340804722709</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.07662635483168</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4289242825193962</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.130073670546149</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.356473115659432</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.145667613258814</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4289242825193962</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.145967853347972</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.236300032294933</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.194882691044915</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5490973658838951</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.219217547806973</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.101046670964956</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.259072138138346</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6843507272138722</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.310457667166399</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.160921498322648</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.221159698596695</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6244758998561801</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.26057026215321</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.041101267411811</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.284376960195238</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6244758998561801</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.275859431387418</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.043570973873617</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.191033276932957</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6220061933943739</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.182021806832776</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.111941160197627</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.082947063888655</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6312818924305889</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.106849087739807</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.223813439823778</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.028634860670086</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6312818924305889</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.097285796371698</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.279333515716368</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.143457667005252</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6312818924305889</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.2343166330639</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.103859255923899</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.218214602914028</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6312818924305889</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.238883865055688</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.095934881338985</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.1971263815092</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6312818924305889</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.214625893816895</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.089656678769136</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.12817597593859</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6375600950004379</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.146931128760254</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.029804059565413</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.162289410052211</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6375600950004379</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.157103515192387</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.943560596539035</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.191733065836623</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6375600950004379</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.152049785766247</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.988867415938015</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.165386113521556</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5967499319912071</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.119339463405234</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.017900520640316</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.154324744673737</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5967499319912071</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.119891336438335</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.925090039189457</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.120721629145447</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6895604134420664</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.104850317200217</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.969479508518884</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.104839317338277</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6451709441126388</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.080090111527161</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.086021113624227</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.053298383807862</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.528629339007296</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.005240856975679</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.125945208206799</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.042820041805501</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.528629339007296</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.010732152806346</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.153725606108152</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.043205084413499</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5008489411059429</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.005561115834073</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.27210627883829</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8342085353220967</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4336310889549667</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.80358612454414</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.380720357281621</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.91091256466397</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4336310889549667</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.923735785263346</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.345311319033478</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.93958920606555</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4336310889549667</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.938248811365669</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.306927656475327</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9523621124311792</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4720147515131179</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.958698450242928</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.129811326440161</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.019937673290547</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4720147515131179</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.95542747908823</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.174903571273707</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.002584167119042</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4101187083437281</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.91897324494851</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.995528150034939</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.068121310920964</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5668954665144468</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.006826275157355</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.040542363555545</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.030923080844311</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5365465711998422</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.969424393300182</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.30754687382798</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.929812839074283</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3421835331568936</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.858498132813359</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.408744655265153</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8885376483959153</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2737747196115744</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.816656766582669</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.40223368865084</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8887419965959571</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2737747196115744</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.814256728136985</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.383195560943543</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8928819668871208</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2155911082803799</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.775871280546514</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.435711363218363</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9911700476113832</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2155911082803799</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.895165682180704</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.449578124552281</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9864566720639494</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1777331915465569</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.873284261126543</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.409095132629936</v>
+        <v>-4.394721590386775</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.008658399229813</v>
+        <v>1.014407816127078</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1777331915465569</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.879292791523469</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.261352162394934</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.965705808601014</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3455405487814401</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.877927427141599</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.345173383669632</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9349709416226155</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3455405487814401</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.88072104867308</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.339020677616848</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9380943724353876</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3516932548342244</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.885075020696409</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.35582997576735</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9304511299152971</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3348839566837227</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.874069918546218</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.293531976991227</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.021705883222567</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3801782209581648</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.967582030907704</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.091741779326069</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9047139640027573</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5781964131273192</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.888684947923324</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.142628492012264</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9546495112504545</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5273097004411247</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.928443152633783</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.056017749362457</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.003921544426421</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6059354316462829</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.990246327472921</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.116227047367742</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9783738060489786</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5457261336409984</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.952656729494422</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.067040398683391</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9965400835626477</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5457261336409984</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.951148347534351</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.022667267044822</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.014152203653511</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.590099265279567</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.977635093952928</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.045147617903707</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9995538574485479</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.590099265279567</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.972028888091518</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.997491887342651</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.024997906700775</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6377549958406227</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.007004083455957</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.896973728843896</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.070097543475002</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7382731543393772</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.072207351929934</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.881068399411544</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.063214347723815</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6591604936301383</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.011494427980263</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.836229997803146</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.085247410977803</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6637039265750078</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.018318190357813</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.855728454045154</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.081608968112077</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6156192852951035</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.993628345220948</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.811525616959254</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.105169705474275</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6598221223810039</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.026029650000326</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.8190852827963</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.100555839608703</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7146255263908232</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.057321692875465</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.660793865257028</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.215120171807452</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7146255263908232</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.108569458058505</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.453151861622552</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.296617677855496</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9222675300252994</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.231595364833443</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.402119768900024</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.311978743182777</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9732996227478273</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.257162848705231</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.336895587772818</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.355255819726364</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.038523803875033</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.313484761474259</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.299468567701684</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.366187600054098</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.043775341904214</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.312596656591048</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.319580223736393</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.359399729971455</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.054802686901634</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.32046985592074</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.291166960636509</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.531322806232619</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9958271241552048</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.445642289294093</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.216384699611496</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.681348619860441</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.070609385180217</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.610624555126918</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.190300615347688</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.683490229579824</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.070609385180217</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.602332531140777</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.102422702238568</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.716834590407251</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.186535027603568</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.670081112178567</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.093530240845284</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.737945980691356</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.186535027603568</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.687635517905358</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.262006357815162</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.662410581307989</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.158587191886988</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.662721863879994</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.815750165185722</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.822182755547627</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.063868522217355</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.587160359266076</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.79302906150257</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.821935219517792</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.063868522217355</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.577824381762981</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.922230874796612</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.929160620051344</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9346667089233127</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.659209419637724</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.948105273270638</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.955888683155381</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9795783176350539</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.723234207358415</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.941050583055465</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.955385915230995</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9866330078502277</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.724142377477065</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.914099358728977</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.976172558606332</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.001513353877947</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.743076738738438</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.935643586559764</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.151657999618977</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.001513353877947</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.927179870883398</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.958051704364636</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.134811447400021</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.001513353877947</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.919296565786391</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.986275939942236</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.125575752718619</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.019490106329255</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.932136616806813</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.995716865830766</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.178053100085053</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.141917223872647</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.061846605054695</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.08459349699924</v>
+        <v>-3.070219954756078</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.145393542162965</v>
+        <v>2.15114295906023</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.053040592704173</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.011411720898912</v>
+        <v>4.020035846244808</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.160923474600146</v>
+        <v>-3.146549932356984</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.112973364016378</v>
+        <v>2.118722780913642</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.053040592704173</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.009523533792687</v>
+        <v>4.018147659138584</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.254587419277687</v>
+        <v>-3.240213877034526</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.070328015748224</v>
+        <v>2.076077432645488</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9593766480266316</v>
+        <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.948145396589025</v>
+        <v>3.956769521934921</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.416155844804942</v>
+        <v>-3.401782302561781</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.004134655747474</v>
+        <v>2.009884072644738</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8325937242287522</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.870509652520449</v>
+        <v>3.879133777866346</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.524456506675062</v>
+        <v>-3.5100829644319</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.973887797865345</v>
+        <v>1.979637214762609</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8325937242287522</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.883583059386368</v>
+        <v>3.892207184732265</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.617603977978428</v>
+        <v>-3.603230435735267</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.928634006126938</v>
+        <v>1.934383423024203</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7097645129462195</v>
+        <v>0.7241380551893805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.801890729399788</v>
+        <v>3.810514854745685</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.645504765087901</v>
+        <v>-3.63113122284474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.915997732410151</v>
+        <v>1.921747149307415</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6751675888032846</v>
+        <v>0.6895411310464457</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.779656616041029</v>
+        <v>3.788280741386926</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.768030867790795</v>
+        <v>-3.753657325547634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.863751735306192</v>
+        <v>1.869501152203457</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5526414861003908</v>
+        <v>0.5670150283435518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.702905398396492</v>
+        <v>3.711529523742389</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.998545363976384</v>
+        <v>-3.984171821733223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.83825189642246</v>
+        <v>1.844001313319725</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.322126989914802</v>
+        <v>0.3365005321579631</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.631302660275642</v>
+        <v>3.639926785621539</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.347290449200828</v>
+        <v>-4.332916906957666</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.83906558133453</v>
+        <v>1.844814998231794</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2133790359959042</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.706365606926151</v>
+        <v>3.714989732272048</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.501276866976968</v>
+        <v>-4.486903324733807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.846451283369713</v>
+        <v>1.852200700266978</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2133790359959042</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.775345876071791</v>
+        <v>3.783970001417687</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.450754963149302</v>
+        <v>-4.436381420906141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.8527112470209</v>
+        <v>1.858460663918165</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2133790359959042</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.761397078191912</v>
+        <v>3.770021203537808</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.703230117157027</v>
+        <v>-4.688856574913865</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.763591674473225</v>
+        <v>1.769341091370489</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2133790359959042</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.773267567247326</v>
+        <v>3.781891692593222</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.996125873636439</v>
+        <v>-4.981752331393277</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.647643906400404</v>
+        <v>1.653393323297668</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2133790359959042</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.774478101766269</v>
+        <v>3.783102227112166</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.182790001771247</v>
+        <v>-5.168416459528085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.577099997373802</v>
+        <v>1.582849414271066</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1866400651713443</v>
+        <v>0.2010136074145054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.762556461498855</v>
+        <v>3.771180586844751</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.328810688685209</v>
+        <v>-5.314437146442048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.513769575344406</v>
+        <v>1.519518992241671</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1775569733774874</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.75218445915873</v>
+        <v>3.760808584504626</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.420524697794795</v>
+        <v>-5.406151155551633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.639288028399616</v>
+        <v>1.645037445296881</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1775569733774874</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.914388515857774</v>
+        <v>3.923012641203671</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.452176356854764</v>
+        <v>-5.437802814611603</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.621474002739443</v>
+        <v>1.627223419636707</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1723885161330472</v>
+        <v>0.1867620583762082</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.906134079474924</v>
+        <v>3.914758204820821</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.534111175123647</v>
+        <v>-5.519737632880486</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.598929493000381</v>
+        <v>1.604678909897645</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.162453770545967</v>
+        <v>0.176827312789128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.910402649691167</v>
+        <v>3.919026775037064</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.636087297372055</v>
+        <v>-5.621713755128893</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.56706468255692</v>
+        <v>1.572814099454185</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.06047764829755942</v>
+        <v>0.07485119054072042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.858142614798025</v>
+        <v>3.866766740143922</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.526081013894833</v>
+        <v>-5.511707471651672</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.603220083191984</v>
+        <v>1.608969500089248</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.08368222021483462</v>
+        <v>0.09805576245799563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.864218245192566</v>
+        <v>3.872842370538462</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.383021438153907</v>
+        <v>-5.368647895910746</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.664693924210328</v>
+        <v>1.670443341107593</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.0916956468048139</v>
+        <v>0.1060691890479749</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.873276311868528</v>
+        <v>3.881900437214424</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.08157471268207</v>
+        <v>-5.067201170438908</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.7925334972816</v>
+        <v>1.798282914178864</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3931423722766512</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.061405230034166</v>
+        <v>4.070029355380062</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.106164956917254</v>
+        <v>-5.091791414674092</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.783668577340237</v>
+        <v>1.789417994237501</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3931423722766512</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.062376407786877</v>
+        <v>4.071000533132773</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.055126580910733</v>
+        <v>-5.040753038667572</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.8049268321226</v>
+        <v>1.810676249019865</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3931423722766512</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.063219312166632</v>
+        <v>4.071843437512529</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.013987286044102</v>
+        <v>-4.999613743800941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.840420648943398</v>
+        <v>1.846170065840663</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.434281667143282</v>
+        <v>0.448655209386443</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.106940987960756</v>
+        <v>4.115565113306652</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.917352374025462</v>
+        <v>-4.902978831782301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.695258609874789</v>
+        <v>1.701008026772053</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5309165791619219</v>
+        <v>0.5452901214050829</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.981105931295875</v>
+        <v>3.989730056641771</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.047933108556305</v>
+        <v>-5.033559566313143</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.646528360136416</v>
+        <v>1.65227777703368</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4003358446310794</v>
+        <v>0.4147093868742404</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.906259534651333</v>
+        <v>3.91488365999723</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.883436774365343</v>
+        <v>-4.869063232122182</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.696753712888883</v>
+        <v>1.702503129786148</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5648321788220413</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.989384154241993</v>
+        <v>3.998008279587889</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.910806707049775</v>
+        <v>-4.896433164806614</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.68499345025154</v>
+        <v>1.690742867148805</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5648321788220413</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.988571864678423</v>
+        <v>3.997195990024319</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.921191901939665</v>
+        <v>-4.906818359696503</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.690708151420657</v>
+        <v>1.696457568317921</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.554446983932152</v>
+        <v>0.568820526175313</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.992209526869561</v>
+        <v>4.000833652215458</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.93978006066189</v>
+        <v>-4.925406518418728</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.754109893708192</v>
+        <v>1.759859310605457</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5358588252099266</v>
+        <v>0.5502323674530876</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.051893637412651</v>
+        <v>4.060517762758548</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.940078607357925</v>
+        <v>-4.925705065114764</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.750859485848076</v>
+        <v>1.756608902745341</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5355602785138907</v>
+        <v>0.5499338207570517</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.048583520213328</v>
+        <v>4.057207645559225</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.839255473667498</v>
+        <v>-4.824881931424336</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.795719634263639</v>
+        <v>1.801469051160903</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5480244939982445</v>
+        <v>0.5623980362414055</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.060592944443332</v>
+        <v>4.069217069789229</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.648474112915091</v>
+        <v>-4.634100570671929</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.872161432043145</v>
+        <v>1.877910848940409</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7388058547506519</v>
+        <v>0.7531793969938129</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.175191014373319</v>
+        <v>4.183815139719216</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.541510755065669</v>
+        <v>-4.527137212822508</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.89478362092051</v>
+        <v>1.900533037817774</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7972704627104533</v>
+        <v>0.8116440049536143</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.190106624886797</v>
+        <v>4.198730750232693</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.486180167163907</v>
+        <v>-4.471806624920745</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.951882792693273</v>
+        <v>1.957632209590538</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8526010506122155</v>
+        <v>0.8669745928553765</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.258271914239913</v>
+        <v>4.266896039585809</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.474126040250944</v>
+        <v>-4.459752498007783</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.950391011359896</v>
+        <v>1.956140428257161</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8646551775251783</v>
+        <v>0.8790287197683393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.259190958289128</v>
+        <v>4.267815083635025</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.515281159819165</v>
+        <v>-4.500907617576003</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.935809593716743</v>
+        <v>1.941559010614008</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8235000579569574</v>
+        <v>0.8378736002001184</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.236378516732332</v>
+        <v>4.245002642078228</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.447232597127635</v>
+        <v>-4.432859054884474</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.975880044671238</v>
+        <v>1.981629461568502</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8915486206484872</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.290058680225131</v>
+        <v>4.298682805571028</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.678832990297136</v>
+        <v>-4.664459448053974</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.903442557577032</v>
+        <v>1.909191974474296</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8915486206484872</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.310261350398726</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.696905498588747</v>
+        <v>-4.682531956345586</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.896213554260387</v>
+        <v>1.901962971157652</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8915486206484872</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.310261350398726</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.872012331165193</v>
+        <v>-4.857638788922031</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.786422734823276</v>
+        <v>1.79217215172054</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8915486206484872</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.270513263992193</v>
+        <v>4.279137389338089</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.840726310624738</v>
+        <v>-4.826352768381576</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.805959762036398</v>
+        <v>1.811709178933662</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9228346411889425</v>
+        <v>0.9372081834321035</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.296307495313406</v>
+        <v>4.304931620659302</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.687700918511453</v>
+        <v>-4.618135634760093</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.966340918454616</v>
+        <v>1.99416703195516</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.075860033302227</v>
+        <v>1.145425317053586</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.487293730154281</v>
+        <v>4.529032900405096</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.716008232384723</v>
+        <v>-4.646442948633363</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.1424842178136</v>
+        <v>2.170310331314144</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.075860033302227</v>
+        <v>1.145425317053586</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.674759955062573</v>
+        <v>4.716499125313389</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.882601457498246</v>
+        <v>-4.813036173746886</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.045249879122273</v>
+        <v>2.073075992622817</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9092668081887043</v>
+        <v>0.9788320919400639</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.544206971348542</v>
+        <v>4.585946141599358</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.85956566413668</v>
+        <v>-4.79000038038532</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.058140599128618</v>
+        <v>2.085966712629161</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9092668081887043</v>
+        <v>0.9788320919400639</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.54788337401026</v>
+        <v>4.589622544261076</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.830319683680983</v>
+        <v>-4.760754399929623</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.067457046434392</v>
+        <v>2.095283159934935</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9092668081887043</v>
+        <v>0.9788320919400639</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.545501429133755</v>
+        <v>4.58724059938457</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.937245231558834</v>
+        <v>-4.867679947807474</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.021980066440886</v>
+        <v>2.04980617994143</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.802341260310853</v>
+        <v>0.8719065440622126</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.478639339564679</v>
+        <v>4.520378509815495</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.082263790066083</v>
+        <v>-5.012698506314723</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.965401445181221</v>
+        <v>1.993227558681764</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6573227018036044</v>
+        <v>0.726887985554964</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.393057006603564</v>
+        <v>4.43479617685438</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.2006055558508</v>
+        <v>-5.13104027209944</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.017995978125087</v>
+        <v>2.04582209162563</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6680087403664945</v>
+        <v>0.7375740241178541</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.499399868999051</v>
+        <v>4.541139039249867</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.252015978171508</v>
+        <v>-5.182450694420148</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.995217506322742</v>
+        <v>2.023043619823286</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6680087403664945</v>
+        <v>0.7375740241178541</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.49718556612499</v>
+        <v>4.538924736375805</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.33143542937926</v>
+        <v>-5.2618701456279</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.963352853913931</v>
+        <v>1.991178967414475</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6680087403664945</v>
+        <v>0.7375740241178541</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.497088694199279</v>
+        <v>4.538827864450095</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.426898427296478</v>
+        <v>-5.357333143545118</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.925161548305087</v>
+        <v>1.952987661805631</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6680087403664945</v>
+        <v>0.7375740241178541</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.497082587757323</v>
+        <v>4.538821758008138</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.466918425340261</v>
+        <v>-5.397353141588901</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.907249945650185</v>
+        <v>1.935076059150729</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6279887423227106</v>
+        <v>0.6975540260740702</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.471166985493663</v>
+        <v>4.512906155744479</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.522287587472455</v>
+        <v>-5.452722303721095</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.890836098545034</v>
+        <v>1.918662212045578</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6279887423227106</v>
+        <v>0.6975540260740702</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.47690080324139</v>
+        <v>4.518639973492205</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.567725367303282</v>
+        <v>-5.498160083551922</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.872199349955636</v>
+        <v>1.90002546345618</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.585143751644551</v>
+        <v>0.6547090353959106</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.450732172177426</v>
+        <v>4.492471342428242</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.479518533155704</v>
+        <v>-5.409953249404344</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.927356476464986</v>
+        <v>1.95518258996553</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.585143751644551</v>
+        <v>0.6547090353959106</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.470606565027746</v>
+        <v>4.512345735278561</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.373483537950395</v>
+        <v>-5.303918254199035</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.953471175071838</v>
+        <v>1.981297288572382</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.585143751644551</v>
+        <v>0.6547090353959106</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.454307265552473</v>
+        <v>4.496046435803289</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.1902718748173</v>
+        <v>-5.12070659106594</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.029186789789121</v>
+        <v>2.057012903289665</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.585143751644551</v>
+        <v>0.6547090353959106</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.456738215016519</v>
+        <v>4.498477385267335</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.118550427803449</v>
+        <v>-5.048985144052089</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.023666554442551</v>
+        <v>2.051492667943095</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6568651986584017</v>
+        <v>0.7264304824097613</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.465562269072719</v>
+        <v>4.507301439323535</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.096177402195742</v>
+        <v>-5.026612118444382</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.979531510606805</v>
+        <v>2.007357624107349</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6681209497713032</v>
+        <v>0.7376862335226628</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.419231465661632</v>
+        <v>4.460970635912448</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.129193698106487</v>
+        <v>-5.059628414355127</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.151523197127863</v>
+        <v>2.179349310628407</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5986835731045517</v>
+        <v>0.6682488568559113</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.562767244546936</v>
+        <v>4.604506414797752</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.117666062456879</v>
+        <v>-5.048100778705519</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.148055477215955</v>
+        <v>2.175881590716499</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6576842313059141</v>
+        <v>0.7272495150572738</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.590088865296003</v>
+        <v>4.631828035546818</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.215007563799247</v>
+        <v>-5.145442280047887</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.112786989200796</v>
+        <v>2.14061310270134</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6132640491404258</v>
+        <v>0.6828293328917854</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.567104868518499</v>
+        <v>4.608844038769314</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.300863593139214</v>
+        <v>-5.231298309387854</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.079695659657648</v>
+        <v>2.107521773158192</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5708879799142907</v>
+        <v>0.6404532636656504</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.542930309175656</v>
+        <v>4.584669479426471</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.309700390555333</v>
+        <v>-5.240135106803973</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.058580142511702</v>
+        <v>2.086406256012246</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.56344580727294</v>
+        <v>0.6330110910242996</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.520884207411346</v>
+        <v>4.562623377662162</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.401082953120792</v>
+        <v>-5.331517669369432</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.032191628530568</v>
+        <v>2.060017742031112</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4720632447074818</v>
+        <v>0.5416285284588414</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.476219180917122</v>
+        <v>4.517958351167938</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.389376235133786</v>
+        <v>-5.319810951382426</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.139002573549639</v>
+        <v>2.166828687050183</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4837699626944882</v>
+        <v>0.5533352464458478</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.585371469533594</v>
+        <v>4.627110639784409</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.802282022642979</v>
+        <v>3.855067360445311</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.289712731050123</v>
+        <v>-5.220147447298763</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.181900313914508</v>
+        <v>2.209726427415053</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5469570458981747</v>
+        <v>0.6165223296495342</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.62631605818721</v>
+        <v>4.668055228438026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>131.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-683.6%</t>
+          <t>-682.9%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-155.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.2%</t>
+          <t>328.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.4%</t>
+          <t>-304.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2077"/>
+  <dimension ref="A1:G2078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.802728266997576</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.3384871294309182</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.314373103356599</v>
+        <v>-0.3191826284292562</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.871310998529737</v>
+        <v>2.868425283486143</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.717763600268256</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.385379337346305</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2294084366272794</v>
+        <v>-0.2342179616999366</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.935196139790988</v>
+        <v>2.932310424747393</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.823353590041361</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>0.2151674118378444</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3349984264003837</v>
+        <v>-0.3398079514730409</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.743866216327906</v>
+        <v>2.740980501284312</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.755119005415933</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.2910055875651016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3165831035278477</v>
+        <v>-0.3213926286005049</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803459751928514</v>
+        <v>2.80057403688492</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.607178964008334</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.2335607954897343</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2962621876192902</v>
+        <v>-0.3010717126919474</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.699031492835242</v>
+        <v>2.696145777791647</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.554209441754345</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.2460346181378519</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2481021904379585</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.722099219934157</v>
+        <v>2.719213504890562</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.388421245794055</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.3053892844268749</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2481021904379585</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.715138607839064</v>
+        <v>2.712252892795469</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.355058039315286</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.3331969213995256</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2481021904379585</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.729600962220207</v>
+        <v>2.726715247176612</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.246798902192764</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.3710326967077293</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2481021904379585</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.724133082679402</v>
+        <v>2.721247367635807</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-6.123507767375633</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.4178472446451584</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1200015305481708</v>
+        <v>-0.124811055620828</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.795605857580257</v>
+        <v>2.792720142536663</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-6.070810900244342</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.446626969735</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.07211418848953682</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.834924956096357</v>
+        <v>2.832039241052762</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.827045458260898</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.5399138548754285</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.07211418848953682</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.830705664443407</v>
+        <v>2.827819949399813</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.737269785884425</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.5779484377460333</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0105147435752268</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.86978964531201</v>
+        <v>2.866903930268415</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.487419391935351</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.6706306703093654</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0105147435752268</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.862531720295712</v>
+        <v>2.859646005252117</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.311527299467919</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.7445866308169871</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0105147435752268</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.86613084381636</v>
+        <v>2.863245128772766</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.140080836445455</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.826492722080526</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1657412445198935</v>
+        <v>0.1609317194472363</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.982326227684392</v>
+        <v>2.979440512640798</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-5.060058549336334</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.8575221145404712</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2457635316290145</v>
+        <v>0.2409540065563573</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.029360077566162</v>
+        <v>3.026474362522567</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-4.9964228071024</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.8876712124883626</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.309399273862949</v>
+        <v>0.3045897487902918</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.072236323960839</v>
+        <v>3.069350608917245</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.902725488886005</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.9063443985587161</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.309399273862949</v>
+        <v>0.3045897487902918</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.053430582744635</v>
+        <v>3.050544867701041</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.913228111951294</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.9038864259574779</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.294087125725003</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>3.045986370486745</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.840985543780099</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.936712767060776</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.294087125725003</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>3.049915684321565</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.823271856902234</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9444768257292622</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2972684546219198</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>3.052503065577055</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.699797585589216</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>0.990864605474463</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2972684546219198</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>3.049501136797049</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.479776787552205</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.080451961699881</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4384882996899</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.135812080848451</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.346909098488927</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.149493220127016</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4384882996899</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.151706263650274</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.226736015124429</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.198708297913117</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5586613830543989</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.224955958109275</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.091482653794452</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.262897745006548</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6939147443843761</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.316196077468701</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.151357481152144</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.224985305464897</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6340399170266839</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.266308672455512</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-4.031537250241307</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.28820256706344</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6340399170266839</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.281597841689721</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-4.034006956703113</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.194858883801159</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.6315702105648777</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.187760217135078</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.102377143027123</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.086772670756856</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6408459096010927</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.112587498042109</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.214249422653274</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.032460467538287</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6408459096010927</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.103024206674</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.269769498545863</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.147283273873454</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6408459096010927</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.240055043366203</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.094295238753395</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.222040209782229</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6408459096010927</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.24462227535799</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.08637086416848</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.200951988377402</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6408459096010927</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.220364304119197</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.080092661598631</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.132001582806791</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6471241121709417</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.152669539062556</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-4.020240042394908</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.166115016920413</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6471241121709417</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.162841925494689</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.933996579368531</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.195558672704824</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6471241121709417</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.157788196068549</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.97930339876751</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.169211720389758</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.6063139491617109</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.125077873707536</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-4.008336503469812</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.158150351541939</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.6063139491617109</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.125629746740638</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.915526022018952</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.124547236013648</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6991244306125702</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.110588727502519</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.95991549134838</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.108664924206478</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.6547349612831426</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.085828521829463</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.076457096453723</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.057123990676064</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5381933561777998</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>3.01097926727798</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.116381191036295</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.046645648673703</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5381933561777998</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>3.016470563108648</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.144161588937648</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.0470306912817</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.5104129582764467</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>3.011299526136375</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.262542261667786</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8380341421902984</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4431951061254705</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.809324534846443</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.371156340111117</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.9147381715321716</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4431951061254705</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.929474195565648</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.335747301862974</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9434148129337516</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4431951061254705</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.943987221667971</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.297363639304823</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9561877192993808</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4815787686836217</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.964436860545231</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.120247309269657</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.023763280158749</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4815787686836217</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.961165889390533</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.165339554103203</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.006409773987244</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.4196827255142319</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.924711655250812</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.985964132864435</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.071946917789165</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.5764594836849506</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>3.012564685459657</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-4.030978346385041</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.034748687712513</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.546110588370346</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.975162803602484</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.297982856657476</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9336384459424847</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.3517475503273974</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.864236543115661</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.399180638094649</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.892363255264117</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2833387367820782</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.822395176884971</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.392669671480336</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.8925676034641588</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.2833387367820782</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.819995138439288</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.373631543773039</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.8967075737553225</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2251551254508837</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.781609690848816</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.426147346047859</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>0.9949956544795848</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2251551254508837</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.900904092483006</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.440014107381777</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>0.9902822789321513</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1872972087170607</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.879022671428846</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.394721590386775</v>
+        <v>-4.399531115459432</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014407816127078</v>
+        <v>1.012484006098015</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1872972087170607</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.885031201825772</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.246978620151772</v>
+        <v>-4.251788145224429</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9714552254982785</v>
+        <v>0.9695314154692156</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3551045659519439</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.883665837443901</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.330799841426471</v>
+        <v>-4.335609366499128</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9407203585198802</v>
+        <v>0.9387965484908172</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3551045659519439</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.886459458975382</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.324647135373686</v>
+        <v>-4.329456660446343</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9438437893326523</v>
+        <v>0.9419199793035893</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.3612572720047282</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.890813430998711</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.341456433524188</v>
+        <v>-4.346265958596845</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9362005468125618</v>
+        <v>0.9342767367834988</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.3444479738542265</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.879808328848521</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.279158434748066</v>
+        <v>-4.283967959820723</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027455300119831</v>
+        <v>1.025531490090769</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.3897422381286686</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.973320441210006</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.077368237082908</v>
+        <v>-4.082177762155565</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9104633809000218</v>
+        <v>0.9085395708709589</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.587760430297823</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.894423358225626</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.128254949769103</v>
+        <v>-4.13306447484176</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9603989281477192</v>
+        <v>0.9584751181186562</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.5368737176116285</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.934181562936085</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.041644207119296</v>
+        <v>-4.046453732191953</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009670961323685</v>
+        <v>1.007747151294623</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.6154994488167868</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.995984737775223</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.101853505124581</v>
+        <v>-4.106663030197238</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9841232229462431</v>
+        <v>0.9821994129171803</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5552901508115022</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.958395139796724</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.057476381512886</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>1.000365690430849</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5552901508115022</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.956886757836653</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-4.013103249874318</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.017977810521713</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5996632824500708</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.98337350425523</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.035583600733203</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>1.00337946431675</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5996632824500708</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.977767298393821</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-3.987927870172147</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.028823513568977</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.6473190130111265</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.012742493758259</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.887409711673392</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.073923150343203</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.747837171509881</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.077945762232236</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.87150438224104</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.067039954592017</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.6687245108006421</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.017232838282565</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.826665980632642</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.089073017846004</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.6732679437455116</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.024056600660115</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.84616443687465</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.085434574980279</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.6251833024656073</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.999366755523251</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.801961599788749</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.108995312342477</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.6693861395515077</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.031768060302628</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.809521265625796</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.104381446476905</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.724189543561327</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.063060103177767</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.651229848086524</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.218945778675654</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.724189543561327</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.114307868360807</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.443587844452048</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.300443284723697</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.9318315471958032</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.237333775135746</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.39255575172952</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.315804350050979</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.9828636399183311</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.262901259007533</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.327331570602314</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.359081426594566</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.048087821045537</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.319223171776561</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.28990455053118</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.3700132069223</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.053339359074718</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.31833506689335</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.310016206565888</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.363225336839657</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.064366704072137</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.326208266223042</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.281602943466005</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.535148413100821</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>1.005391141325709</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.451380699596395</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.206820682440992</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.685174226728643</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.080173402350721</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.61636296542922</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.180736598177184</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.687315836448025</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.080173402350721</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.608070941443079</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.092858685068064</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.720660197275453</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.196099044774072</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.675819522480869</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.08396622367478</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.741771587559558</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.196099044774072</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.693373928207661</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.252442340644658</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.666236188176191</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.168151209057491</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.668460274182296</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.806186148015218</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.826008362415829</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.073432539387859</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.592898769568378</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.783465044332066</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.825760826385994</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.073432539387859</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.583562792065283</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.912666857626108</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.932986226919546</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.9442307260938165</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.664947829940027</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.938541256100134</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.959714290023582</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>0.9891423348055577</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.728972617660718</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.93148656588496</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.959211522099197</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9961970250207315</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.729880787779368</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.904535341558472</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.979998165474534</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.011077371048451</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.74881514904074</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.926079569389259</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.155483606487179</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.011077371048451</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.9329182811857</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.948487687194131</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.138637054268223</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.011077371048451</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.925034976088694</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-2.976711922771732</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.12940135958682</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.029054123499759</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.937875027109116</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-2.986152848660262</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.181878706953255</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.151481241043151</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.067585015356998</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.070219954756078</v>
+        <v>-3.075029479828736</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.15114295906023</v>
+        <v>2.149219149031167</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.067414134947334</v>
+        <v>1.062604609874677</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.020035846244808</v>
+        <v>4.017150131201214</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.146549932356984</v>
+        <v>-3.151359457429642</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118722780913642</v>
+        <v>2.116798970884579</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.067414134947334</v>
+        <v>1.062604609874677</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.018147659138584</v>
+        <v>4.015261944094989</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.240213877034526</v>
+        <v>-3.245023402107183</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076077432645488</v>
+        <v>2.074153622616425</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>0.9689406651971354</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.953883806891327</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.401782302561781</v>
+        <v>-3.406591827634438</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009884072644738</v>
+        <v>2.007960262615676</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.842157741399256</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.876248062822752</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5100829644319</v>
+        <v>-3.514892489504557</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.979637214762609</v>
+        <v>1.977713404733546</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.842157741399256</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.88932146968867</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.603230435735267</v>
+        <v>-3.608039960807924</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934383423024203</v>
+        <v>1.93245961299514</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7241380551893805</v>
+        <v>0.7193285301167233</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810514854745685</v>
+        <v>3.807629139702091</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.63113122284474</v>
+        <v>-3.635940747917397</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.921747149307415</v>
+        <v>1.919823339278352</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6895411310464457</v>
+        <v>0.6847316059737885</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788280741386926</v>
+        <v>3.785395026343332</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.753657325547634</v>
+        <v>-3.758466850620291</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869501152203457</v>
+        <v>1.867577342174394</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5670150283435518</v>
+        <v>0.5622055032708946</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711529523742389</v>
+        <v>3.708643808698795</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.984171821733223</v>
+        <v>-3.98898134680588</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.844001313319725</v>
+        <v>1.842077503290662</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3365005321579631</v>
+        <v>0.3316910070853059</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639926785621539</v>
+        <v>3.637041070577945</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.332916906957666</v>
+        <v>-4.337726432030323</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844814998231794</v>
+        <v>1.842891188202731</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2229430531664081</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714989732272048</v>
+        <v>3.712104017228453</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.486903324733807</v>
+        <v>-4.491712849806464</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852200700266978</v>
+        <v>1.850276890237915</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2229430531664081</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783970001417687</v>
+        <v>3.781084286374093</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.436381420906141</v>
+        <v>-4.441190945978798</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858460663918165</v>
+        <v>1.856536853889102</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2229430531664081</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770021203537808</v>
+        <v>3.767135488494214</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.688856574913865</v>
+        <v>-4.693666099986523</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769341091370489</v>
+        <v>1.767417281341426</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2229430531664081</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781891692593222</v>
+        <v>3.779005977549628</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.981752331393277</v>
+        <v>-4.986561856465935</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653393323297668</v>
+        <v>1.651469513268605</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2229430531664081</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783102227112166</v>
+        <v>3.780216512068571</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.168416459528085</v>
+        <v>-5.173225984600743</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582849414271066</v>
+        <v>1.580925604242004</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2010136074145054</v>
+        <v>0.1962040823418482</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771180586844751</v>
+        <v>3.768294871801157</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.314437146442048</v>
+        <v>-5.319246671514705</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519518992241671</v>
+        <v>1.517595182212608</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.1871209905479912</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760808584504626</v>
+        <v>3.757922869461032</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.406151155551633</v>
+        <v>-5.41096068062429</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645037445296881</v>
+        <v>1.643113635267818</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.1871209905479912</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923012641203671</v>
+        <v>3.920126926160076</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.437802814611603</v>
+        <v>-5.44261233968426</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627223419636707</v>
+        <v>1.625299609607644</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1867620583762082</v>
+        <v>0.181952533303551</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914758204820821</v>
+        <v>3.911872489777227</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.519737632880486</v>
+        <v>-5.524547157953143</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604678909897645</v>
+        <v>1.602755099868582</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.176827312789128</v>
+        <v>0.1720177877164708</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919026775037064</v>
+        <v>3.916141059993469</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.621713755128893</v>
+        <v>-5.626523280201551</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572814099454185</v>
+        <v>1.570890289425122</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07485119054072042</v>
+        <v>0.07004166546806323</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866766740143922</v>
+        <v>3.863881025100327</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.511707471651672</v>
+        <v>-5.516516996724329</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608969500089248</v>
+        <v>1.607045690060186</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09805576245799563</v>
+        <v>0.09324623738533844</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872842370538462</v>
+        <v>3.869956655494868</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.368647895910746</v>
+        <v>-5.373457420983403</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670443341107593</v>
+        <v>1.66851953107853</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1060691890479749</v>
+        <v>0.1012596639753177</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881900437214424</v>
+        <v>3.87901472217083</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.067201170438908</v>
+        <v>-5.072010695511565</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798282914178864</v>
+        <v>1.796359104149801</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.402706389447155</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070029355380062</v>
+        <v>4.067143640336468</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.091791414674092</v>
+        <v>-5.096600939746749</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789417994237501</v>
+        <v>1.787494184208438</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.402706389447155</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071000533132773</v>
+        <v>4.068114818089179</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.040753038667572</v>
+        <v>-5.045562563740229</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810676249019865</v>
+        <v>1.808752438990802</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.402706389447155</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071843437512529</v>
+        <v>4.068957722468935</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.999613743800941</v>
+        <v>-5.004423268873598</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846170065840663</v>
+        <v>1.8442462558116</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.448655209386443</v>
+        <v>0.4438456843137858</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115565113306652</v>
+        <v>4.112679398263058</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.902978831782301</v>
+        <v>-4.907788356854958</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701008026772053</v>
+        <v>1.69908421674299</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5452901214050829</v>
+        <v>0.5404805963324257</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989730056641771</v>
+        <v>3.986844341598177</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.033559566313143</v>
+        <v>-5.038369091385801</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65227777703368</v>
+        <v>1.650353967004618</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4147093868742404</v>
+        <v>0.4098998618015832</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488365999723</v>
+        <v>3.911997944953635</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.869063232122182</v>
+        <v>-4.873872757194839</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702503129786148</v>
+        <v>1.700579319757085</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5743961959925451</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998008279587889</v>
+        <v>3.995122564544295</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.896433164806614</v>
+        <v>-4.901242689879271</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690742867148805</v>
+        <v>1.688819057119742</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.5743961959925451</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997195990024319</v>
+        <v>3.994310274980725</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.906818359696503</v>
+        <v>-4.91162788476916</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696457568317921</v>
+        <v>1.694533758288858</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.568820526175313</v>
+        <v>0.5640110011026558</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000833652215458</v>
+        <v>3.997947937171864</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.925406518418728</v>
+        <v>-4.930216043491385</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759859310605457</v>
+        <v>1.757935500576393</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5502323674530876</v>
+        <v>0.5454228423804304</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060517762758548</v>
+        <v>4.057632047714954</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.925705065114764</v>
+        <v>-4.930514590187421</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756608902745341</v>
+        <v>1.754685092716278</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5499338207570517</v>
+        <v>0.5451242956843945</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057207645559225</v>
+        <v>4.054321930515631</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.824881931424336</v>
+        <v>-4.829691456496993</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801469051160903</v>
+        <v>1.79954524113184</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5623980362414055</v>
+        <v>0.5575885111687483</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069217069789229</v>
+        <v>4.066331354745634</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.634100570671929</v>
+        <v>-4.638910095744587</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877910848940409</v>
+        <v>1.875987038911346</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7531793969938129</v>
+        <v>0.7483698719211557</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183815139719216</v>
+        <v>4.180929424675622</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527137212822508</v>
+        <v>-4.531946737895165</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900533037817774</v>
+        <v>1.898609227788711</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8116440049536143</v>
+        <v>0.8068344798809571</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198730750232693</v>
+        <v>4.195845035189099</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471806624920745</v>
+        <v>-4.476616149993403</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.957632209590538</v>
+        <v>1.955708399561475</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8669745928553765</v>
+        <v>0.8621650677827193</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266896039585809</v>
+        <v>4.264010324542215</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459752498007783</v>
+        <v>-4.46456202308044</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.956140428257161</v>
+        <v>1.954216618228098</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8790287197683393</v>
+        <v>0.8742191946956821</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267815083635025</v>
+        <v>4.264929368591431</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.500907617576003</v>
+        <v>-4.505717142648661</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.941559010614008</v>
+        <v>1.939635200584945</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8378736002001184</v>
+        <v>0.8330640751274612</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245002642078228</v>
+        <v>4.242116927034633</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.432859054884474</v>
+        <v>-4.437668579957131</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981629461568502</v>
+        <v>1.979705651539439</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.901112637818991</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298682805571028</v>
+        <v>4.295797090527434</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.664459448053974</v>
+        <v>-4.669268973126631</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909191974474296</v>
+        <v>1.907268164445234</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.901112637818991</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318885475744622</v>
+        <v>4.315999760701028</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.682531956345586</v>
+        <v>-4.687341481418243</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901962971157652</v>
+        <v>1.900039161128589</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.901112637818991</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318885475744622</v>
+        <v>4.315999760701028</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.857638788922031</v>
+        <v>-4.862448313994689</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79217215172054</v>
+        <v>1.790248341691477</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.901112637818991</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.279137389338089</v>
+        <v>4.276251674294495</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.826352768381576</v>
+        <v>-4.831162293454233</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.811709178933662</v>
+        <v>1.8097853689046</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9372081834321035</v>
+        <v>0.9323986583594464</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.304931620659302</v>
+        <v>4.302045905615708</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.618135634760093</v>
+        <v>-4.611481141859566</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.99416703195516</v>
+        <v>1.996828829115371</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.145425317053586</v>
+        <v>1.152079809954113</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.529032900405096</v>
+        <v>4.533025596145412</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.646442948633363</v>
+        <v>-4.639788455732837</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.170310331314144</v>
+        <v>2.172972128474354</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.145425317053586</v>
+        <v>1.152079809954113</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.716499125313389</v>
+        <v>4.720491821053705</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.813036173746886</v>
+        <v>-4.806381680846359</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.073075992622817</v>
+        <v>2.075737789783028</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9788320919400639</v>
+        <v>0.9854865848405907</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.585946141599358</v>
+        <v>4.589938837339673</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.79000038038532</v>
+        <v>-4.783345887484793</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.085966712629161</v>
+        <v>2.088628509789372</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9788320919400639</v>
+        <v>0.9854865848405907</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.589622544261076</v>
+        <v>4.593615240001391</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.760754399929623</v>
+        <v>-4.754099907029096</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.095283159934935</v>
+        <v>2.097944957095146</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9788320919400639</v>
+        <v>0.9854865848405907</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.58724059938457</v>
+        <v>4.591233295124886</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.867679947807474</v>
+        <v>-4.861025454906947</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.04980617994143</v>
+        <v>2.052467977101641</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8719065440622126</v>
+        <v>0.8785610369627394</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.520378509815495</v>
+        <v>4.524371205555811</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.012698506314723</v>
+        <v>-5.006044013414196</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.993227558681764</v>
+        <v>1.995889355841975</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.726887985554964</v>
+        <v>0.7335424784554908</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.43479617685438</v>
+        <v>4.438788872594696</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.13104027209944</v>
+        <v>-5.124385779198914</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.04582209162563</v>
+        <v>2.048483888785841</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7375740241178541</v>
+        <v>0.7442285170183809</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.541139039249867</v>
+        <v>4.545131734990183</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.182450694420148</v>
+        <v>-5.175796201519621</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.023043619823286</v>
+        <v>2.025705416983497</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7375740241178541</v>
+        <v>0.7442285170183809</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.538924736375805</v>
+        <v>4.542917432116122</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.2618701456279</v>
+        <v>-5.255215652727373</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.991178967414475</v>
+        <v>1.993840764574686</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7375740241178541</v>
+        <v>0.7442285170183809</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.538827864450095</v>
+        <v>4.542820560190411</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.357333143545118</v>
+        <v>-5.350678650644591</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.952987661805631</v>
+        <v>1.955649458965842</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7375740241178541</v>
+        <v>0.7442285170183809</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.538821758008138</v>
+        <v>4.542814453748455</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.397353141588901</v>
+        <v>-5.390698648688375</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.935076059150729</v>
+        <v>1.937737856310939</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6975540260740702</v>
+        <v>0.704208518974597</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.512906155744479</v>
+        <v>4.516898851484795</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.452722303721095</v>
+        <v>-5.446067810820568</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.918662212045578</v>
+        <v>1.921324009205788</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6975540260740702</v>
+        <v>0.704208518974597</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.518639973492205</v>
+        <v>4.522632669232522</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.498160083551922</v>
+        <v>-5.491505590651395</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.90002546345618</v>
+        <v>1.90268726061639</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6547090353959106</v>
+        <v>0.6613635282964374</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.492471342428242</v>
+        <v>4.496464038168559</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.409953249404344</v>
+        <v>-5.403298756503817</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.95518258996553</v>
+        <v>1.957844387125741</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6547090353959106</v>
+        <v>0.6613635282964374</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.512345735278561</v>
+        <v>4.516338431018878</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.303918254199035</v>
+        <v>-5.297263761298508</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.981297288572382</v>
+        <v>1.983959085732593</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6547090353959106</v>
+        <v>0.6613635282964374</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.496046435803289</v>
+        <v>4.500039131543605</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.12070659106594</v>
+        <v>-5.114052098165413</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.057012903289665</v>
+        <v>2.059674700449876</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6547090353959106</v>
+        <v>0.6613635282964374</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.498477385267335</v>
+        <v>4.502470081007651</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.048985144052089</v>
+        <v>-5.042330651151562</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.051492667943095</v>
+        <v>2.054154465103306</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7264304824097613</v>
+        <v>0.733084975310288</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.507301439323535</v>
+        <v>4.511294135063851</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.026612118444382</v>
+        <v>-5.019957625543856</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.007357624107349</v>
+        <v>2.01001942126756</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7376862335226628</v>
+        <v>0.7443407264231896</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.460970635912448</v>
+        <v>4.464963331652763</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.059628414355127</v>
+        <v>-5.0529739214546</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.179349310628407</v>
+        <v>2.182011107788618</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6682488568559113</v>
+        <v>0.6749033497564381</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.604506414797752</v>
+        <v>4.608499110538068</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.048100778705519</v>
+        <v>-5.041446285804992</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.175881590716499</v>
+        <v>2.17854338787671</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7272495150572738</v>
+        <v>0.7339040079578005</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.631828035546818</v>
+        <v>4.635820731287135</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.145442280047887</v>
+        <v>-5.13878778714736</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.14061310270134</v>
+        <v>2.143274899861551</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6828293328917854</v>
+        <v>0.6894838257923122</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.608844038769314</v>
+        <v>4.61283673450963</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.231298309387854</v>
+        <v>-5.224643816487327</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.107521773158192</v>
+        <v>2.110183570318403</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6404532636656504</v>
+        <v>0.6471077565661771</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.584669479426471</v>
+        <v>4.588662175166787</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.240135106803973</v>
+        <v>-5.233480613903446</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.086406256012246</v>
+        <v>2.089068053172457</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6330110910242996</v>
+        <v>0.6396655839248264</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.562623377662162</v>
+        <v>4.566616073402479</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.331517669369432</v>
+        <v>-5.324863176468905</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.060017742031112</v>
+        <v>2.062679539191323</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5416285284588414</v>
+        <v>0.5482830213593681</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.517958351167938</v>
+        <v>4.521951046908253</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.319810951382426</v>
+        <v>-5.313156458481899</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.166828687050183</v>
+        <v>2.169490484210393</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5533352464458478</v>
+        <v>0.5599897393463745</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.627110639784409</v>
+        <v>4.631103335524725</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,45 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.855067360445311</v>
+        <v>3.682496284692309</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.220147447298763</v>
+        <v>-5.213492954398236</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.209726427415053</v>
+        <v>2.212388224575263</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.6165223296495342</v>
+        <v>0.623176822550061</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.668055228438026</v>
+        <v>4.672047924178342</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="2" t="n">
+        <v>45540</v>
+      </c>
+      <c r="B2078" t="n">
+        <v>3.853613255566063</v>
+      </c>
+      <c r="C2078" t="n">
+        <v>4.434916007410366</v>
+      </c>
+      <c r="D2078" t="n">
+        <v>-5.213492954398236</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>2.212388224575263</v>
+      </c>
+      <c r="F2078" t="n">
+        <v>0.623176822550061</v>
+      </c>
+      <c r="G2078" t="n">
+        <v>4.427979804396734</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>108.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.7%</t>
+          <t>419.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.9%</t>
+          <t>-699.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.0%</t>
+          <t>-161.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>328.6%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-304.7%</t>
+          <t>-278.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-168.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-26.5%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.162891593480584</v>
+        <v>-9.325868545081876</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4867688715912042</v>
+        <v>-0.5519596522317212</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.585050501644609</v>
+        <v>-1.611472483353487</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.227713889128012</v>
+        <v>2.211860700102685</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.038312937142992</v>
+        <v>-9.201289888744284</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4357982645001086</v>
+        <v>-0.5009890451406256</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.585050501644609</v>
+        <v>-1.611472483353487</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.228853033684071</v>
+        <v>2.212999844658744</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.013276255574482</v>
+        <v>-9.176253207175774</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4231498177105966</v>
+        <v>-0.4883405983511135</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.559721414093873</v>
+        <v>-1.586143395802751</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.24668426037662</v>
+        <v>2.230831071351293</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.941143080286601</v>
+        <v>-9.104120031887893</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3885628433568078</v>
+        <v>-0.4537536239973248</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.559721414093873</v>
+        <v>-1.586143395802751</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.252417964615256</v>
+        <v>2.23656477558993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.869776687676953</v>
+        <v>-9.032753639278246</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.369753548706814</v>
+        <v>-0.434944329347331</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.514777003193103</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.28550053778718</v>
+        <v>2.269647348761853</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.776317653691729</v>
+        <v>-8.939294605293021</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3422534164256317</v>
+        <v>-0.4074441970661487</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.514777003193103</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.275617056474272</v>
+        <v>2.259763867448946</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.765664472138297</v>
+        <v>-8.92864142373959</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3398267043036332</v>
+        <v>-0.4050174849441501</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.514777003193103</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.273782495974899</v>
+        <v>2.257929306949572</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.667757433461807</v>
+        <v>-8.830734385063099</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3009642038064975</v>
+        <v>-0.3661549844470144</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.420369271623669</v>
+        <v>-1.446791253332547</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.314273630917771</v>
+        <v>2.298420441892445</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.643803892485849</v>
+        <v>-8.806780844087141</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2907142812706209</v>
+        <v>-0.3559050619111379</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.396415730647711</v>
+        <v>-1.422837712356589</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.32931426164884</v>
+        <v>2.313461072623513</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.379743954163052</v>
+        <v>-8.542720905764345</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1983506221032543</v>
+        <v>-0.2635414027437712</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.132355792324915</v>
+        <v>-1.158777774033793</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.474489908480765</v>
+        <v>2.458636719455439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.672664330658214</v>
+        <v>-7.835641282259506</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.08169419363838015</v>
+        <v>0.01650341299786318</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.132355792324915</v>
+        <v>-1.158777774033793</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.471702874820465</v>
+        <v>2.455849685795138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.632480032292023</v>
+        <v>-7.795456983893316</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.09811153687269769</v>
+        <v>0.03292075623218071</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.092171493958724</v>
+        <v>-1.118593475667602</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.49615707772802</v>
+        <v>2.480303888702694</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.469080161352661</v>
+        <v>-7.632057112953953</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1628383064691996</v>
+        <v>0.09764752582868264</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9287716230193617</v>
+        <v>-0.9551936047282394</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.593563821512395</v>
+        <v>2.577710632487068</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.235598939123062</v>
+        <v>-7.398575890724355</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2641552241988916</v>
+        <v>0.1989644435583746</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6952904007897631</v>
+        <v>-0.7217123824986409</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.741576983688006</v>
+        <v>2.72572379466268</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.085932548115547</v>
+        <v>-7.24890949971684</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3211295702889383</v>
+        <v>0.2559387896484213</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6023869095472272</v>
+        <v>-0.628808891256105</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.794426868120569</v>
+        <v>2.778573679095242</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.953657074484661</v>
+        <v>-7.116634026085953</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2753005457484474</v>
+        <v>0.2101097651079304</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4701114359163405</v>
+        <v>-0.4965334176252183</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.775052938306255</v>
+        <v>2.759199749280929</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.802728266997576</v>
+        <v>-6.960895693526211</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3384871294309182</v>
+        <v>0.2752201588194643</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3191826284292562</v>
+        <v>-0.3407950850654767</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.868425283486143</v>
+        <v>2.85545780950441</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.717763600268256</v>
+        <v>-6.875931026796891</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.385379337346305</v>
+        <v>0.3221123667348507</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2342179616999366</v>
+        <v>-0.2558304183361572</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.932310424747393</v>
+        <v>2.919342950765661</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.823353590041361</v>
+        <v>-6.981521016569996</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2151674118378444</v>
+        <v>0.1519004412263905</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3398079514730409</v>
+        <v>-0.3614204081092615</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.740980501284312</v>
+        <v>2.72801302730258</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.755119005415933</v>
+        <v>-6.913286431944568</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2910055875651016</v>
+        <v>0.2277386169536477</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3213926286005049</v>
+        <v>-0.3430050852367255</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.80057403688492</v>
+        <v>2.787606562903187</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.607178964008334</v>
+        <v>-6.765346390536969</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2335607954897343</v>
+        <v>0.1702938248782804</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3010717126919474</v>
+        <v>-0.322684169328168</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.696145777791647</v>
+        <v>2.683178303809915</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.554209441754345</v>
+        <v>-6.712376868282981</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2460346181378519</v>
+        <v>0.1827676475263975</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2481021904379585</v>
+        <v>-0.2697146470741791</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.719213504890562</v>
+        <v>2.70624603090883</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.388421245794055</v>
+        <v>-6.54658867232269</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3053892844268749</v>
+        <v>0.2421223138154209</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2481021904379585</v>
+        <v>-0.2697146470741791</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.712252892795469</v>
+        <v>2.699285418813737</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.355058039315286</v>
+        <v>-6.513225465843921</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3331969213995256</v>
+        <v>0.2699299507880712</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2481021904379585</v>
+        <v>-0.2697146470741791</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.726715247176612</v>
+        <v>2.71374777319488</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.246798902192764</v>
+        <v>-6.404966328721399</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3710326967077293</v>
+        <v>0.3077657260962749</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2481021904379585</v>
+        <v>-0.2697146470741791</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.721247367635807</v>
+        <v>2.708279893654075</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792048</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.123507767375633</v>
+        <v>-6.281675193904269</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4178472446451584</v>
+        <v>0.3545802740337041</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.124811055620828</v>
+        <v>-0.1464235122570486</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.792720142536663</v>
+        <v>2.77975266855493</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.070810900244342</v>
+        <v>-6.228978326772977</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.446626969735</v>
+        <v>0.3833599991235461</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.07211418848953682</v>
+        <v>-0.0937266451257574</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.832039241052762</v>
+        <v>2.81907176707103</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.827045458260898</v>
+        <v>-5.985212884789533</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5399138548754285</v>
+        <v>0.4766468842639746</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.07211418848953682</v>
+        <v>-0.0937266451257574</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.827819949399813</v>
+        <v>2.814852475418081</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.737269785884425</v>
+        <v>-5.895437212413061</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5779484377460333</v>
+        <v>0.5146814671345794</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.0105147435752268</v>
+        <v>-0.03212720021144738</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.866903930268415</v>
+        <v>2.853936456286683</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.487419391935351</v>
+        <v>-5.645586818463986</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6706306703093654</v>
+        <v>0.6073636996979115</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.0105147435752268</v>
+        <v>-0.03212720021144738</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.859646005252117</v>
+        <v>2.846678531270385</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.311527299467919</v>
+        <v>-5.469694725996554</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7445866308169871</v>
+        <v>0.6813196602055327</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.0105147435752268</v>
+        <v>-0.03212720021144738</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.863245128772766</v>
+        <v>2.850277654791034</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.140080836445455</v>
+        <v>-5.298248262974091</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.826492722080526</v>
+        <v>0.7632257514690721</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1609317194472363</v>
+        <v>0.1393192628110158</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.979440512640798</v>
+        <v>2.966473038659065</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.060058549336334</v>
+        <v>-5.21822597586497</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8575221145404712</v>
+        <v>0.7942551439290173</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2409540065563573</v>
+        <v>0.2193415499201367</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.026474362522567</v>
+        <v>3.013506888540835</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.9964228071024</v>
+        <v>-5.154590233631035</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8876712124883626</v>
+        <v>0.8244042418769082</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3045897487902918</v>
+        <v>0.2829772921540712</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.069350608917245</v>
+        <v>3.056383134935513</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.902725488886005</v>
+        <v>-5.06089291541464</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9063443985587161</v>
+        <v>0.8430774279472621</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3045897487902918</v>
+        <v>0.2829772921540712</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.050544867701041</v>
+        <v>3.037577393719308</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.913228111951294</v>
+        <v>-5.071395538479929</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9038864259574779</v>
+        <v>0.8406194553460238</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.294087125725003</v>
+        <v>0.2724746690887824</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.045986370486745</v>
+        <v>3.033018896505012</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.840985543780099</v>
+        <v>-4.999152970308734</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.936712767060776</v>
+        <v>0.8734457964493219</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.294087125725003</v>
+        <v>0.2724746690887824</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.049915684321565</v>
+        <v>3.036948210339832</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.823271856902234</v>
+        <v>-4.981439283430869</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9444768257292622</v>
+        <v>0.881209855117808</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2972684546219198</v>
+        <v>0.2756559979856992</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.052503065577055</v>
+        <v>3.039535591595323</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502337</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.699797585589216</v>
+        <v>-4.857965012117851</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.990864605474463</v>
+        <v>0.9275976348630088</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2972684546219198</v>
+        <v>0.2756559979856992</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.049501136797049</v>
+        <v>3.036533662815316</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.479776787552205</v>
+        <v>-4.63794421408084</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.080451961699881</v>
+        <v>1.017184991088427</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4384882996899</v>
+        <v>0.4168758430536794</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.135812080848451</v>
+        <v>3.122844606866718</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.346909098488927</v>
+        <v>-4.505076525017563</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.149493220127016</v>
+        <v>1.086226249515561</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4384882996899</v>
+        <v>0.4168758430536794</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.151706263650274</v>
+        <v>3.138738789668542</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.226736015124429</v>
+        <v>-4.384903441653064</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.198708297913117</v>
+        <v>1.135441327301663</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5586613830543989</v>
+        <v>0.5370489264181784</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.224955958109275</v>
+        <v>3.211988484127543</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.091482653794452</v>
+        <v>-4.249650080323087</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.262897745006548</v>
+        <v>1.199630774395094</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6939147443843761</v>
+        <v>0.6723022877481555</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.316196077468701</v>
+        <v>3.303228603486969</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.151357481152144</v>
+        <v>-4.309524907680779</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.224985305464897</v>
+        <v>1.161718334853443</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6340399170266839</v>
+        <v>0.6124274603904634</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.266308672455512</v>
+        <v>3.25334119847378</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.031537250241307</v>
+        <v>-4.189704676769942</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.28820256706344</v>
+        <v>1.224935596451986</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6340399170266839</v>
+        <v>0.6124274603904634</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.281597841689721</v>
+        <v>3.268630367707988</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.034006956703113</v>
+        <v>-4.192174383231748</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.194858883801159</v>
+        <v>1.131591913189705</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6315702105648777</v>
+        <v>0.6099577539286571</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.187760217135078</v>
+        <v>3.174792743153346</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.102377143027123</v>
+        <v>-4.260544569555758</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.086772670756856</v>
+        <v>1.023505700145402</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6408459096010927</v>
+        <v>0.6192334529648721</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.112587498042109</v>
+        <v>3.099620024060377</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.214249422653274</v>
+        <v>-4.372416849181909</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.032460467538287</v>
+        <v>0.9691934969268332</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6408459096010927</v>
+        <v>0.6192334529648721</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.103024206674</v>
+        <v>3.090056732692268</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.269769498545863</v>
+        <v>-4.427936925074499</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.147283273873454</v>
+        <v>1.084016303262</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6408459096010927</v>
+        <v>0.6192334529648721</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.240055043366203</v>
+        <v>3.22708756938447</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.094295238753395</v>
+        <v>-4.25246266528203</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.222040209782229</v>
+        <v>1.158773239170775</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6408459096010927</v>
+        <v>0.6192334529648721</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.24462227535799</v>
+        <v>3.231654801376258</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.08637086416848</v>
+        <v>-4.244538290697116</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.200951988377402</v>
+        <v>1.137685017765948</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6408459096010927</v>
+        <v>0.6192334529648721</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.220364304119197</v>
+        <v>3.207396830137465</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.080092661598631</v>
+        <v>-4.238260088127267</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.132001582806791</v>
+        <v>1.068734612195337</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6471241121709417</v>
+        <v>0.6255116555347211</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.152669539062556</v>
+        <v>3.139702065080824</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.020240042394908</v>
+        <v>-4.178407468923544</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.166115016920413</v>
+        <v>1.102848046308959</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6471241121709417</v>
+        <v>0.6255116555347211</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.162841925494689</v>
+        <v>3.149874451512956</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.933996579368531</v>
+        <v>-4.092164005897166</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.195558672704824</v>
+        <v>1.13229170209337</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6471241121709417</v>
+        <v>0.6255116555347211</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.157788196068549</v>
+        <v>3.144820722086817</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.97930339876751</v>
+        <v>-4.137470825296146</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.169211720389758</v>
+        <v>1.105944749778304</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6063139491617109</v>
+        <v>0.5847014925254903</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.125077873707536</v>
+        <v>3.112110399725804</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.008336503469812</v>
+        <v>-4.166503929998447</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.158150351541939</v>
+        <v>1.094883380930485</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6063139491617109</v>
+        <v>0.5847014925254903</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.125629746740638</v>
+        <v>3.112662272758906</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.915526022018952</v>
+        <v>-4.073693448547587</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124547236013648</v>
+        <v>1.061280265402194</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6991244306125702</v>
+        <v>0.6775119739763497</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.110588727502519</v>
+        <v>3.097621253520787</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.95991549134838</v>
+        <v>-4.118082917877015</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108664924206478</v>
+        <v>1.045397953595024</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6547349612831426</v>
+        <v>0.633122504646922</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.085828521829463</v>
+        <v>3.072861047847731</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.076457096453723</v>
+        <v>-4.234624522982357</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.057123990676064</v>
+        <v>0.9938570200646104</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5381933561777998</v>
+        <v>0.5165808995415793</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.01097926727798</v>
+        <v>2.998011793296248</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.116381191036295</v>
+        <v>-4.274548617564929</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.046645648673703</v>
+        <v>0.9833786780622487</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5381933561777998</v>
+        <v>0.5165808995415793</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.016470563108648</v>
+        <v>3.003503089126915</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.144161588937648</v>
+        <v>-4.302329015466282</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.0470306912817</v>
+        <v>0.9837637206702468</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5104129582764467</v>
+        <v>0.4888005016402261</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.011299526136375</v>
+        <v>2.998332052154643</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.262542261667786</v>
+        <v>-4.42070968819642</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8380341421902984</v>
+        <v>0.7747671715788447</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4431951061254705</v>
+        <v>0.4215826494892499</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.809324534846443</v>
+        <v>2.79635706086471</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.371156340111117</v>
+        <v>-4.529323766639751</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9147381715321716</v>
+        <v>0.8514712009207179</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4431951061254705</v>
+        <v>0.4215826494892499</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.929474195565648</v>
+        <v>2.916506721583916</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.335747301862974</v>
+        <v>-4.493914728391609</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9434148129337516</v>
+        <v>0.8801478423222979</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4431951061254705</v>
+        <v>0.4215826494892499</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.943987221667971</v>
+        <v>2.931019747686239</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.297363639304823</v>
+        <v>-4.455531065833457</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9561877192993808</v>
+        <v>0.8929207486879271</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4815787686836217</v>
+        <v>0.4599663120474011</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.964436860545231</v>
+        <v>2.951469386563498</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.120247309269657</v>
+        <v>-4.278414735798291</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.023763280158749</v>
+        <v>0.9604963095472954</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4815787686836217</v>
+        <v>0.4599663120474011</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.961165889390533</v>
+        <v>2.9481984154088</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.165339554103203</v>
+        <v>-4.323506980631837</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.006409773987244</v>
+        <v>0.9431428033757903</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4196827255142319</v>
+        <v>0.3980702688780113</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.924711655250812</v>
+        <v>2.911744181269079</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.985964132864435</v>
+        <v>-4.144131559393069</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.071946917789165</v>
+        <v>1.008679947177712</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5764594836849506</v>
+        <v>0.55484702704873</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.012564685459657</v>
+        <v>2.999597211477925</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.030978346385041</v>
+        <v>-4.189145772913676</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.034748687712513</v>
+        <v>0.9714817171010588</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.546110588370346</v>
+        <v>0.5244981317341254</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.975162803602484</v>
+        <v>2.962195329620752</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.297982856657476</v>
+        <v>-4.456150283186111</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9336384459424847</v>
+        <v>0.8703714753310305</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3517475503273974</v>
+        <v>0.3301350936911768</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.864236543115661</v>
+        <v>2.851269069133929</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760815</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.399180638094649</v>
+        <v>-4.557348064623284</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.892363255264117</v>
+        <v>0.8290962846526628</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2833387367820782</v>
+        <v>0.2617262801458576</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.822395176884971</v>
+        <v>2.809427702903239</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.70557166181546</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.392669671480336</v>
+        <v>-4.550837098008971</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8925676034641588</v>
+        <v>0.8293006328527046</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2833387367820782</v>
+        <v>0.2617262801458576</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.819995138439288</v>
+        <v>2.807027664457555</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378106</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.373631543773039</v>
+        <v>-4.531798970301674</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8967075737553225</v>
+        <v>0.8334406031438686</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2251551254508837</v>
+        <v>0.2035426688146631</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.781609690848816</v>
+        <v>2.768642216867083</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131253</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.426147346047859</v>
+        <v>-4.584314772576494</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9949956544795848</v>
+        <v>0.9317286838681307</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2251551254508837</v>
+        <v>0.2035426688146631</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.900904092483006</v>
+        <v>2.887936618501274</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.440014107381777</v>
+        <v>-4.598181533910412</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9902822789321513</v>
+        <v>0.9270153083206971</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1872972087170607</v>
+        <v>0.1656847520808402</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.879022671428846</v>
+        <v>2.866055197447114</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.399531115459432</v>
+        <v>-4.557698541988067</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.012484006098015</v>
+        <v>0.949217035486561</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1872972087170607</v>
+        <v>0.1656847520808402</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.885031201825772</v>
+        <v>2.87206372784404</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.251788145224429</v>
+        <v>-4.51747620097977</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9695314154692156</v>
+        <v>0.8632561931670795</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3551045659519439</v>
+        <v>0.2347856356456299</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.883665837443901</v>
+        <v>2.811474479260113</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.335609366499128</v>
+        <v>-4.601297422254468</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9387965484908172</v>
+        <v>0.832521326188681</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3551045659519439</v>
+        <v>0.2347856356456299</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.886459458975382</v>
+        <v>2.814268100791594</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.329456660446343</v>
+        <v>-4.595144716201684</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9419199793035893</v>
+        <v>0.8356447570014531</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3612572720047282</v>
+        <v>0.2409383416984142</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.890813430998711</v>
+        <v>2.818622072814923</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.346265958596845</v>
+        <v>-4.611954014352186</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9342767367834988</v>
+        <v>0.8280015144813626</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3444479738542265</v>
+        <v>0.2241290435479125</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.879808328848521</v>
+        <v>2.807616970664732</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.283967959820723</v>
+        <v>-4.549656015576064</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.025531490090769</v>
+        <v>0.9192562677886325</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3897422381286686</v>
+        <v>0.2694233078223546</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.973320441210006</v>
+        <v>2.901129083026218</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.082177762155565</v>
+        <v>-4.347865817910906</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9085395708709589</v>
+        <v>0.8022643485688226</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.587760430297823</v>
+        <v>0.467441499991509</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.894423358225626</v>
+        <v>2.822232000041838</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.13306447484176</v>
+        <v>-4.3987525305971</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9584751181186562</v>
+        <v>0.85219989581652</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5368737176116285</v>
+        <v>0.4165547873053144</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.934181562936085</v>
+        <v>2.861990204752296</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.046453732191953</v>
+        <v>-4.312141787947294</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.007747151294623</v>
+        <v>0.9014719289924864</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6154994488167868</v>
+        <v>0.4951805185104727</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.995984737775223</v>
+        <v>2.923793379591435</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.106663030197238</v>
+        <v>-4.372351085952578</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9821994129171803</v>
+        <v>0.8759241906150441</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5552901508115022</v>
+        <v>0.4349712205051882</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.958395139796724</v>
+        <v>2.886203781612936</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.057476381512886</v>
+        <v>-4.323164437268227</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.000365690430849</v>
+        <v>0.8940904681287132</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5552901508115022</v>
+        <v>0.4349712205051882</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.956886757836653</v>
+        <v>2.884695399652864</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.83351346031625</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.013103249874318</v>
+        <v>-4.278791305629658</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.017977810521713</v>
+        <v>0.9117025882195768</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5996632824500708</v>
+        <v>0.4793443521437568</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.98337350425523</v>
+        <v>2.911182146071442</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105969</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.035583600733203</v>
+        <v>-4.301271656488543</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.00337946431675</v>
+        <v>0.8971042420146134</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5996632824500708</v>
+        <v>0.4793443521437568</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.977767298393821</v>
+        <v>2.905575940210032</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190327</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.987927870172147</v>
+        <v>-4.253615925927487</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.028823513568977</v>
+        <v>0.9225482912668403</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6473190130111265</v>
+        <v>0.5270000827048125</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.012742493758259</v>
+        <v>2.94055113557447</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569619</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.887409711673392</v>
+        <v>-4.153097767428733</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.073923150343203</v>
+        <v>0.967647928041067</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.747837171509881</v>
+        <v>0.627518241203567</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.077945762232236</v>
+        <v>3.005754404048448</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.828808877557296</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.87150438224104</v>
+        <v>-4.13719243799638</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.067039954592017</v>
+        <v>0.9607647322898802</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6687245108006421</v>
+        <v>0.5484055804943282</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.017232838282565</v>
+        <v>2.945041480098777</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932771</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.826665980632642</v>
+        <v>-4.092354036387982</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.089073017846004</v>
+        <v>0.9827977955438683</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6732679437455116</v>
+        <v>0.5529490134391977</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.024056600660115</v>
+        <v>2.951865242476327</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917053</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.84616443687465</v>
+        <v>-4.11185249262999</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.085434574980279</v>
+        <v>0.979159352678143</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6251833024656073</v>
+        <v>0.5048643721592934</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.999366755523251</v>
+        <v>2.927175397339463</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.801961599788749</v>
+        <v>-4.06764965554409</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.108995312342477</v>
+        <v>1.00272009004034</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6693861395515077</v>
+        <v>0.5490672092451938</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.031768060302628</v>
+        <v>2.95957670211884</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.809521265625796</v>
+        <v>-4.075209321381136</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.104381446476905</v>
+        <v>0.9981062241747694</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.724189543561327</v>
+        <v>0.6038706132550131</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.063060103177767</v>
+        <v>2.990868744993979</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.651229848086524</v>
+        <v>-3.916917903841864</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.218945778675654</v>
+        <v>1.112670556373518</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.724189543561327</v>
+        <v>0.6038706132550131</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.114307868360807</v>
+        <v>3.042116510177019</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.443587844452048</v>
+        <v>-3.709275900207388</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.300443284723697</v>
+        <v>1.194168062421561</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9318315471958032</v>
+        <v>0.8115126168894893</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.237333775135746</v>
+        <v>3.165142416951958</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.39255575172952</v>
+        <v>-3.65824380748486</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.315804350050979</v>
+        <v>1.209529127748843</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9828636399183311</v>
+        <v>0.8625447096120172</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.262901259007533</v>
+        <v>3.190709900823745</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.327331570602314</v>
+        <v>-3.593019626357654</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.359081426594566</v>
+        <v>1.25280620429243</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.048087821045537</v>
+        <v>0.9277688907392229</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.319223171776561</v>
+        <v>3.247031813592772</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.28990455053118</v>
+        <v>-3.55559260628652</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.3700132069223</v>
+        <v>1.263737984620164</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.053339359074718</v>
+        <v>0.9330204287684045</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.31833506689335</v>
+        <v>3.246143708709562</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.310016206565888</v>
+        <v>-3.575704262321228</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.363225336839657</v>
+        <v>1.256950114537521</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.064366704072137</v>
+        <v>0.9440477737658237</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.326208266223042</v>
+        <v>3.254016908039254</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.281602943466005</v>
+        <v>-3.547290999221345</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.535148413100821</v>
+        <v>1.428873190798685</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.005391141325709</v>
+        <v>0.8850722110193949</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.451380699596395</v>
+        <v>3.379189341412607</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.206820682440992</v>
+        <v>-3.472508738196332</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.685174226728643</v>
+        <v>1.578899004426507</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.080173402350721</v>
+        <v>0.9598544720444075</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.61636296542922</v>
+        <v>3.544171607245432</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998756</v>
+        <v>3.814230727998758</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.180736598177184</v>
+        <v>-3.446424653932524</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.687315836448025</v>
+        <v>1.581040614145889</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.080173402350721</v>
+        <v>0.9598544720444075</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.608070941443079</v>
+        <v>3.535879583259291</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896932</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.092858685068064</v>
+        <v>-3.358546740823404</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.720660197275453</v>
+        <v>1.614384974973317</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.196099044774072</v>
+        <v>1.075780114467759</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.675819522480869</v>
+        <v>3.603628164297081</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959858</v>
+        <v>3.79626414395986</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.08396622367478</v>
+        <v>-3.34965427943012</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.741771587559558</v>
+        <v>1.635496365257422</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.196099044774072</v>
+        <v>1.075780114467759</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.693373928207661</v>
+        <v>3.621182570023873</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945367</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.252442340644658</v>
+        <v>-3.518130396399998</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.666236188176191</v>
+        <v>1.559960965874055</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.168151209057491</v>
+        <v>1.047832278751178</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.668460274182296</v>
+        <v>3.596268915998508</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.806186148015218</v>
+        <v>-3.071874203770558</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.826008362415829</v>
+        <v>1.719733140113692</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.073432539387859</v>
+        <v>0.9531136090815453</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.592898769568378</v>
+        <v>3.52070741138459</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.783465044332066</v>
+        <v>-3.049153100087405</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.825760826385994</v>
+        <v>1.719485604083858</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.073432539387859</v>
+        <v>0.9531136090815453</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.583562792065283</v>
+        <v>3.511371433881495</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.912666857626108</v>
+        <v>-3.178354913381448</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.932986226919546</v>
+        <v>1.82671100461741</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9442307260938165</v>
+        <v>0.8239117957875031</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.664947829940027</v>
+        <v>3.592756471756239</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.938541256100134</v>
+        <v>-3.204229311855474</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.959714290023582</v>
+        <v>1.853439067721446</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9891423348055577</v>
+        <v>0.8688234044992442</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.728972617660718</v>
+        <v>3.65678125947693</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799965</v>
+        <v>3.769443619799967</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.93148656588496</v>
+        <v>-3.1971746216403</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.959211522099197</v>
+        <v>1.852936299797061</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9961970250207315</v>
+        <v>0.875878094714418</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.729880787779368</v>
+        <v>3.657689429595579</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.904535341558472</v>
+        <v>-3.170223397313812</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.979998165474534</v>
+        <v>1.873722943172398</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.011077371048451</v>
+        <v>0.8907584407421372</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.74881514904074</v>
+        <v>3.676623790856953</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784109</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.926079569389259</v>
+        <v>-3.191767625144599</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.155483606487179</v>
+        <v>2.049208384185043</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.011077371048451</v>
+        <v>0.8907584407421372</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.9329182811857</v>
+        <v>3.860726923001912</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714427</v>
+        <v>3.743925505714429</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.948487687194131</v>
+        <v>-3.214175742949471</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.138637054268223</v>
+        <v>2.032361831966087</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.011077371048451</v>
+        <v>0.8907584407421372</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.925034976088694</v>
+        <v>3.852843617904905</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.976711922771732</v>
+        <v>-3.242399978527072</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.12940135958682</v>
+        <v>2.023126137284684</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.029054123499759</v>
+        <v>0.9087351931934458</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.937875027109116</v>
+        <v>3.865683668925328</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.986152848660262</v>
+        <v>-3.251840904415602</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.181878706953255</v>
+        <v>2.075603484651119</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.151481241043151</v>
+        <v>1.031162310736837</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.067585015356998</v>
+        <v>3.99539365717321</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.075029479828736</v>
+        <v>-3.340717535584075</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.149219149031167</v>
+        <v>2.042943926729031</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.062604609874677</v>
+        <v>0.9422856795683634</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.017150131201214</v>
+        <v>3.944958773017427</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.151359457429642</v>
+        <v>-3.417047513184981</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.116798970884579</v>
+        <v>2.010523748582443</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.062604609874677</v>
+        <v>0.9422856795683634</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.015261944094989</v>
+        <v>3.943070585911202</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.245023402107183</v>
+        <v>-3.510711457862523</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.074153622616425</v>
+        <v>1.967878400314289</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9689406651971354</v>
+        <v>0.8486217348908219</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.953883806891327</v>
+        <v>3.881692448707539</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343067</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.406591827634438</v>
+        <v>-3.672279883389778</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.007960262615676</v>
+        <v>1.901685040313539</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.842157741399256</v>
+        <v>0.7218388110929426</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.876248062822752</v>
+        <v>3.804056704638964</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389349</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.514892489504557</v>
+        <v>-3.780580545259897</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.977713404733546</v>
+        <v>1.87143818243141</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.842157741399256</v>
+        <v>0.7218388110929426</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.88932146968867</v>
+        <v>3.817130111504882</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378392</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.608039960807924</v>
+        <v>-3.873728016563264</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.93245961299514</v>
+        <v>1.826184390693004</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7193285301167233</v>
+        <v>0.5990095998104098</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.807629139702091</v>
+        <v>3.735437781518303</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006978</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.635940747917397</v>
+        <v>-3.901628803672737</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.919823339278352</v>
+        <v>1.813548116976216</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6847316059737885</v>
+        <v>0.564412675667475</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.785395026343332</v>
+        <v>3.713203668159544</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.758466850620291</v>
+        <v>-4.024154906375631</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.867577342174394</v>
+        <v>1.761302119872258</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5622055032708946</v>
+        <v>0.4418865729645811</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.708643808698795</v>
+        <v>3.636452450515006</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.61934808158594</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.98898134680588</v>
+        <v>-4.25466940256122</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.842077503290662</v>
+        <v>1.735802280988526</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3316910070853059</v>
+        <v>0.2113720767789924</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.637041070577945</v>
+        <v>3.564849712394157</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.337726432030323</v>
+        <v>-4.603414487785663</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.842891188202731</v>
+        <v>1.736615965900596</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2229430531664081</v>
+        <v>0.1026241228600946</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.712104017228453</v>
+        <v>3.639912659044665</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.491712849806464</v>
+        <v>-4.757400905561804</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.850276890237915</v>
+        <v>1.744001667935779</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2229430531664081</v>
+        <v>0.1026241228600946</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.781084286374093</v>
+        <v>3.708892928190305</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.441190945978798</v>
+        <v>-4.706879001734138</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.856536853889102</v>
+        <v>1.750261631586966</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2229430531664081</v>
+        <v>0.1026241228600946</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.767135488494214</v>
+        <v>3.694944130310426</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.693666099986523</v>
+        <v>-4.959354155741862</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.767417281341426</v>
+        <v>1.66114205903929</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2229430531664081</v>
+        <v>0.1026241228600946</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.779005977549628</v>
+        <v>3.70681461936584</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.986561856465935</v>
+        <v>-5.252249912221274</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.651469513268605</v>
+        <v>1.54519429096647</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2229430531664081</v>
+        <v>0.1026241228600946</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.780216512068571</v>
+        <v>3.708025153884783</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.173225984600743</v>
+        <v>-5.438914040356083</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.580925604242004</v>
+        <v>1.474650381939868</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1962040823418482</v>
+        <v>0.0758851520355347</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.768294871801157</v>
+        <v>3.696103513617369</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.319246671514705</v>
+        <v>-5.584934727270045</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.517595182212608</v>
+        <v>1.411319959910472</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1871209905479912</v>
+        <v>0.06680206024167773</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.757922869461032</v>
+        <v>3.685731511277244</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.41096068062429</v>
+        <v>-5.676648736379629</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.643113635267818</v>
+        <v>1.536838412965682</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1871209905479912</v>
+        <v>0.06680206024167773</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.920126926160076</v>
+        <v>3.847935567976288</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071553</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.44261233968426</v>
+        <v>-5.708300395439599</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.625299609607644</v>
+        <v>1.519024387305509</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.181952533303551</v>
+        <v>0.06163360299723752</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.911872489777227</v>
+        <v>3.839681131593438</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868145</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.524547157953143</v>
+        <v>-5.790235213708482</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.602755099868582</v>
+        <v>1.496479877566447</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1720177877164708</v>
+        <v>0.05169885741015734</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.916141059993469</v>
+        <v>3.843949701809681</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.626523280201551</v>
+        <v>-5.89221133595689</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.570890289425122</v>
+        <v>1.464615067122986</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07004166546806323</v>
+        <v>-0.05027726483825024</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.863881025100327</v>
+        <v>3.791689666916539</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.516516996724329</v>
+        <v>-5.782205052479668</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.607045690060186</v>
+        <v>1.50077046775805</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09324623738533844</v>
+        <v>-0.02707269292097503</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.869956655494868</v>
+        <v>3.79776529731108</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.373457420983403</v>
+        <v>-5.639145476738742</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.66851953107853</v>
+        <v>1.562244308776395</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1012596639753177</v>
+        <v>-0.01905926633099575</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.87901472217083</v>
+        <v>3.806823363987041</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051789</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.072010695511565</v>
+        <v>-5.337698751266904</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.796359104149801</v>
+        <v>1.690083881847666</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.402706389447155</v>
+        <v>0.2823874591408415</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.067143640336468</v>
+        <v>3.99495228215268</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.096600939746749</v>
+        <v>-5.362288995502088</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.787494184208438</v>
+        <v>1.681218961906303</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.402706389447155</v>
+        <v>0.2823874591408415</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.068114818089179</v>
+        <v>3.995923459905391</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.045562563740229</v>
+        <v>-5.311250619495568</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.808752438990802</v>
+        <v>1.702477216688667</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.402706389447155</v>
+        <v>0.2823874591408415</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.068957722468935</v>
+        <v>3.996766364285146</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.004423268873598</v>
+        <v>-5.270111324628937</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.8442462558116</v>
+        <v>1.737971033509464</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4438456843137858</v>
+        <v>0.3235267540074723</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.112679398263058</v>
+        <v>4.04048804007927</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.907788356854958</v>
+        <v>-5.173476412610297</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.69908421674299</v>
+        <v>1.592808994440855</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5404805963324257</v>
+        <v>0.4201616660261123</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.986844341598177</v>
+        <v>3.914652983414388</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.80468896107764</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.038369091385801</v>
+        <v>-5.30405714714114</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.650353967004618</v>
+        <v>1.544078744702482</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4098998618015832</v>
+        <v>0.2895809314952698</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.911997944953635</v>
+        <v>3.839806586769847</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.873872757194839</v>
+        <v>-5.139560812950178</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.700579319757085</v>
+        <v>1.594304097454949</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5743961959925451</v>
+        <v>0.4540772656862316</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.995122564544295</v>
+        <v>3.922931206360507</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.901242689879271</v>
+        <v>-5.16693074563461</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.688819057119742</v>
+        <v>1.582543834817606</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5743961959925451</v>
+        <v>0.4540772656862316</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.994310274980725</v>
+        <v>3.922118916796936</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.91162788476916</v>
+        <v>-5.177315940524499</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.694533758288858</v>
+        <v>1.588258535986723</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5640110011026558</v>
+        <v>0.4436920707963423</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.997947937171864</v>
+        <v>3.925756578988075</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.930216043491385</v>
+        <v>-5.195904099246724</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.757935500576393</v>
+        <v>1.651660278274258</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5454228423804304</v>
+        <v>0.425103912074117</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.057632047714954</v>
+        <v>3.985440689531165</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.930514590187421</v>
+        <v>-5.19620264594276</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.754685092716278</v>
+        <v>1.648409870414142</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5451242956843945</v>
+        <v>0.4248053653780811</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.054321930515631</v>
+        <v>3.982130572331842</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.829691456496993</v>
+        <v>-5.095379512252332</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.79954524113184</v>
+        <v>1.693270018829705</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5575885111687483</v>
+        <v>0.4372695808624349</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.066331354745634</v>
+        <v>3.994139996561846</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.638910095744587</v>
+        <v>-4.904598151499926</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.875987038911346</v>
+        <v>1.769711816609211</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7483698719211557</v>
+        <v>0.6280509416148423</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.180929424675622</v>
+        <v>4.108738066491834</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.531946737895165</v>
+        <v>-4.797634793650504</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.898609227788711</v>
+        <v>1.792334005486576</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8068344798809571</v>
+        <v>0.6865155495746438</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.195845035189099</v>
+        <v>4.123653677005311</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.476616149993403</v>
+        <v>-4.742304205748741</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.955708399561475</v>
+        <v>1.849433177259339</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8621650677827193</v>
+        <v>0.7418461374764059</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.264010324542215</v>
+        <v>4.191818966358427</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.46456202308044</v>
+        <v>-4.730250078835779</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.954216618228098</v>
+        <v>1.847941395925962</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8742191946956821</v>
+        <v>0.7539002643893687</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.264929368591431</v>
+        <v>4.192738010407642</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.505717142648661</v>
+        <v>-4.771405198404</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.939635200584945</v>
+        <v>1.83335997828281</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8330640751274612</v>
+        <v>0.7127451448211478</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.242116927034633</v>
+        <v>4.169925568850846</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.437668579957131</v>
+        <v>-4.70335663571247</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.979705651539439</v>
+        <v>1.873430429237304</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.901112637818991</v>
+        <v>0.7807937075126776</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.295797090527434</v>
+        <v>4.223605732343646</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.669268973126631</v>
+        <v>-4.93495702888197</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.907268164445234</v>
+        <v>1.800992942143098</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.901112637818991</v>
+        <v>0.7807937075126776</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.315999760701028</v>
+        <v>4.24380840251724</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781706</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.687341481418243</v>
+        <v>-4.953029537173582</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.900039161128589</v>
+        <v>1.793763938826453</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.901112637818991</v>
+        <v>0.7807937075126776</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.315999760701028</v>
+        <v>4.24380840251724</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082835</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.862448313994689</v>
+        <v>-5.128136369750028</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.790248341691477</v>
+        <v>1.683973119389342</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.901112637818991</v>
+        <v>0.7807937075126776</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.276251674294495</v>
+        <v>4.204060316110707</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943587</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.831162293454233</v>
+        <v>-5.096850349209572</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.8097853689046</v>
+        <v>1.703510146602464</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9323986583594464</v>
+        <v>0.812079728053133</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.302045905615708</v>
+        <v>4.22985454743192</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677823</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.611481141859566</v>
+        <v>-4.943824957096288</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.996828829115371</v>
+        <v>1.863891303020682</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.152079809954113</v>
+        <v>0.9651051201664171</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.533025596145412</v>
+        <v>4.420840782272795</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073882</v>
+        <v>3.741298518073884</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.639788455732837</v>
+        <v>-4.927454927611688</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.172972128474354</v>
+        <v>2.057905539722814</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.152079809954113</v>
+        <v>0.9651051201664171</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.720491821053705</v>
+        <v>4.608307007181087</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903169</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.806381680846359</v>
+        <v>-5.09404815272521</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.075737789783028</v>
+        <v>1.960671201031488</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9854865848405907</v>
+        <v>0.7985118950528947</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.589938837339673</v>
+        <v>4.477754023467056</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568381</v>
+        <v>3.708202704568383</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.783345887484793</v>
+        <v>-5.071012359363644</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.088628509789372</v>
+        <v>1.973561921037831</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9854865848405907</v>
+        <v>0.7985118950528947</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.593615240001391</v>
+        <v>4.481430426128774</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682203</v>
+        <v>3.740601586682205</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.754099907029096</v>
+        <v>-5.041766378907948</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.097944957095146</v>
+        <v>1.982878368343605</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9854865848405907</v>
+        <v>0.7985118950528947</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.591233295124886</v>
+        <v>4.479048481252269</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539106</v>
+        <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.861025454906947</v>
+        <v>-5.148691926785799</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.052467977101641</v>
+        <v>1.9374013883501</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8785610369627394</v>
+        <v>0.6915863471750433</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.524371205555811</v>
+        <v>4.412186391683193</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983736</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.006044013414196</v>
+        <v>-5.293710485293047</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.995889355841975</v>
+        <v>1.880822767090435</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7335424784554908</v>
+        <v>0.5465677886677948</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.438788872594696</v>
+        <v>4.326604058722078</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969748</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.124385779198914</v>
+        <v>-5.412052251077765</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.048483888785841</v>
+        <v>1.933417300034301</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7442285170183809</v>
+        <v>0.5572538272306848</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.545131734990183</v>
+        <v>4.432946921117566</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073538</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.175796201519621</v>
+        <v>-5.463462673398473</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.025705416983497</v>
+        <v>1.910638828231956</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7442285170183809</v>
+        <v>0.5572538272306848</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.542917432116122</v>
+        <v>4.430732618243504</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720065</v>
+        <v>3.704778134720067</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.255215652727373</v>
+        <v>-5.542882124606225</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.993840764574686</v>
+        <v>1.878774175823145</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7442285170183809</v>
+        <v>0.5572538272306848</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.542820560190411</v>
+        <v>4.430635746317794</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581133</v>
+        <v>3.736825137581135</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.350678650644591</v>
+        <v>-5.638345122523442</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.955649458965842</v>
+        <v>1.840582870214301</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7442285170183809</v>
+        <v>0.5572538272306848</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.542814453748455</v>
+        <v>4.430629639875837</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500735</v>
+        <v>3.715393145500737</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.390698648688375</v>
+        <v>-5.678365120567226</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.937737856310939</v>
+        <v>1.822671267559399</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.704208518974597</v>
+        <v>0.517233829186901</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.516898851484795</v>
+        <v>4.404714037612178</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.73610959863627</v>
+        <v>3.736109598636272</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.446067810820568</v>
+        <v>-5.73373428269942</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.921324009205788</v>
+        <v>1.806257420454248</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.704208518974597</v>
+        <v>0.517233829186901</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.522632669232522</v>
+        <v>4.410447855359904</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396013</v>
+        <v>3.736843055396015</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.491505590651395</v>
+        <v>-5.779172062530247</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.90268726061639</v>
+        <v>1.78762067186485</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6613635282964374</v>
+        <v>0.4743888385087413</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.496464038168559</v>
+        <v>4.384279224295941</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396422</v>
+        <v>3.790292685396424</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.403298756503817</v>
+        <v>-5.690965228382669</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.957844387125741</v>
+        <v>1.8427777983742</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6613635282964374</v>
+        <v>0.4743888385087413</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.516338431018878</v>
+        <v>4.40415361714626</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299176</v>
+        <v>3.794507029299178</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.297263761298508</v>
+        <v>-5.584930233177359</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.983959085732593</v>
+        <v>1.868892496981052</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6613635282964374</v>
+        <v>0.4743888385087413</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.500039131543605</v>
+        <v>4.387854317670988</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590407</v>
+        <v>3.794725278590409</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.114052098165413</v>
+        <v>-5.401718570044264</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.059674700449876</v>
+        <v>1.944608111698336</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6613635282964374</v>
+        <v>0.4743888385087413</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.502470081007651</v>
+        <v>4.390285267135034</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146286</v>
+        <v>3.776866743146288</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.042330651151562</v>
+        <v>-5.329997123030413</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.054154465103306</v>
+        <v>1.939087876351765</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.733084975310288</v>
+        <v>0.5461102855225919</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.511294135063851</v>
+        <v>4.399109321191233</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.72380989067685</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.019957625543856</v>
+        <v>-5.307624097422707</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.01001942126756</v>
+        <v>1.894952832516019</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7443407264231896</v>
+        <v>0.5573660366354934</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.464963331652763</v>
+        <v>4.352778517780146</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739465</v>
+        <v>3.715627631739467</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.0529739214546</v>
+        <v>-5.340640393333452</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.182011107788618</v>
+        <v>2.066944519037077</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6749033497564381</v>
+        <v>0.4879286599687419</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.608499110538068</v>
+        <v>4.49631429666545</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166414</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.041446285804992</v>
+        <v>-5.329112757683843</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.17854338787671</v>
+        <v>2.06347679912517</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7339040079578005</v>
+        <v>0.5469293181701043</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.635820731287135</v>
+        <v>4.523635917414516</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519034</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.13878778714736</v>
+        <v>-5.426454259026212</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.143274899861551</v>
+        <v>2.02820831111001</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6894838257923122</v>
+        <v>0.5025091360046159</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.61283673450963</v>
+        <v>4.500651920637012</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710421</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.224643816487327</v>
+        <v>-5.512310288366178</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.110183570318403</v>
+        <v>1.995116981566862</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6471077565661771</v>
+        <v>0.4601330667784809</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.588662175166787</v>
+        <v>4.47647736129417</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893116</v>
+        <v>3.691855684893118</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.233480613903446</v>
+        <v>-5.521147085782298</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.089068053172457</v>
+        <v>1.974001464420916</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6396655839248264</v>
+        <v>0.4526908941371301</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.566616073402479</v>
+        <v>4.454431259529861</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950189</v>
+        <v>3.715564596950191</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.324863176468905</v>
+        <v>-5.492112731976445</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.062679539191323</v>
+        <v>1.995779716988307</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5482830213593681</v>
+        <v>0.4817252479429827</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.521951046908253</v>
+        <v>4.482016382858422</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171926</v>
+        <v>3.673998560171928</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.313156458481899</v>
+        <v>-5.480406013989439</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.169490484210393</v>
+        <v>2.102590662007377</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5599897393463745</v>
+        <v>0.4934319659299891</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.631103335524725</v>
+        <v>4.591168671474894</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692309</v>
+        <v>3.682496284692308</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.213492954398236</v>
+        <v>-5.380742509905777</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.212388224575263</v>
+        <v>2.145488402372247</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.623176822550061</v>
+        <v>0.5566190491336755</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.672047924178342</v>
+        <v>4.63211326012851</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.853613255566063</v>
+        <v>3.440392349865186</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.434916007410366</v>
+        <v>4.202617220545396</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.213492954398236</v>
+        <v>-5.380742509905777</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.212388224575263</v>
+        <v>2.145488402372247</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.623176822550061</v>
+        <v>0.5566190491336755</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.427979804396734</v>
+        <v>4.195681017531764</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>158.4%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.9%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-699.6%</t>
+          <t>-672.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.7%</t>
+          <t>-150.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>589.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-278.8%</t>
+          <t>-306.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-168.3%</t>
+          <t>-167.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.325868545081876</v>
+        <v>-9.162891593480584</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5519596522317212</v>
+        <v>-0.4867688715912042</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611472483353487</v>
+        <v>-1.585050501644609</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211860700102685</v>
+        <v>2.227713889128012</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.201289888744284</v>
+        <v>-9.038312937142992</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5009890451406256</v>
+        <v>-0.4357982645001086</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611472483353487</v>
+        <v>-1.585050501644609</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212999844658744</v>
+        <v>2.228853033684071</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.176253207175774</v>
+        <v>-9.013276255574482</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4883405983511135</v>
+        <v>-0.4231498177105966</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.586143395802751</v>
+        <v>-1.559721414093873</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.230831071351293</v>
+        <v>2.24668426037662</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.104120031887893</v>
+        <v>-8.941143080286601</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4537536239973248</v>
+        <v>-0.3885628433568078</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.586143395802751</v>
+        <v>-1.559721414093873</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.23656477558993</v>
+        <v>2.252417964615256</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.032753639278246</v>
+        <v>-8.869776687676953</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.434944329347331</v>
+        <v>-0.369753548706814</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.514777003193103</v>
+        <v>-1.488355021484225</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.269647348761853</v>
+        <v>2.28550053778718</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.939294605293021</v>
+        <v>-8.776317653691729</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4074441970661487</v>
+        <v>-0.3422534164256317</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.514777003193103</v>
+        <v>-1.488355021484225</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.259763867448946</v>
+        <v>2.275617056474272</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.92864142373959</v>
+        <v>-8.644196757357518</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4050174849441501</v>
+        <v>-0.2912396183913213</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.514777003193103</v>
+        <v>-1.488355021484225</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.257929306949572</v>
+        <v>2.273782495974899</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.830734385063099</v>
+        <v>-8.546289718681027</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3661549844470144</v>
+        <v>-0.2523771178941856</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.446791253332547</v>
+        <v>-1.420369271623669</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.298420441892445</v>
+        <v>2.314273630917771</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.806780844087141</v>
+        <v>-8.522336177705069</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3559050619111379</v>
+        <v>-0.2421271953583091</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.422837712356589</v>
+        <v>-1.396415730647711</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.313461072623513</v>
+        <v>2.32931426164884</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.542720905764345</v>
+        <v>-8.258276239382273</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2635414027437712</v>
+        <v>-0.1497635361909424</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.158777774033793</v>
+        <v>-1.132355792324915</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.458636719455439</v>
+        <v>2.474489908480765</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.835641282259506</v>
+        <v>-7.551196615877434</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.01650341299786318</v>
+        <v>0.130281279550692</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.158777774033793</v>
+        <v>-1.132355792324915</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.455849685795138</v>
+        <v>2.471702874820465</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.795456983893316</v>
+        <v>-7.511012317511244</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.03292075623218071</v>
+        <v>0.1466986227850096</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.118593475667602</v>
+        <v>-1.092171493958724</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.480303888702694</v>
+        <v>2.49615707772802</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.632057112953953</v>
+        <v>-7.347612446571882</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.09764752582868264</v>
+        <v>0.2114253923815115</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9551936047282394</v>
+        <v>-0.9287716230193617</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.577710632487068</v>
+        <v>2.593563821512395</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.398575890724355</v>
+        <v>-7.114131224342283</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1989644435583746</v>
+        <v>0.3127423101112035</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7217123824986409</v>
+        <v>-0.6952904007897631</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.72572379466268</v>
+        <v>2.741576983688006</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.24890949971684</v>
+        <v>-6.964464833334768</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2559387896484213</v>
+        <v>0.3697166562012502</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.628808891256105</v>
+        <v>-0.6023869095472272</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.778573679095242</v>
+        <v>2.794426868120569</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.116634026085953</v>
+        <v>-6.832189359703881</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2101097651079304</v>
+        <v>0.3238876316607593</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4965334176252183</v>
+        <v>-0.4701114359163405</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.759199749280929</v>
+        <v>2.775052938306255</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.960895693526211</v>
+        <v>-6.67645102714414</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2752201588194643</v>
+        <v>0.3889980253722927</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3407950850654767</v>
+        <v>-0.314373103356599</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.85545780950441</v>
+        <v>2.871310998529737</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.875931026796891</v>
+        <v>-6.59148636041482</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3221123667348507</v>
+        <v>0.4358902332876795</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2558304183361572</v>
+        <v>-0.2294084366272794</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.919342950765661</v>
+        <v>2.935196139790988</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.981521016569996</v>
+        <v>-6.697076350187924</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1519004412263905</v>
+        <v>0.2656783077792193</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3614204081092615</v>
+        <v>-0.3349984264003837</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.72801302730258</v>
+        <v>2.743866216327906</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.913286431944568</v>
+        <v>-6.628841765562496</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2277386169536477</v>
+        <v>0.3415164835064766</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3430050852367255</v>
+        <v>-0.3165831035278477</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.787606562903187</v>
+        <v>2.803459751928514</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.765346390536969</v>
+        <v>-6.480901724154897</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1702938248782804</v>
+        <v>0.2840716914311092</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.322684169328168</v>
+        <v>-0.2962621876192902</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.683178303809915</v>
+        <v>2.699031492835242</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.712376868282981</v>
+        <v>-6.427932201900909</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1827676475263975</v>
+        <v>0.2965455140792264</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2697146470741791</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.70624603090883</v>
+        <v>2.722099219934157</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.54658867232269</v>
+        <v>-6.262144005940618</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2421223138154209</v>
+        <v>0.3559001803682493</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2697146470741791</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.699285418813737</v>
+        <v>2.715138607839064</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.513225465843921</v>
+        <v>-6.228780799461849</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2699299507880712</v>
+        <v>0.3837078173409001</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2697146470741791</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.71374777319488</v>
+        <v>2.729600962220207</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.404966328721399</v>
+        <v>-6.120521662339327</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3077657260962749</v>
+        <v>0.4215435926491038</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2697146470741791</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.708279893654075</v>
+        <v>2.724133082679402</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792048</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.281675193904269</v>
+        <v>-5.997230527522197</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3545802740337041</v>
+        <v>0.4683581405865329</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1464235122570486</v>
+        <v>-0.1200015305481708</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.77975266855493</v>
+        <v>2.795605857580257</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.228978326772977</v>
+        <v>-5.944533660390905</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3833599991235461</v>
+        <v>0.497137865676375</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.0937266451257574</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.81907176707103</v>
+        <v>2.834924956096357</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.985212884789533</v>
+        <v>-5.700768218407461</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4766468842639746</v>
+        <v>0.590424750816803</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.0937266451257574</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814852475418081</v>
+        <v>2.830705664443407</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.895437212413061</v>
+        <v>-5.610992546030989</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5146814671345794</v>
+        <v>0.6284593336874083</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03212720021144738</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853936456286683</v>
+        <v>2.86978964531201</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.645586818463986</v>
+        <v>-5.361142152081914</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6073636996979115</v>
+        <v>0.7211415662507399</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03212720021144738</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846678531270385</v>
+        <v>2.862531720295712</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.469694725996554</v>
+        <v>-5.185250059614482</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6813196602055327</v>
+        <v>0.7950975267583615</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03212720021144738</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.850277654791034</v>
+        <v>2.86613084381636</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.298248262974091</v>
+        <v>-5.013803596592019</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7632257514690721</v>
+        <v>0.8770036180219005</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1393192628110158</v>
+        <v>0.1657412445198935</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.966473038659065</v>
+        <v>2.982326227684392</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.21822597586497</v>
+        <v>-4.933781309482898</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7942551439290173</v>
+        <v>0.9080330104818461</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2193415499201367</v>
+        <v>0.2457635316290145</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.013506888540835</v>
+        <v>3.029360077566162</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.154590233631035</v>
+        <v>-4.870145567248963</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8244042418769082</v>
+        <v>0.938182108429737</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2829772921540712</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.056383134935513</v>
+        <v>3.072236323960839</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.06089291541464</v>
+        <v>-4.776448249032568</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8430774279472621</v>
+        <v>0.9568552945000908</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2829772921540712</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.037577393719308</v>
+        <v>3.053430582744635</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.071395538479929</v>
+        <v>-4.786950872097857</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8406194553460238</v>
+        <v>0.9543973218988526</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2724746690887824</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.033018896505012</v>
+        <v>3.048872085530339</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.999152970308734</v>
+        <v>-4.669918641382706</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8734457964493219</v>
+        <v>1.005139528019733</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2724746690887824</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036948210339832</v>
+        <v>3.052801399365159</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879965</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.981439283430869</v>
+        <v>-4.652204954504841</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.881209855117808</v>
+        <v>1.012903586688219</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2756559979856992</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.039535591595323</v>
+        <v>3.055388780620649</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502337</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.857965012117851</v>
+        <v>-4.528730683191823</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9275976348630088</v>
+        <v>1.05929136643342</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2756559979856992</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.036533662815316</v>
+        <v>3.052386851840643</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.63794421408084</v>
+        <v>-4.308709885154812</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.017184991088427</v>
+        <v>1.148878722658838</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4168758430536794</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122844606866718</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.505076525017563</v>
+        <v>-4.175842196091534</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.086226249515561</v>
+        <v>1.217919981085973</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4168758430536794</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138738789668542</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.384903441653064</v>
+        <v>-4.055669112727036</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.135441327301663</v>
+        <v>1.267135058872074</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5370489264181784</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211988484127543</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.249650080323087</v>
+        <v>-3.920415751397059</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.199630774395094</v>
+        <v>1.331324505965505</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6723022877481555</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.303228603486969</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.309524907680779</v>
+        <v>-3.980290578754751</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.161718334853443</v>
+        <v>1.293412066423854</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6124274603904634</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.25334119847378</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.76264747767451</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.189704676769942</v>
+        <v>-3.860470347843914</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.224935596451986</v>
+        <v>1.356629328022397</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6124274603904634</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268630367707988</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.192174383231748</v>
+        <v>-3.86294005430572</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.131591913189705</v>
+        <v>1.263285644760116</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6099577539286571</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174792743153346</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.260544569555758</v>
+        <v>-3.931310240629729</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.023505700145402</v>
+        <v>1.155199431715814</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6192334529648721</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.099620024060377</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.372416849181909</v>
+        <v>-4.04318252025588</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9691934969268332</v>
+        <v>1.100887228497245</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6192334529648721</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.090056732692268</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.427936925074499</v>
+        <v>-4.09870259614847</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.084016303262</v>
+        <v>1.215710034832411</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6192334529648721</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.22708756938447</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.25246266528203</v>
+        <v>-3.923228336356</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.158773239170775</v>
+        <v>1.290466970741187</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6192334529648721</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.231654801376258</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.244538290697116</v>
+        <v>-3.915303961771086</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.137685017765948</v>
+        <v>1.26937874933636</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6192334529648721</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.207396830137465</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.238260088127267</v>
+        <v>-3.909025759201237</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.068734612195337</v>
+        <v>1.200428343765749</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6255116555347211</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.139702065080824</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.178407468923544</v>
+        <v>-3.849173139997514</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.102848046308959</v>
+        <v>1.234541777879371</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6255116555347211</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.149874451512956</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.092164005897166</v>
+        <v>-3.762929676971137</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.13229170209337</v>
+        <v>1.263985433663782</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6255116555347211</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.144820722086817</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.137470825296146</v>
+        <v>-3.808236496370117</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.105944749778304</v>
+        <v>1.237638481348716</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5847014925254903</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.112110399725804</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.166503929998447</v>
+        <v>-3.837269601072418</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.094883380930485</v>
+        <v>1.226577112500896</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5847014925254903</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.112662272758906</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.073693448547587</v>
+        <v>-3.744459119621559</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.061280265402194</v>
+        <v>1.192973996972606</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6775119739763497</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.097621253520787</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.118082917877015</v>
+        <v>-3.788848588950986</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.045397953595024</v>
+        <v>1.177091685165436</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.633122504646922</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.072861047847731</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.234624522982357</v>
+        <v>-3.905390194056329</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9938570200646104</v>
+        <v>1.125550751635021</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5165808995415793</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.998011793296248</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.274548617564929</v>
+        <v>-3.945314288638901</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9833786780622487</v>
+        <v>1.11507240963266</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5165808995415793</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.003503089126915</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.302329015466282</v>
+        <v>-3.973094686540254</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9837637206702468</v>
+        <v>1.115457452240658</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4888005016402261</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.998332052154643</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.42070968819642</v>
+        <v>-4.091475359270392</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7747671715788447</v>
+        <v>0.9064609031492559</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4215826494892499</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.79635706086471</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729265</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.529323766639751</v>
+        <v>-4.200089437713723</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8514712009207179</v>
+        <v>0.9831649324911291</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4215826494892499</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.916506721583916</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.493914728391609</v>
+        <v>-4.16468039946558</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8801478423222979</v>
+        <v>1.011841573892709</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4215826494892499</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.931019747686239</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.455531065833457</v>
+        <v>-4.126296736907429</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8929207486879271</v>
+        <v>1.024614480258338</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4599663120474011</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.951469386563498</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.278414735798291</v>
+        <v>-3.949180406872263</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9604963095472954</v>
+        <v>1.092190041117707</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4599663120474011</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.9481984154088</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.323506980631837</v>
+        <v>-3.994272651705809</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9431428033757903</v>
+        <v>1.074836534946201</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3980702688780113</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.911744181269079</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.75072937701123</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.144131559393069</v>
+        <v>-3.814897230467041</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.008679947177712</v>
+        <v>1.140373678748123</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.55484702704873</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.999597211477925</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.189145772913676</v>
+        <v>-3.859911443987647</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9714817171010588</v>
+        <v>1.10317544867147</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5244981317341254</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.962195329620752</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.456150283186111</v>
+        <v>-4.126915954260083</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8703714753310305</v>
+        <v>1.002065206901442</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3301350936911768</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.851269069133929</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760815</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.557348064623284</v>
+        <v>-4.228113735697256</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8290962846526628</v>
+        <v>0.9607900162230743</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2617262801458576</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.809427702903239</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70557166181546</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.550837098008971</v>
+        <v>-4.221602769082943</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8293006328527046</v>
+        <v>0.960994364423116</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2617262801458576</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.807027664457555</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378106</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.531798970301674</v>
+        <v>-4.202564641375646</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8334406031438686</v>
+        <v>0.9651343347142798</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2035426688146631</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.768642216867083</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131253</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.584314772576494</v>
+        <v>-4.255080443650466</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9317286838681307</v>
+        <v>1.063422415438542</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2035426688146631</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.887936618501274</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.598181533910412</v>
+        <v>-4.268947204984384</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9270153083206971</v>
+        <v>1.058709039891108</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1656847520808402</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.866055197447114</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.557698541988067</v>
+        <v>-4.228464213062039</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.949217035486561</v>
+        <v>1.080910767056972</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1656847520808402</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.87206372784404</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.51747620097977</v>
+        <v>-4.080721242827036</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8632561931670795</v>
+        <v>1.037958176428173</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2347856356456299</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.811474479260113</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.601297422254468</v>
+        <v>-4.164542464101735</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.832521326188681</v>
+        <v>1.007223309449774</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2347856356456299</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.814268100791594</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.595144716201684</v>
+        <v>-4.15838975804895</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8356447570014531</v>
+        <v>1.010346740262547</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2409383416984142</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.818622072814923</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.611954014352186</v>
+        <v>-4.175199056199452</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8280015144813626</v>
+        <v>1.002703497742456</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2241290435479125</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.807616970664732</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.549656015576064</v>
+        <v>-4.11290105742333</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9192562677886325</v>
+        <v>1.093958251049726</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2694233078223546</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901129083026218</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.347865817910906</v>
+        <v>-3.911110859758172</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8022643485688226</v>
+        <v>0.976966331829916</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.467441499991509</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.822232000041838</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.3987525305971</v>
+        <v>-3.961997572444367</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.85219989581652</v>
+        <v>1.026901879077613</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4165547873053144</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.861990204752296</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.312141787947294</v>
+        <v>-3.87538682979456</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9014719289924864</v>
+        <v>1.07617391225358</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4951805185104727</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.923793379591435</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.372351085952578</v>
+        <v>-3.935596127799844</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8759241906150441</v>
+        <v>1.050626173876138</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4349712205051882</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.886203781612936</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.323164437268227</v>
+        <v>-3.886409479115493</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8940904681287132</v>
+        <v>1.068792451389807</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4349712205051882</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.884695399652864</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.83351346031625</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.278791305629658</v>
+        <v>-3.842036347476924</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9117025882195768</v>
+        <v>1.086404571480671</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4793443521437568</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.911182146071442</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105969</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.301271656488543</v>
+        <v>-3.864516698335809</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8971042420146134</v>
+        <v>1.071806225275707</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4793443521437568</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.905575940210032</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190327</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.253615925927487</v>
+        <v>-3.816860967774753</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9225482912668403</v>
+        <v>1.097250274527934</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5270000827048125</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.94055113557447</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569619</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.153097767428733</v>
+        <v>-3.716342809275998</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.967647928041067</v>
+        <v>1.142349911302161</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.627518241203567</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.005754404048448</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557296</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.13719243799638</v>
+        <v>-3.700437479843646</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9607647322898802</v>
+        <v>1.135466715550974</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5484055804943282</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.945041480098777</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932771</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.092354036387982</v>
+        <v>-3.655599078235248</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9827977955438683</v>
+        <v>1.157499778804962</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5529490134391977</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.951865242476327</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917053</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.11185249262999</v>
+        <v>-3.675097534477256</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.979159352678143</v>
+        <v>1.153861335939237</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5048643721592934</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.927175397339463</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.06764965554409</v>
+        <v>-3.630894697391355</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.00272009004034</v>
+        <v>1.177422073301434</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5490672092451938</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.95957670211884</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.075209321381136</v>
+        <v>-3.638454363228402</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9981062241747694</v>
+        <v>1.172808207435863</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6038706132550131</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.990868744993979</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284874</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.916917903841864</v>
+        <v>-3.48016294568913</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.112670556373518</v>
+        <v>1.287372539634611</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6038706132550131</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.042116510177019</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321018</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.709275900207388</v>
+        <v>-3.272520942054654</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.194168062421561</v>
+        <v>1.368870045682655</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8115126168894893</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.165142416951958</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.65824380748486</v>
+        <v>-3.221488849332126</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.209529127748843</v>
+        <v>1.384231111009936</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8625447096120172</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.190709900823745</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.593019626357654</v>
+        <v>-3.15626466820492</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.25280620429243</v>
+        <v>1.427508187553523</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9277688907392229</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.247031813592772</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.55559260628652</v>
+        <v>-3.118837648133786</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.263737984620164</v>
+        <v>1.438439967881257</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9330204287684045</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.246143708709562</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.575704262321228</v>
+        <v>-3.138949304168495</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.256950114537521</v>
+        <v>1.431652097798614</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9440477737658237</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.254016908039254</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.547290999221345</v>
+        <v>-3.110536041068611</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.428873190798685</v>
+        <v>1.603575174059778</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8850722110193949</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.379189341412607</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.472508738196332</v>
+        <v>-3.035753780043598</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.578899004426507</v>
+        <v>1.753600987687601</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9598544720444075</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.544171607245432</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998758</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.446424653932524</v>
+        <v>-3.00966969577979</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.581040614145889</v>
+        <v>1.755742597406983</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9598544720444075</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.535879583259291</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896932</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.358546740823404</v>
+        <v>-2.92179178267067</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.614384974973317</v>
+        <v>1.789086958234411</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.075780114467759</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.603628164297081</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395986</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.34965427943012</v>
+        <v>-2.912899321277386</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.635496365257422</v>
+        <v>1.810198348518515</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.075780114467759</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.621182570023873</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945367</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.518130396399998</v>
+        <v>-3.081375438247264</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.559960965874055</v>
+        <v>1.734662949135148</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.047832278751178</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.596268915998508</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.071874203770558</v>
+        <v>-2.635119245617824</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.719733140113692</v>
+        <v>1.894435123374786</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9531136090815453</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.52070741138459</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.049153100087405</v>
+        <v>-2.612398141934672</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.719485604083858</v>
+        <v>1.894187587344952</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9531136090815453</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.511371433881495</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.178354913381448</v>
+        <v>-2.741599955228714</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.82671100461741</v>
+        <v>2.001412987878504</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8239117957875031</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.592756471756239</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.204229311855474</v>
+        <v>-2.76747435370274</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.853439067721446</v>
+        <v>2.02814105098254</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8688234044992442</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.65678125947693</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799967</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.1971746216403</v>
+        <v>-2.760419663487566</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.852936299797061</v>
+        <v>2.027638283058154</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.875878094714418</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.657689429595579</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.170223397313812</v>
+        <v>-2.733468439161078</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.873722943172398</v>
+        <v>2.048424926433491</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8907584407421372</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.676623790856953</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.191767625144599</v>
+        <v>-2.755012666991866</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.049208384185043</v>
+        <v>2.223910367446136</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8907584407421372</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.860726923001912</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714429</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.214175742949471</v>
+        <v>-2.777420784796738</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.032361831966087</v>
+        <v>2.207063815227181</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8907584407421372</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.852843617904905</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.242399978527072</v>
+        <v>-2.805645020374338</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.023126137284684</v>
+        <v>2.197828120545778</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9087351931934458</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.865683668925328</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.251840904415602</v>
+        <v>-2.815085946262868</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.075603484651119</v>
+        <v>2.250305467912213</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.031162310736837</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.99539365717321</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.340717535584075</v>
+        <v>-2.903962577431342</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.042943926729031</v>
+        <v>2.217645909990124</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9422856795683634</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.944958773017427</v>
+        <v>4.020035846244808</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.417047513184981</v>
+        <v>-2.980292555032248</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.010523748582443</v>
+        <v>2.185225731843537</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9422856795683634</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.943070585911202</v>
+        <v>4.018147659138584</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488775</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.510711457862523</v>
+        <v>-3.073956499709789</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.967878400314289</v>
+        <v>2.142580383575383</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8486217348908219</v>
+        <v>0.9737501902697926</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.881692448707539</v>
+        <v>3.956769521934921</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.672279883389778</v>
+        <v>-3.235524925237044</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.901685040313539</v>
+        <v>2.076387023574633</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7218388110929426</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.804056704638964</v>
+        <v>3.879133777866346</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389351</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.780580545259897</v>
+        <v>-3.343825587107164</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.87143818243141</v>
+        <v>2.046140165692504</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7218388110929426</v>
+        <v>0.8469672664719132</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.817130111504882</v>
+        <v>3.892207184732265</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.873728016563264</v>
+        <v>-3.43697305841053</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.826184390693004</v>
+        <v>2.000886373954097</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5990095998104098</v>
+        <v>0.7241380551893805</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.735437781518303</v>
+        <v>3.810514854745685</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006978</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.901628803672737</v>
+        <v>-3.464873845520003</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.813548116976216</v>
+        <v>1.98825010023731</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.564412675667475</v>
+        <v>0.6895411310464457</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.713203668159544</v>
+        <v>3.788280741386926</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.024154906375631</v>
+        <v>-3.587399948222897</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.761302119872258</v>
+        <v>1.936004103133351</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4418865729645811</v>
+        <v>0.5670150283435518</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.636452450515006</v>
+        <v>3.711529523742389</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.61934808158594</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.25466940256122</v>
+        <v>-3.817914444408486</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.735802280988526</v>
+        <v>1.910504264249619</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2113720767789924</v>
+        <v>0.3365005321579631</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.564849712394157</v>
+        <v>3.639926785621539</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814667</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.603414487785663</v>
+        <v>-4.16665952963293</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.736615965900596</v>
+        <v>1.911317949161689</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1026241228600946</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.639912659044665</v>
+        <v>3.714989732272048</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.757400905561804</v>
+        <v>-4.32064594740907</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.744001667935779</v>
+        <v>1.918703651196872</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1026241228600946</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.708892928190305</v>
+        <v>3.783970001417687</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.706879001734138</v>
+        <v>-4.270124043581404</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.750261631586966</v>
+        <v>1.92496361484806</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1026241228600946</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.694944130310426</v>
+        <v>3.770021203537808</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.959354155741862</v>
+        <v>-4.522599197589129</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.66114205903929</v>
+        <v>1.835844042300384</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1026241228600946</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.70681461936584</v>
+        <v>3.781891692593222</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.252249912221274</v>
+        <v>-4.815494954068541</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.54519429096647</v>
+        <v>1.719896274227563</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1026241228600946</v>
+        <v>0.2277525782390653</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.708025153884783</v>
+        <v>3.783102227112166</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.438914040356083</v>
+        <v>-5.002159082203349</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.474650381939868</v>
+        <v>1.649352365200961</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.0758851520355347</v>
+        <v>0.2010136074145054</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.696103513617369</v>
+        <v>3.771180586844751</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.584934727270045</v>
+        <v>-5.148179769117311</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.411319959910472</v>
+        <v>1.586021943171565</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.06680206024167773</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.685731511277244</v>
+        <v>3.760808584504626</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.676648736379629</v>
+        <v>-5.239893778226897</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.536838412965682</v>
+        <v>1.711540396226776</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.06680206024167773</v>
+        <v>0.1919305156206484</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.847935567976288</v>
+        <v>3.923012641203671</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071553</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.708300395439599</v>
+        <v>-5.271545437286866</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.519024387305509</v>
+        <v>1.693726370566602</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.06163360299723752</v>
+        <v>0.1867620583762082</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.839681131593438</v>
+        <v>3.914758204820821</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.790235213708482</v>
+        <v>-5.353480255555749</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.496479877566447</v>
+        <v>1.67118186082754</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.05169885741015734</v>
+        <v>0.176827312789128</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.843949701809681</v>
+        <v>3.919026775037064</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332692</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.89221133595689</v>
+        <v>-5.455456377804157</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.464615067122986</v>
+        <v>1.639317050384079</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.05027726483825024</v>
+        <v>0.07485119054072042</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.791689666916539</v>
+        <v>3.866766740143922</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.782205052479668</v>
+        <v>-5.345450094326935</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.50077046775805</v>
+        <v>1.675472451019143</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.02707269292097503</v>
+        <v>0.09805576245799563</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.79776529731108</v>
+        <v>3.872842370538462</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.639145476738742</v>
+        <v>-5.202390518586009</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.562244308776395</v>
+        <v>1.736946292037488</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.01905926633099575</v>
+        <v>0.1060691890479749</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.806823363987041</v>
+        <v>3.881900437214424</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051789</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.337698751266904</v>
+        <v>-4.900943793114171</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.690083881847666</v>
+        <v>1.864785865108759</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2823874591408415</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.99495228215268</v>
+        <v>4.070029355380062</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.362288995502088</v>
+        <v>-4.925534037349355</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.681218961906303</v>
+        <v>1.855920945167396</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2823874591408415</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.995923459905391</v>
+        <v>4.071000533132773</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.311250619495568</v>
+        <v>-4.874495661342835</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.702477216688667</v>
+        <v>1.87717919994976</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2823874591408415</v>
+        <v>0.4075159145198122</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.996766364285146</v>
+        <v>4.071843437512529</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969538</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.270111324628937</v>
+        <v>-4.833356366476204</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.737971033509464</v>
+        <v>1.912673016770557</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3235267540074723</v>
+        <v>0.448655209386443</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.04048804007927</v>
+        <v>4.115565113306652</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700474</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.173476412610297</v>
+        <v>-4.736721454457564</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.592808994440855</v>
+        <v>1.767510977701948</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4201616660261123</v>
+        <v>0.5452901214050829</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.914652983414388</v>
+        <v>3.989730056641771</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80468896107764</v>
+        <v>3.804688961077636</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.30405714714114</v>
+        <v>-4.867302188988407</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.544078744702482</v>
+        <v>1.718780727963575</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2895809314952698</v>
+        <v>0.4147093868742404</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.839806586769847</v>
+        <v>3.91488365999723</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833453</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.139560812950178</v>
+        <v>-4.702805854797445</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.594304097454949</v>
+        <v>1.769006080716042</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4540772656862316</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.922931206360507</v>
+        <v>3.998008279587889</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.16693074563461</v>
+        <v>-4.730175787481877</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.582543834817606</v>
+        <v>1.757245818078699</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4540772656862316</v>
+        <v>0.5792057210652023</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.922118916796936</v>
+        <v>3.997195990024319</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147905</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.177315940524499</v>
+        <v>-4.740560982371766</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.588258535986723</v>
+        <v>1.762960519247816</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4436920707963423</v>
+        <v>0.568820526175313</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.925756578988075</v>
+        <v>4.000833652215458</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.195904099246724</v>
+        <v>-4.759149141093991</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.651660278274258</v>
+        <v>1.826362261535351</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.425103912074117</v>
+        <v>0.5502323674530876</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.985440689531165</v>
+        <v>4.060517762758548</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.19620264594276</v>
+        <v>-4.759447687790027</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.648409870414142</v>
+        <v>1.823111853675235</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4248053653780811</v>
+        <v>0.5499338207570517</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.982130572331842</v>
+        <v>4.057207645559225</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.095379512252332</v>
+        <v>-4.6586245540996</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.693270018829705</v>
+        <v>1.867972002090798</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4372695808624349</v>
+        <v>0.5623980362414055</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.994139996561846</v>
+        <v>4.069217069789229</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.904598151499926</v>
+        <v>-4.467843193347193</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.769711816609211</v>
+        <v>1.944413799870304</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6280509416148423</v>
+        <v>0.7531793969938129</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.108738066491834</v>
+        <v>4.183815139719216</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.797634793650504</v>
+        <v>-4.360879835497771</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.792334005486576</v>
+        <v>1.967035988747669</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6865155495746438</v>
+        <v>0.8116440049536143</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.123653677005311</v>
+        <v>4.198730750232693</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.742304205748741</v>
+        <v>-4.305549247596009</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.849433177259339</v>
+        <v>2.024135160520432</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7418461374764059</v>
+        <v>0.8669745928553765</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.191818966358427</v>
+        <v>4.266896039585809</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.730250078835779</v>
+        <v>-4.293495120683046</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.847941395925962</v>
+        <v>2.022643379187056</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7539002643893687</v>
+        <v>0.8790287197683393</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.192738010407642</v>
+        <v>4.267815083635025</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.771405198404</v>
+        <v>-4.334650240251267</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.83335997828281</v>
+        <v>2.008061961543903</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7127451448211478</v>
+        <v>0.8378736002001184</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.169925568850846</v>
+        <v>4.245002642078228</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.70335663571247</v>
+        <v>-4.266601677559737</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.873430429237304</v>
+        <v>2.048132412498397</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7807937075126776</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.223605732343646</v>
+        <v>4.298682805571028</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.93495702888197</v>
+        <v>-4.498202070729238</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.800992942143098</v>
+        <v>1.975694925404191</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7807937075126776</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.24380840251724</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781706</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.953029537173582</v>
+        <v>-4.516274579020849</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.793763938826453</v>
+        <v>1.968465922087546</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7807937075126776</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.24380840251724</v>
+        <v>4.318885475744622</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082835</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.128136369750028</v>
+        <v>-4.691381411597295</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.683973119389342</v>
+        <v>1.858675102650435</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7807937075126776</v>
+        <v>0.9059221628916482</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.204060316110707</v>
+        <v>4.279137389338089</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943587</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.096850349209572</v>
+        <v>-4.660095391056839</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.703510146602464</v>
+        <v>1.878212129863557</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.812079728053133</v>
+        <v>0.9372081834321035</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.22985454743192</v>
+        <v>4.304931620659302</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677825</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.943824957096288</v>
+        <v>-4.507069998943555</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.863891303020682</v>
+        <v>2.038593286281775</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9651051201664171</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.420840782272795</v>
+        <v>4.495917855500178</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073884</v>
+        <v>3.741298518073878</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.927454927611688</v>
+        <v>-4.535377312816825</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.057905539722814</v>
+        <v>2.214736585640759</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9651051201664171</v>
+        <v>1.090233575545388</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.608307007181087</v>
+        <v>4.683384080408469</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903169</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.09404815272521</v>
+        <v>-4.701970537930348</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.960671201031488</v>
+        <v>2.117502246949432</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7985118950528947</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.477754023467056</v>
+        <v>4.552831096694439</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568383</v>
+        <v>3.708202704568378</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.071012359363644</v>
+        <v>-4.678934744568782</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.973561921037831</v>
+        <v>2.130392966955776</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7985118950528947</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.481430426128774</v>
+        <v>4.556507499356156</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682205</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.041766378907948</v>
+        <v>-4.649688764113085</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.982878368343605</v>
+        <v>2.13970941426155</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7985118950528947</v>
+        <v>0.9236403504318653</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.479048481252269</v>
+        <v>4.554125554479652</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539108</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.148691926785799</v>
+        <v>-4.756614311990936</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.9374013883501</v>
+        <v>2.094232434268045</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6915863471750433</v>
+        <v>0.816714802554014</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.412186391683193</v>
+        <v>4.487263464910575</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983738</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.293710485293047</v>
+        <v>-4.901632870498185</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.880822767090435</v>
+        <v>2.03765381300838</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5465677886677948</v>
+        <v>0.6716962440467654</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.326604058722078</v>
+        <v>4.40168113194946</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.412052251077765</v>
+        <v>-5.019974636282902</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.933417300034301</v>
+        <v>2.090248345952246</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5572538272306848</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.432946921117566</v>
+        <v>4.508023994344947</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.463462673398473</v>
+        <v>-5.07138505860361</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.910638828231956</v>
+        <v>2.067469874149901</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5572538272306848</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.430732618243504</v>
+        <v>4.505809691470886</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720067</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.542882124606225</v>
+        <v>-5.150804509811362</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.878774175823145</v>
+        <v>2.03560522174109</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5572538272306848</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.430635746317794</v>
+        <v>4.505712819545176</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581135</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.638345122523442</v>
+        <v>-5.24626750772858</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.840582870214301</v>
+        <v>1.997413916132247</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5572538272306848</v>
+        <v>0.6823822826096555</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.430629639875837</v>
+        <v>4.505706713103219</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500737</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.678365120567226</v>
+        <v>-5.286287505772363</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.822671267559399</v>
+        <v>1.979502313477344</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.517233829186901</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.404714037612178</v>
+        <v>4.479791110839559</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636272</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.73373428269942</v>
+        <v>-5.341656667904557</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.806257420454248</v>
+        <v>1.963088466372193</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.517233829186901</v>
+        <v>0.6423622845658716</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.410447855359904</v>
+        <v>4.485524928587286</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396015</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.779172062530247</v>
+        <v>-5.387094447735384</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.78762067186485</v>
+        <v>1.944451717782795</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4743888385087413</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.384279224295941</v>
+        <v>4.459356297523323</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396424</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.690965228382669</v>
+        <v>-5.298887613587806</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.8427777983742</v>
+        <v>1.999608844292145</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4743888385087413</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.40415361714626</v>
+        <v>4.479230690373642</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299178</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.584930233177359</v>
+        <v>-5.192852618382497</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.868892496981052</v>
+        <v>2.025723542898997</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4743888385087413</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.387854317670988</v>
+        <v>4.462931390898371</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590409</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.401718570044264</v>
+        <v>-5.009640955249401</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.944608111698336</v>
+        <v>2.101439157616281</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4743888385087413</v>
+        <v>0.599517293887712</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.390285267135034</v>
+        <v>4.465362340362416</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146288</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.329997123030413</v>
+        <v>-4.93791950823555</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.939087876351765</v>
+        <v>2.095918922269711</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5461102855225919</v>
+        <v>0.6712387409015627</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.399109321191233</v>
+        <v>4.474186394418616</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72380989067685</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.307624097422707</v>
+        <v>-4.915546482627844</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.894952832516019</v>
+        <v>2.051783878433964</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5573660366354934</v>
+        <v>0.6824944920144642</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.352778517780146</v>
+        <v>4.427855591007528</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739467</v>
+        <v>3.715627631739461</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.340640393333452</v>
+        <v>-4.948562778538589</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.066944519037077</v>
+        <v>2.223775564955022</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.4879286599687419</v>
+        <v>0.6130571153477127</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.49631429666545</v>
+        <v>4.571391369892833</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166414</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.329112757683843</v>
+        <v>-4.93703514288898</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.06347679912517</v>
+        <v>2.220307845043115</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.5469293181701043</v>
+        <v>0.6720577735490751</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.523635917414516</v>
+        <v>4.598712990641899</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519034</v>
+        <v>3.717170884519029</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.426454259026212</v>
+        <v>-5.034376644231349</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.02820831111001</v>
+        <v>2.185039357027956</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5025091360046159</v>
+        <v>0.6276375913835868</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.500651920637012</v>
+        <v>4.575728993864395</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710421</v>
+        <v>3.705221264710415</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.512310288366178</v>
+        <v>-5.120232673571316</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.995116981566862</v>
+        <v>2.151948027484807</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.4601330667784809</v>
+        <v>0.5852615221574518</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.47647736129417</v>
+        <v>4.551554434521552</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893118</v>
+        <v>3.691855684893112</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.521147085782298</v>
+        <v>-5.129069470987435</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.974001464420916</v>
+        <v>2.130832510338861</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.4526908941371301</v>
+        <v>0.577819349516101</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.454431259529861</v>
+        <v>4.529508332757244</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950191</v>
+        <v>3.715564596950186</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.492112731976445</v>
+        <v>-5.220452033552894</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.995779716988307</v>
+        <v>2.104443996357727</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4817252479429827</v>
+        <v>0.4864367869506428</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.482016382858422</v>
+        <v>4.484843306263018</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171928</v>
+        <v>3.673998560171922</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.480406013989439</v>
+        <v>-5.208745315565888</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.102590662007377</v>
+        <v>2.211254941376798</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4934319659299891</v>
+        <v>0.4981435049376493</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.591168671474894</v>
+        <v>4.59399559487949</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692308</v>
+        <v>3.682496284692298</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.380742509905777</v>
+        <v>-5.109081811482225</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.145488402372247</v>
+        <v>2.254152681741667</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5566190491336755</v>
+        <v>0.5613305881413357</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.63211326012851</v>
+        <v>4.634940183533106</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.440392349865186</v>
+        <v>3.788030820012067</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.202617220545396</v>
+        <v>4.700328743050276</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.380742509905777</v>
+        <v>-5.109081811482225</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.145488402372247</v>
+        <v>2.254152681741667</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5566190491336755</v>
+        <v>0.5613305881413357</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.195681017531764</v>
+        <v>4.693392540036644</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>104.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>158.4%</t>
+          <t>145.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-50.6%</t>
+          <t>-37.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.2%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-672.5%</t>
+          <t>-667.7%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.8%</t>
+          <t>-148.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.3%</t>
+          <t>588.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-306.5%</t>
+          <t>-305.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.9%</t>
+          <t>-153.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.644196757357518</v>
+        <v>-8.765664472138297</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2912396183913213</v>
+        <v>-0.3398267043036332</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.488355021484225</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.546289718681027</v>
+        <v>-8.667757433461807</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2523771178941856</v>
+        <v>-0.3009642038064975</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.420369271623669</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.522336177705069</v>
+        <v>-8.643803892485849</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2421271953583091</v>
+        <v>-0.2907142812706209</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.396415730647711</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.258276239382273</v>
+        <v>-8.379743954163052</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1497635361909424</v>
+        <v>-0.1983506221032543</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.132355792324915</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.551196615877434</v>
+        <v>-7.672664330658214</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.130281279550692</v>
+        <v>0.08169419363838015</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.132355792324915</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.511012317511244</v>
+        <v>-7.632480032292023</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1466986227850096</v>
+        <v>0.09811153687269769</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.092171493958724</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.347612446571882</v>
+        <v>-7.469080161352661</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2114253923815115</v>
+        <v>0.1628383064691996</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9287716230193617</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.114131224342283</v>
+        <v>-7.235598939123062</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3127423101112035</v>
+        <v>0.2641552241988916</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6952904007897631</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.964464833334768</v>
+        <v>-7.085932548115547</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3697166562012502</v>
+        <v>0.3211295702889383</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6023869095472272</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.832189359703881</v>
+        <v>-6.953657074484661</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3238876316607593</v>
+        <v>0.2753005457484474</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4701114359163405</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.67645102714414</v>
+        <v>-6.797918741924919</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3889980253722927</v>
+        <v>0.3404109394599812</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.314373103356599</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.59148636041482</v>
+        <v>-6.712954075195599</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4358902332876795</v>
+        <v>0.3873031473753676</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2294084366272794</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.697076350187924</v>
+        <v>-6.818544064968703</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2656783077792193</v>
+        <v>0.2170912218669074</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3349984264003837</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.628841765562496</v>
+        <v>-6.750309480343276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3415164835064766</v>
+        <v>0.2929293975941647</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3165831035278477</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.480901724154897</v>
+        <v>-6.602369438935677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2840716914311092</v>
+        <v>0.2354846055187974</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2962621876192902</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.427932201900909</v>
+        <v>-6.549399916681688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2965455140792264</v>
+        <v>0.2479584281669145</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2432926653653013</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.262144005940618</v>
+        <v>-6.383611720721397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3559001803682493</v>
+        <v>0.3073130944559379</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2432926653653013</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.228780799461849</v>
+        <v>-6.350248514242629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3837078173409001</v>
+        <v>0.3351207314285882</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2432926653653013</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.120521662339327</v>
+        <v>-6.241989377120107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4215435926491038</v>
+        <v>0.3729565067367919</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2432926653653013</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.997230527522197</v>
+        <v>-6.118698242302976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4683581405865329</v>
+        <v>0.419771054674221</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1200015305481708</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.944533660390905</v>
+        <v>-6.066001375171685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.497137865676375</v>
+        <v>0.4485507797640631</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.06730466341687963</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.700768218407461</v>
+        <v>-5.822235933188241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.590424750816803</v>
+        <v>0.5418376649044916</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.06730466341687963</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.610992546030989</v>
+        <v>-5.732460260811768</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6284593336874083</v>
+        <v>0.5798722477750964</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.005705218502569609</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.361142152081914</v>
+        <v>-5.482609866862694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7211415662507399</v>
+        <v>0.6725544803384285</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.005705218502569609</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.185250059614482</v>
+        <v>-5.306717774395262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7950975267583615</v>
+        <v>0.7465104408460497</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.005705218502569609</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.013803596592019</v>
+        <v>-5.135271311372798</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8770036180219005</v>
+        <v>0.8284165321095891</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1657412445198935</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.933781309482898</v>
+        <v>-5.055249024263677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9080330104818461</v>
+        <v>0.8594459245695343</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2457635316290145</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.870145567248963</v>
+        <v>-4.991613282029743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.938182108429737</v>
+        <v>0.8895950225174254</v>
       </c>
       <c r="F1923" t="n">
         <v>0.309399273862949</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.776448249032568</v>
+        <v>-4.897915963813348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9568552945000908</v>
+        <v>0.9082682085877791</v>
       </c>
       <c r="F1924" t="n">
         <v>0.309399273862949</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.786950872097857</v>
+        <v>-4.908418586878637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9543973218988526</v>
+        <v>0.9058102359865408</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2988966507976601</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.669918641382706</v>
+        <v>-4.836176018707442</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.005139528019733</v>
+        <v>0.9386365770898388</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.652204954504841</v>
+        <v>-4.818462331829577</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.012903586688219</v>
+        <v>0.946400635758325</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.528730683191823</v>
+        <v>-4.694988060516558</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.05929136643342</v>
+        <v>0.9927884155035258</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.308709885154812</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.148878722658838</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.175842196091534</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.217919981085973</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.055669112727036</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.267135058872074</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.920415751397059</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.331324505965505</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.980290578754751</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.293412066423854</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767451</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.860470347843914</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.356629328022397</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.86294005430572</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.263285644760116</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.931310240629729</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.155199431715814</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.04318252025588</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.100887228497245</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.09870259614847</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.215710034832411</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.923228336356</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.290466970741187</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.915303961771086</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.26937874933636</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.909025759201237</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.200428343765749</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.849173139997514</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.234541777879371</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.762929676971137</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.263985433663782</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.808236496370117</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.237638481348716</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.837269601072418</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.226577112500896</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.744459119621559</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.192973996972606</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.788848588950986</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.177091685165436</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.905390194056329</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.125550751635021</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.945314288638901</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.11507240963266</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.973094686540254</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.115457452240658</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.091475359270392</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9064609031492559</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729265</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.200089437713723</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9831649324911291</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.16468039946558</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.011841573892709</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.126296736907429</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.024614480258338</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.949180406872263</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.092190041117707</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.994272651705809</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.074836534946201</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701123</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.814897230467041</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.140373678748123</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.859911443987647</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.10317544867147</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.126915954260083</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.002065206901442</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760813</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.228113735697256</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9607900162230743</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.221602769082943</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.960994364423116</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.202564641375646</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9651343347142798</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.255080443650466</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.063422415438542</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067859</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.268947204984384</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.058709039891108</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789117</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.228464213062039</v>
+        <v>-4.394721590386775</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.080910767056972</v>
+        <v>1.014407816127078</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.080721242827036</v>
+        <v>-4.246978620151772</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.037958176428173</v>
+        <v>0.9714552254982785</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3599140910246011</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.164542464101735</v>
+        <v>-4.330799841426471</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.007223309449774</v>
+        <v>0.9407203585198802</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3599140910246011</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.15838975804895</v>
+        <v>-4.324647135373686</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.010346740262547</v>
+        <v>0.9438437893326523</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.175199056199452</v>
+        <v>-4.341456433524188</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.002703497742456</v>
+        <v>0.9362005468125618</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798421</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.11290105742333</v>
+        <v>-4.279158434748066</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.093958251049726</v>
+        <v>1.027455300119831</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.911110859758172</v>
+        <v>-4.077368237082908</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.976966331829916</v>
+        <v>0.9104633809000218</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.961997572444367</v>
+        <v>-4.128254949769103</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.026901879077613</v>
+        <v>0.9603989281477192</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.87538682979456</v>
+        <v>-4.041644207119296</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.07617391225358</v>
+        <v>1.009670961323685</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.935596127799844</v>
+        <v>-4.101853505124581</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.050626173876138</v>
+        <v>0.9841232229462431</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.886409479115493</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.068792451389807</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.842036347476924</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.086404571480671</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.864516698335809</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.071806225275707</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.816860967774753</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.097250274527934</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.716342809275998</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.142349911302161</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.700437479843646</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.135466715550974</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.655599078235248</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.157499778804962</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.675097534477256</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.153861335939237</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.630894697391355</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.177422073301434</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.638454363228402</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.172808207435863</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284874</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.48016294568913</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.287372539634611</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321018</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.272520942054654</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.368870045682655</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.221488849332126</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.384231111009936</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.15626466820492</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.427508187553523</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.118837648133786</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.438439967881257</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.138949304168495</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.431652097798614</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.110536041068611</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.603575174059778</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.035753780043598</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.753600987687601</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47390,10 +47390,10 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.00966969577979</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.755742597406983</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47413,10 +47413,10 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.92179178267067</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.789086958234411</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47436,10 +47436,10 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.912899321277386</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.810198348518515</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47459,10 +47459,10 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.081375438247264</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.734662949135148</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47482,10 +47482,10 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.635119245617824</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.894435123374786</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47505,10 +47505,10 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.612398141934672</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.894187587344952</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47528,10 +47528,10 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.741599955228714</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.001412987878504</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.76747435370274</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.02814105098254</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47574,10 +47574,10 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.760419663487566</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.027638283058154</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
@@ -47597,10 +47597,10 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.733468439161078</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.048424926433491</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.755012666991866</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.223910367446136</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.777420784796738</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.207063815227181</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.805645020374338</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.197828120545778</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.815085946262868</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.250305467912213</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
         <v>1.156290766115808</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.903962577431342</v>
+        <v>-3.070219954756078</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.217645909990124</v>
+        <v>2.15114295906023</v>
       </c>
       <c r="F2007" t="n">
         <v>1.067414134947334</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.980292555032248</v>
+        <v>-3.146549932356984</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.185225731843537</v>
+        <v>2.118722780913642</v>
       </c>
       <c r="F2008" t="n">
         <v>1.067414134947334</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.073956499709789</v>
+        <v>-3.240213877034526</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.142580383575383</v>
+        <v>2.076077432645488</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9737501902697926</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.235524925237044</v>
+        <v>-3.401782302561781</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.076387023574633</v>
+        <v>2.009884072644738</v>
       </c>
       <c r="F2010" t="n">
         <v>0.8469672664719132</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.343825587107164</v>
+        <v>-3.5100829644319</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.046140165692504</v>
+        <v>1.979637214762609</v>
       </c>
       <c r="F2011" t="n">
         <v>0.8469672664719132</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.43697305841053</v>
+        <v>-3.603230435735267</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.000886373954097</v>
+        <v>1.934383423024203</v>
       </c>
       <c r="F2012" t="n">
         <v>0.7241380551893805</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.464873845520003</v>
+        <v>-3.63113122284474</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.98825010023731</v>
+        <v>1.921747149307415</v>
       </c>
       <c r="F2013" t="n">
         <v>0.6895411310464457</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.587399948222897</v>
+        <v>-3.753657325547634</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.936004103133351</v>
+        <v>1.869501152203457</v>
       </c>
       <c r="F2014" t="n">
         <v>0.5670150283435518</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.817914444408486</v>
+        <v>-3.984171821733223</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.910504264249619</v>
+        <v>1.844001313319725</v>
       </c>
       <c r="F2015" t="n">
         <v>0.3365005321579631</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.16665952963293</v>
+        <v>-4.332916906957666</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.911317949161689</v>
+        <v>1.844814998231794</v>
       </c>
       <c r="F2016" t="n">
         <v>0.2277525782390653</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.32064594740907</v>
+        <v>-4.486903324733807</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.918703651196872</v>
+        <v>1.852200700266978</v>
       </c>
       <c r="F2017" t="n">
         <v>0.2277525782390653</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.270124043581404</v>
+        <v>-4.436381420906141</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.92496361484806</v>
+        <v>1.858460663918165</v>
       </c>
       <c r="F2018" t="n">
         <v>0.2277525782390653</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.522599197589129</v>
+        <v>-4.688856574913865</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.835844042300384</v>
+        <v>1.769341091370489</v>
       </c>
       <c r="F2019" t="n">
         <v>0.2277525782390653</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973155</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.815494954068541</v>
+        <v>-4.981752331393277</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.719896274227563</v>
+        <v>1.653393323297668</v>
       </c>
       <c r="F2020" t="n">
         <v>0.2277525782390653</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.002159082203349</v>
+        <v>-5.168416459528085</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.649352365200961</v>
+        <v>1.582849414271066</v>
       </c>
       <c r="F2021" t="n">
         <v>0.2010136074145054</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916199</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.148179769117311</v>
+        <v>-5.314437146442048</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.586021943171565</v>
+        <v>1.519518992241671</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1919305156206484</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.239893778226897</v>
+        <v>-5.406151155551633</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.711540396226776</v>
+        <v>1.645037445296881</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1919305156206484</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.271545437286866</v>
+        <v>-5.437802814611603</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.693726370566602</v>
+        <v>1.627223419636707</v>
       </c>
       <c r="F2024" t="n">
         <v>0.1867620583762082</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868143</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.353480255555749</v>
+        <v>-5.519737632880486</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.67118186082754</v>
+        <v>1.604678909897645</v>
       </c>
       <c r="F2025" t="n">
         <v>0.176827312789128</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.455456377804157</v>
+        <v>-5.621713755128893</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.639317050384079</v>
+        <v>1.572814099454185</v>
       </c>
       <c r="F2026" t="n">
         <v>0.07485119054072042</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.345450094326935</v>
+        <v>-5.511707471651672</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.675472451019143</v>
+        <v>1.608969500089248</v>
       </c>
       <c r="F2027" t="n">
         <v>0.09805576245799563</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.202390518586009</v>
+        <v>-5.368647895910746</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.736946292037488</v>
+        <v>1.670443341107593</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1060691890479749</v>
@@ -48212,16 +48212,16 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.900943793114171</v>
+        <v>-5.067201170438908</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.864785865108759</v>
+        <v>1.798282914178864</v>
       </c>
       <c r="F2029" t="n">
         <v>0.4075159145198122</v>
@@ -48235,16 +48235,16 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.925534037349355</v>
+        <v>-5.091791414674092</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.855920945167396</v>
+        <v>1.789417994237501</v>
       </c>
       <c r="F2030" t="n">
         <v>0.4075159145198122</v>
@@ -48258,16 +48258,16 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.874495661342835</v>
+        <v>-5.040753038667572</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.87717919994976</v>
+        <v>1.810676249019865</v>
       </c>
       <c r="F2031" t="n">
         <v>0.4075159145198122</v>
@@ -48281,16 +48281,16 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969538</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.833356366476204</v>
+        <v>-4.999613743800941</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.912673016770557</v>
+        <v>1.846170065840663</v>
       </c>
       <c r="F2032" t="n">
         <v>0.448655209386443</v>
@@ -48304,16 +48304,16 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700474</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.736721454457564</v>
+        <v>-4.902978831782301</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.767510977701948</v>
+        <v>1.701008026772053</v>
       </c>
       <c r="F2033" t="n">
         <v>0.5452901214050829</v>
@@ -48327,16 +48327,16 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077636</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.867302188988407</v>
+        <v>-5.033559566313143</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.718780727963575</v>
+        <v>1.65227777703368</v>
       </c>
       <c r="F2034" t="n">
         <v>0.4147093868742404</v>
@@ -48350,16 +48350,16 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833453</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.702805854797445</v>
+        <v>-4.869063232122182</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.769006080716042</v>
+        <v>1.702503129786148</v>
       </c>
       <c r="F2035" t="n">
         <v>0.5792057210652023</v>
@@ -48373,16 +48373,16 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.730175787481877</v>
+        <v>-4.896433164806614</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.757245818078699</v>
+        <v>1.690742867148805</v>
       </c>
       <c r="F2036" t="n">
         <v>0.5792057210652023</v>
@@ -48396,16 +48396,16 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147905</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.740560982371766</v>
+        <v>-4.906818359696503</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.762960519247816</v>
+        <v>1.696457568317921</v>
       </c>
       <c r="F2037" t="n">
         <v>0.568820526175313</v>
@@ -48419,16 +48419,16 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735277</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.759149141093991</v>
+        <v>-4.925406518418728</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.826362261535351</v>
+        <v>1.759859310605457</v>
       </c>
       <c r="F2038" t="n">
         <v>0.5502323674530876</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.759447687790027</v>
+        <v>-4.925705065114764</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.823111853675235</v>
+        <v>1.756608902745341</v>
       </c>
       <c r="F2039" t="n">
         <v>0.5499338207570517</v>
@@ -48465,16 +48465,16 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.6586245540996</v>
+        <v>-4.824881931424336</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.867972002090798</v>
+        <v>1.801469051160903</v>
       </c>
       <c r="F2040" t="n">
         <v>0.5623980362414055</v>
@@ -48488,16 +48488,16 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.467843193347193</v>
+        <v>-4.634100570671929</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.944413799870304</v>
+        <v>1.877910848940409</v>
       </c>
       <c r="F2041" t="n">
         <v>0.7531793969938129</v>
@@ -48511,16 +48511,16 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.360879835497771</v>
+        <v>-4.527137212822508</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.967035988747669</v>
+        <v>1.900533037817774</v>
       </c>
       <c r="F2042" t="n">
         <v>0.8116440049536143</v>
@@ -48534,16 +48534,16 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.305549247596009</v>
+        <v>-4.471806624920745</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.024135160520432</v>
+        <v>1.957632209590538</v>
       </c>
       <c r="F2043" t="n">
         <v>0.8669745928553765</v>
@@ -48557,16 +48557,16 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.293495120683046</v>
+        <v>-4.459752498007783</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.022643379187056</v>
+        <v>1.956140428257161</v>
       </c>
       <c r="F2044" t="n">
         <v>0.8790287197683393</v>
@@ -48580,16 +48580,16 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.334650240251267</v>
+        <v>-4.500907617576003</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.008061961543903</v>
+        <v>1.941559010614008</v>
       </c>
       <c r="F2045" t="n">
         <v>0.8378736002001184</v>
@@ -48603,16 +48603,16 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.266601677559737</v>
+        <v>-4.432859054884474</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.048132412498397</v>
+        <v>1.981629461568502</v>
       </c>
       <c r="F2046" t="n">
         <v>0.9059221628916482</v>
@@ -48626,16 +48626,16 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.498202070729238</v>
+        <v>-4.664459448053974</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.975694925404191</v>
+        <v>1.909191974474296</v>
       </c>
       <c r="F2047" t="n">
         <v>0.9059221628916482</v>
@@ -48649,16 +48649,16 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781701</v>
+        <v>3.666767386781703</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.516274579020849</v>
+        <v>-4.682531956345586</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.968465922087546</v>
+        <v>1.901962971157652</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9059221628916482</v>
@@ -48672,16 +48672,16 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.67006888808283</v>
+        <v>3.670068888082832</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.691381411597295</v>
+        <v>-4.857638788922031</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.858675102650435</v>
+        <v>1.79217215172054</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9059221628916482</v>
@@ -48695,16 +48695,16 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943582</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.660095391056839</v>
+        <v>-4.826352768381576</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.878212129863557</v>
+        <v>1.811709178933662</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9372081834321035</v>
@@ -48718,16 +48718,16 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677819</v>
+        <v>3.730590658677821</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.507069998943555</v>
+        <v>-4.673327376268292</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.038593286281775</v>
+        <v>1.972090335351881</v>
       </c>
       <c r="F2051" t="n">
         <v>1.090233575545388</v>
@@ -48741,16 +48741,16 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073878</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.535377312816825</v>
+        <v>-4.701634690141562</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.214736585640759</v>
+        <v>2.148233634710865</v>
       </c>
       <c r="F2052" t="n">
         <v>1.090233575545388</v>
@@ -48764,16 +48764,16 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903166</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.701970537930348</v>
+        <v>-4.868227915255084</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.117502246949432</v>
+        <v>2.050999296019538</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9236403504318653</v>
@@ -48787,16 +48787,16 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568378</v>
+        <v>3.70820270456838</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.678934744568782</v>
+        <v>-4.845192121893518</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.130392966955776</v>
+        <v>2.063890016025882</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9236403504318653</v>
@@ -48810,16 +48810,16 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682201</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.649688764113085</v>
+        <v>-4.815946141437822</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.13970941426155</v>
+        <v>2.073206463331656</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9236403504318653</v>
@@ -48833,16 +48833,16 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539103</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.756614311990936</v>
+        <v>-4.922871689315673</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.094232434268045</v>
+        <v>2.027729483338151</v>
       </c>
       <c r="F2056" t="n">
         <v>0.816714802554014</v>
@@ -48856,16 +48856,16 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983733</v>
+        <v>3.689962785983735</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.901632870498185</v>
+        <v>-5.067890247822922</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.03765381300838</v>
+        <v>1.971150862078485</v>
       </c>
       <c r="F2057" t="n">
         <v>0.6716962440467654</v>
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969747</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.019974636282902</v>
+        <v>-5.018189459049233</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.090248345952246</v>
+        <v>2.090962416845714</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7525075183161191</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.508023994344947</v>
+        <v>4.550099135768826</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073534</v>
+        <v>3.714899237073537</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.07138505860361</v>
+        <v>-5.069599881369941</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.067469874149901</v>
+        <v>2.068183945043369</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7525075183161191</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.505809691470886</v>
+        <v>4.547884832894765</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720064</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.150804509811362</v>
+        <v>-5.149019332577693</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.03560522174109</v>
+        <v>2.036319292634558</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7525075183161191</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.505712819545176</v>
+        <v>4.547787960969054</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581131</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.24626750772858</v>
+        <v>-5.24448233049491</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.997413916132247</v>
+        <v>1.998127987025714</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6823822826096555</v>
+        <v>0.7525075183161191</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.505706713103219</v>
+        <v>4.547781854527098</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500733</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.286287505772363</v>
+        <v>-5.284502328538694</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.979502313477344</v>
+        <v>1.980216384370812</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.7124875202723353</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.479791110839559</v>
+        <v>4.521866252263438</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.341656667904557</v>
+        <v>-5.339871490670888</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.963088466372193</v>
+        <v>1.963802537265661</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6423622845658716</v>
+        <v>0.7124875202723353</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.485524928587286</v>
+        <v>4.527600070011164</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396012</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.387094447735384</v>
+        <v>-5.385309270501715</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.944451717782795</v>
+        <v>1.945165788676263</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6696425295941757</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.459356297523323</v>
+        <v>4.501431438947201</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396421</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.298887613587806</v>
+        <v>-5.297102436354137</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.999608844292145</v>
+        <v>2.000322915185613</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6696425295941757</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.479230690373642</v>
+        <v>4.521305831797521</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299172</v>
+        <v>3.794507029299174</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.192852618382497</v>
+        <v>-5.191067441148827</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.025723542898997</v>
+        <v>2.026437613792465</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6696425295941757</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.462931390898371</v>
+        <v>4.505006532322248</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590406</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.009640955249401</v>
+        <v>-5.007855778015732</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.101439157616281</v>
+        <v>2.102153228509748</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.599517293887712</v>
+        <v>0.6696425295941757</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.465362340362416</v>
+        <v>4.507437481786294</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.93791950823555</v>
+        <v>-4.936134331001881</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.095918922269711</v>
+        <v>2.096632993163178</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6712387409015627</v>
+        <v>0.7413639766080263</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.474186394418616</v>
+        <v>4.516261535842494</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676846</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.915546482627844</v>
+        <v>-4.913761305394175</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.051783878433964</v>
+        <v>2.052497949327432</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6824944920144642</v>
+        <v>0.7526197277209279</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.427855591007528</v>
+        <v>4.469930732431406</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739461</v>
+        <v>3.715627631739464</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.948562778538589</v>
+        <v>-4.900450698970863</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.223775564955022</v>
+        <v>2.243020396782113</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6130571153477127</v>
+        <v>0.7593924682514022</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.571391369892833</v>
+        <v>4.659192581635047</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.71378272216641</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.93703514288898</v>
+        <v>-4.888923063321254</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.220307845043115</v>
+        <v>2.239552676870205</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6720577735490751</v>
+        <v>0.8183931264527646</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.598712990641899</v>
+        <v>4.686514202384113</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519029</v>
+        <v>3.717170884519031</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.034376644231349</v>
+        <v>-4.986264564663623</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.185039357027956</v>
+        <v>2.204284188855046</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6276375913835868</v>
+        <v>0.7739729442872763</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.575728993864395</v>
+        <v>4.663530205606609</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710415</v>
+        <v>3.705221264710417</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.120232673571316</v>
+        <v>-5.072120594003589</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.151948027484807</v>
+        <v>2.171192859311898</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5852615221574518</v>
+        <v>0.7315968750611412</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.551554434521552</v>
+        <v>4.639355646263766</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893112</v>
+        <v>3.691855684893114</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.129069470987435</v>
+        <v>-5.080957391419709</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.130832510338861</v>
+        <v>2.150077342165952</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.577819349516101</v>
+        <v>0.7241547024197905</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.529508332757244</v>
+        <v>4.617309544499457</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950186</v>
+        <v>3.715564596950188</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.220452033552894</v>
+        <v>-5.172339953985167</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.104443996357727</v>
+        <v>2.123688828184818</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4864367869506428</v>
+        <v>0.6327721398543322</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.484843306263018</v>
+        <v>4.572644518005232</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171922</v>
+        <v>3.673998560171924</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.208745315565888</v>
+        <v>-5.160633235998161</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.211254941376798</v>
+        <v>2.230499773203888</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4981435049376493</v>
+        <v>0.6444788578413386</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.59399559487949</v>
+        <v>4.681796806621704</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692298</v>
+        <v>3.682496284692296</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.109081811482225</v>
+        <v>-5.060969731914499</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.254152681741667</v>
+        <v>2.273397513568758</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5613305881413357</v>
+        <v>0.7076659410450251</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.634940183533106</v>
+        <v>4.72274139527532</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.788030820012067</v>
+        <v>3.892708793850364</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.700328743050276</v>
+        <v>4.568555758418031</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.109081811482225</v>
+        <v>-5.060969731914499</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.254152681741667</v>
+        <v>2.273397513568758</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5613305881413357</v>
+        <v>0.7076659410450251</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.693392540036644</v>
+        <v>4.561619555404399</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>43.7%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>104.6%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>145.2%</t>
+          <t>117.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-50.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.1%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.8%</t>
+          <t>422.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-667.7%</t>
+          <t>-689.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.9%</t>
+          <t>-158.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.0%</t>
+          <t>589.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-305.1%</t>
+          <t>-308.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.2%</t>
+          <t>-166.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.052666856440229</v>
+        <v>-4.034557818915463</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002289500459912</v>
+        <v>1.009533115469819</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.008293724801661</v>
+        <v>-3.990184687276894</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019901620550776</v>
+        <v>1.027145235560682</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.030774075660545</v>
+        <v>-4.012665038135779</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.005303274345813</v>
+        <v>1.012546889355719</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.98311834509949</v>
+        <v>-3.965009307574723</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.03074732359804</v>
+        <v>1.037990938607946</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.882600186600735</v>
+        <v>-3.864491149075969</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.075846960372266</v>
+        <v>1.083090575382173</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.866694857168382</v>
+        <v>-3.848585819643616</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.068963764621079</v>
+        <v>1.076207379630986</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.821856455559984</v>
+        <v>-3.803747418035218</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.090996827875067</v>
+        <v>1.098240442884974</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.841354911801993</v>
+        <v>-3.823245874277226</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.087358385009342</v>
+        <v>1.094602000019248</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.797152074716092</v>
+        <v>-3.779043037191326</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.110919122371539</v>
+        <v>1.118162737381446</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.804711740553139</v>
+        <v>-3.786602703028373</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.106305256505968</v>
+        <v>1.113548871515875</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284876</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.646420323013867</v>
+        <v>-3.6283112854891</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.220869588704717</v>
+        <v>1.228113203714623</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.438778319379391</v>
+        <v>-3.420669281854624</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.30236709475276</v>
+        <v>1.309610709762667</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.387746226656863</v>
+        <v>-3.369637189132096</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.317728160080041</v>
+        <v>1.324971775089948</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.322522045529657</v>
+        <v>-3.30441300800489</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.361005236623629</v>
+        <v>1.368248851633535</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.285095025458523</v>
+        <v>-3.266985987933757</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.371937016951362</v>
+        <v>1.379180631961269</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.305206681493231</v>
+        <v>-3.287097643968465</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.36514914686872</v>
+        <v>1.372392761878626</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.276793418393348</v>
+        <v>-3.258684380868581</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.537072223129884</v>
+        <v>1.54431583813979</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.202011157368335</v>
+        <v>-3.183902119843569</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.687098036757706</v>
+        <v>1.694341651767613</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.175927073104527</v>
+        <v>-3.157818035579761</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.689239646477088</v>
+        <v>1.696483261486995</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.088049159995407</v>
+        <v>-3.06994012247064</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.722584007304516</v>
+        <v>1.729827622314422</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.079156698602123</v>
+        <v>-3.061047661077357</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.743695397588621</v>
+        <v>1.750939012598527</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.247632815572001</v>
+        <v>-3.229523778047235</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.668159998205254</v>
+        <v>1.67540361321516</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.801376622942561</v>
+        <v>-2.783267585417795</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.827932172444891</v>
+        <v>1.835175787454798</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.778655519259408</v>
+        <v>-2.760546481734642</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.827684636415057</v>
+        <v>1.834928251424963</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.907857332553451</v>
+        <v>-2.889748295028685</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.934910036948609</v>
+        <v>1.942153651958515</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.933731731027477</v>
+        <v>-2.91562269350271</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.961638100052645</v>
+        <v>1.968881715062552</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.926677040812303</v>
+        <v>-2.917247192576625</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.96113533212826</v>
+        <v>1.964907271422531</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>0.9923273608042997</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.727558989249508</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.899725816485815</v>
+        <v>-2.890295968250137</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.981921975503597</v>
+        <v>1.985693914797868</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.007207706832019</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.746493350510881</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.921270044316602</v>
+        <v>-2.911840196080925</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.157407416516241</v>
+        <v>2.161179355810512</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.007207706832019</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.930596482655841</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.943678162121474</v>
+        <v>-2.934248313885797</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.140560864297286</v>
+        <v>2.144332803591557</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.007207706832019</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.922713177558834</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.971902397699075</v>
+        <v>-2.962472549463397</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.131325169615883</v>
+        <v>2.135097108910154</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.025184459283327</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.935553228579256</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.981343323587605</v>
+        <v>-2.971913475351927</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.183802516982318</v>
+        <v>2.18757445627659</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.147611576826719</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.065263216827139</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.070219954756078</v>
+        <v>-3.017661742180871</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.15114295906023</v>
+        <v>2.172166244090312</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.067414134947334</v>
+        <v>1.101863309997774</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.020035846244808</v>
+        <v>4.040705351275073</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.146549932356984</v>
+        <v>-3.093991719781777</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.118722780913642</v>
+        <v>2.139746065943725</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.067414134947334</v>
+        <v>1.101863309997774</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.018147659138584</v>
+        <v>4.038817164168848</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.240213877034526</v>
+        <v>-3.187655664459319</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.076077432645488</v>
+        <v>2.097100717675571</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9737501902697926</v>
+        <v>1.008199365320233</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.956769521934921</v>
+        <v>3.977439026965186</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.401782302561781</v>
+        <v>-3.349224089986574</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.009884072644738</v>
+        <v>2.030907357674821</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8814164415223537</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.879133777866346</v>
+        <v>3.89980328289661</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.5100829644319</v>
+        <v>-3.457524751856693</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.979637214762609</v>
+        <v>2.000660499792692</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8469672664719132</v>
+        <v>0.8814164415223537</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.892207184732265</v>
+        <v>3.912876689762529</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.603230435735267</v>
+        <v>-3.55067222316006</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.934383423024203</v>
+        <v>1.955406708054285</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7241380551893805</v>
+        <v>0.7585872302398209</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.810514854745685</v>
+        <v>3.831184359775949</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.63113122284474</v>
+        <v>-3.578573010269533</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.921747149307415</v>
+        <v>1.942770434337498</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6895411310464457</v>
+        <v>0.7239903060968861</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.788280741386926</v>
+        <v>3.80895024641719</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.753657325547634</v>
+        <v>-3.701099112972427</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.869501152203457</v>
+        <v>1.890524437233539</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5670150283435518</v>
+        <v>0.6014642033939922</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.711529523742389</v>
+        <v>3.732199028772653</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.984171821733223</v>
+        <v>-3.931613609158015</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.844001313319725</v>
+        <v>1.865024598349808</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3365005321579631</v>
+        <v>0.3709497072084035</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.639926785621539</v>
+        <v>3.660596290651803</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.332916906957666</v>
+        <v>-4.280358694382459</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.844814998231794</v>
+        <v>1.865838283261877</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2622017532895057</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.714989732272048</v>
+        <v>3.735659237302312</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237093</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.486903324733807</v>
+        <v>-4.434345112158599</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.852200700266978</v>
+        <v>1.873223985297061</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2622017532895057</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.783970001417687</v>
+        <v>3.804639506447951</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.436381420906141</v>
+        <v>-4.383823208330933</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.858460663918165</v>
+        <v>1.879483948948248</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2622017532895057</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.770021203537808</v>
+        <v>3.790690708568072</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.688856574913865</v>
+        <v>-4.636298362338658</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.769341091370489</v>
+        <v>1.790364376400572</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2622017532895057</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.781891692593222</v>
+        <v>3.802561197623486</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.981752331393277</v>
+        <v>-4.92919411881807</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.653393323297668</v>
+        <v>1.674416608327751</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2277525782390653</v>
+        <v>0.2622017532895057</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.783102227112166</v>
+        <v>3.80377173214243</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.168416459528085</v>
+        <v>-5.115858246952878</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.582849414271066</v>
+        <v>1.603872699301149</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2010136074145054</v>
+        <v>0.2354627824649458</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.771180586844751</v>
+        <v>3.791850091875016</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.314437146442048</v>
+        <v>-5.26187893386684</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.519518992241671</v>
+        <v>1.540542277271754</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2263796906710888</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.760808584504626</v>
+        <v>3.781478089534891</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.406151155551633</v>
+        <v>-5.353592942976425</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.645037445296881</v>
+        <v>1.666060730326964</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1919305156206484</v>
+        <v>0.2263796906710888</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923012641203671</v>
+        <v>3.943682146233935</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.437802814611603</v>
+        <v>-5.385244602036394</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.627223419636707</v>
+        <v>1.648246704666791</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1867620583762082</v>
+        <v>0.2212112334266486</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.914758204820821</v>
+        <v>3.935427709851085</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.519737632880486</v>
+        <v>-5.467179420305277</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.604678909897645</v>
+        <v>1.625702194927729</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.176827312789128</v>
+        <v>0.2112764878395684</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.919026775037064</v>
+        <v>3.939696280067328</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.621713755128893</v>
+        <v>-5.569155542553685</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.572814099454185</v>
+        <v>1.593837384484268</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.07485119054072042</v>
+        <v>0.1093003655911609</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.866766740143922</v>
+        <v>3.887436245174186</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.511707471651672</v>
+        <v>-5.459149259076463</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.608969500089248</v>
+        <v>1.629992785119332</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.09805576245799563</v>
+        <v>0.1325049375084361</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.872842370538462</v>
+        <v>3.893511875568727</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818522</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.368647895910746</v>
+        <v>-5.316089683335537</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.670443341107593</v>
+        <v>1.691466626137677</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1060691890479749</v>
+        <v>0.1405183640984153</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.881900437214424</v>
+        <v>3.902569942244688</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.067201170438908</v>
+        <v>-5.0146429578637</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.798282914178864</v>
+        <v>1.819306199208948</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4419650895702526</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.070029355380062</v>
+        <v>4.090698860410327</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.091791414674092</v>
+        <v>-5.039233202098884</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.789417994237501</v>
+        <v>1.810441279267585</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4419650895702526</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.071000533132773</v>
+        <v>4.091670038163037</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.040753038667572</v>
+        <v>-4.988194826092363</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.810676249019865</v>
+        <v>1.831699534049948</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4075159145198122</v>
+        <v>0.4419650895702526</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.071843437512529</v>
+        <v>4.092512942542792</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.999613743800941</v>
+        <v>-4.947055531225732</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.846170065840663</v>
+        <v>1.867193350870746</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.448655209386443</v>
+        <v>0.4831043844368834</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.115565113306652</v>
+        <v>4.136234618336917</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.902978831782301</v>
+        <v>-4.850420619207092</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.701008026772053</v>
+        <v>1.722031311802137</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5452901214050829</v>
+        <v>0.5797392964555234</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.989730056641771</v>
+        <v>4.010399561672036</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.033559566313143</v>
+        <v>-4.981001353737935</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.65227777703368</v>
+        <v>1.673301062063764</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4147093868742404</v>
+        <v>0.4491585619246808</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.91488365999723</v>
+        <v>3.935553165027494</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.869063232122182</v>
+        <v>-4.816505019546973</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.702503129786148</v>
+        <v>1.723526414816231</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.6136548961156427</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.998008279587889</v>
+        <v>4.018677784618154</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.896433164806614</v>
+        <v>-4.843874952231405</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.690742867148805</v>
+        <v>1.711766152178888</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5792057210652023</v>
+        <v>0.6136548961156427</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.997195990024319</v>
+        <v>4.017865495054584</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.906818359696503</v>
+        <v>-4.854260147121295</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.696457568317921</v>
+        <v>1.717480853348005</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.568820526175313</v>
+        <v>0.6032697012257534</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.000833652215458</v>
+        <v>4.021503157245722</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.925406518418728</v>
+        <v>-4.87284830584352</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.759859310605457</v>
+        <v>1.78088259563554</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5502323674530876</v>
+        <v>0.5846815425035281</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.060517762758548</v>
+        <v>4.081187267788812</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.925705065114764</v>
+        <v>-4.873146852539556</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.756608902745341</v>
+        <v>1.777632187775424</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5499338207570517</v>
+        <v>0.5843829958074922</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.057207645559225</v>
+        <v>4.077877150589489</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.824881931424336</v>
+        <v>-4.772323718849128</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.801469051160903</v>
+        <v>1.822492336190986</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5623980362414055</v>
+        <v>0.596847211291846</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.069217069789229</v>
+        <v>4.089886574819492</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.634100570671929</v>
+        <v>-4.581542358096721</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.877910848940409</v>
+        <v>1.898934133970493</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7531793969938129</v>
+        <v>0.7876285720442534</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.183815139719216</v>
+        <v>4.20448464474948</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.527137212822508</v>
+        <v>-4.474579000247299</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.900533037817774</v>
+        <v>1.921556322847858</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8116440049536143</v>
+        <v>0.8460931800040549</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.198730750232693</v>
+        <v>4.219400255262958</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.471806624920745</v>
+        <v>-4.419248412345537</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.957632209590538</v>
+        <v>1.978655494620621</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8669745928553765</v>
+        <v>0.901423767905817</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.266896039585809</v>
+        <v>4.287565544616074</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.459752498007783</v>
+        <v>-4.407194285432574</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.956140428257161</v>
+        <v>1.977163713287244</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8790287197683393</v>
+        <v>0.9134778948187798</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.267815083635025</v>
+        <v>4.288484588665289</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.500907617576003</v>
+        <v>-4.448349405000795</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.941559010614008</v>
+        <v>1.962582295644092</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8378736002001184</v>
+        <v>0.8723227752505589</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.245002642078228</v>
+        <v>4.265672147108492</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.432859054884474</v>
+        <v>-4.380300842309265</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.981629461568502</v>
+        <v>2.002652746598586</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9403713379420887</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.298682805571028</v>
+        <v>4.319352310601293</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.664459448053974</v>
+        <v>-4.611901235478766</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.909191974474296</v>
+        <v>1.93021525950438</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9403713379420887</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.318885475744622</v>
+        <v>4.339554980774887</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781703</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.682531956345586</v>
+        <v>-4.629973743770377</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901962971157652</v>
+        <v>1.922986256187735</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9403713379420887</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318885475744622</v>
+        <v>4.339554980774887</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.857638788922031</v>
+        <v>-4.805080576346823</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.79217215172054</v>
+        <v>1.813195436750624</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9059221628916482</v>
+        <v>0.9403713379420887</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.279137389338089</v>
+        <v>4.299806894368354</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.826352768381576</v>
+        <v>-4.773794555806368</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.811709178933662</v>
+        <v>1.832732463963746</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9372081834321035</v>
+        <v>0.9716573584825441</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.304931620659302</v>
+        <v>4.325601125689567</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.673327376268292</v>
+        <v>-4.620769163693083</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.972090335351881</v>
+        <v>1.993113620381964</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.090233575545388</v>
+        <v>1.124682750595828</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.495917855500178</v>
+        <v>4.516587360530441</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.701634690141562</v>
+        <v>-4.649076477566354</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.148233634710865</v>
+        <v>2.169256919740948</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.090233575545388</v>
+        <v>1.124682750595828</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.683384080408469</v>
+        <v>4.704053585438734</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.868227915255084</v>
+        <v>-4.815669702679876</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.050999296019538</v>
+        <v>2.072022581049621</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9580895254823056</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.552831096694439</v>
+        <v>4.573500601724702</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.845192121893518</v>
+        <v>-4.79263390931831</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.063890016025882</v>
+        <v>2.084913301055965</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9580895254823056</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.556507499356156</v>
+        <v>4.57717700438642</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.815946141437822</v>
+        <v>-4.763387928862613</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.073206463331656</v>
+        <v>2.094229748361739</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9236403504318653</v>
+        <v>0.9580895254823056</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.554125554479652</v>
+        <v>4.574795059509915</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.922871689315673</v>
+        <v>-4.870313476740464</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.027729483338151</v>
+        <v>2.048752768368234</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.816714802554014</v>
+        <v>0.8511639776044543</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.487263464910575</v>
+        <v>4.50793296994084</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.067890247822922</v>
+        <v>-5.015332035247713</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.971150862078485</v>
+        <v>1.992174147108569</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6716962440467654</v>
+        <v>0.7061454190972057</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.40168113194946</v>
+        <v>4.422350636979725</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969747</v>
+        <v>3.711872614969746</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.018189459049233</v>
+        <v>-5.133673801032431</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.090962416845714</v>
+        <v>2.044768680052435</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7525075183161191</v>
+        <v>0.7168314576600958</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.550099135768826</v>
+        <v>4.528693499375212</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073537</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.069599881369941</v>
+        <v>-5.185084223353138</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.068183945043369</v>
+        <v>2.02199020825009</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7525075183161191</v>
+        <v>0.7168314576600958</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.547884832894765</v>
+        <v>4.526479196501151</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720064</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.149019332577693</v>
+        <v>-5.26450367456089</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.036319292634558</v>
+        <v>1.990125555841279</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7525075183161191</v>
+        <v>0.7168314576600958</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.547787960969054</v>
+        <v>4.52638232457544</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581131</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.24448233049491</v>
+        <v>-5.359966672478108</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.998127987025714</v>
+        <v>1.951934250232435</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7525075183161191</v>
+        <v>0.7168314576600958</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.547781854527098</v>
+        <v>4.526376218133484</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500733</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.284502328538694</v>
+        <v>-5.399986670521892</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.980216384370812</v>
+        <v>1.934022647577533</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7124875202723353</v>
+        <v>0.676811459616312</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.521866252263438</v>
+        <v>4.500460615869824</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.339871490670888</v>
+        <v>-5.455355832654085</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.963802537265661</v>
+        <v>1.917608800472382</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7124875202723353</v>
+        <v>0.676811459616312</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.527600070011164</v>
+        <v>4.506194433617551</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396012</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.385309270501715</v>
+        <v>-5.500793612484912</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.945165788676263</v>
+        <v>1.898972051882984</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6696425295941757</v>
+        <v>0.6339664689381523</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.501431438947201</v>
+        <v>4.480025802553588</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396421</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.297102436354137</v>
+        <v>-5.412586778337334</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.000322915185613</v>
+        <v>1.954129178392334</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6696425295941757</v>
+        <v>0.6339664689381523</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.521305831797521</v>
+        <v>4.499900195403907</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299174</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.191067441148827</v>
+        <v>-5.306551783132025</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.026437613792465</v>
+        <v>1.980243876999185</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6696425295941757</v>
+        <v>0.6339664689381523</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.505006532322248</v>
+        <v>4.483600895928634</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590406</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.007855778015732</v>
+        <v>-5.12334011999893</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.102153228509748</v>
+        <v>2.055959491716469</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6696425295941757</v>
+        <v>0.6339664689381523</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.507437481786294</v>
+        <v>4.48603184539268</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146284</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.936134331001881</v>
+        <v>-5.051618672985079</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.096632993163178</v>
+        <v>2.050439256369899</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7413639766080263</v>
+        <v>0.705687915952003</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.516261535842494</v>
+        <v>4.49485589944888</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676846</v>
+        <v>3.723809890676844</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.913761305394175</v>
+        <v>-5.029245647377373</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.052497949327432</v>
+        <v>2.006304212534153</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7526197277209279</v>
+        <v>0.7169436670649045</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.469930732431406</v>
+        <v>4.448525096037792</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739464</v>
+        <v>3.71562763173946</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.900450698970863</v>
+        <v>-5.062261943288117</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.243020396782113</v>
+        <v>2.178295899055211</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.7593924682514022</v>
+        <v>0.647506290398153</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.659192581635047</v>
+        <v>4.592060874923097</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.71378272216641</v>
+        <v>3.713782722166406</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.888923063321254</v>
+        <v>-5.050734307638509</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.239552676870205</v>
+        <v>2.174828179143303</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.8183931264527646</v>
+        <v>0.7065069485995155</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.686514202384113</v>
+        <v>4.619382495672164</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519031</v>
+        <v>3.717170884519026</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.986264564663623</v>
+        <v>-5.148075808980877</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.204284188855046</v>
+        <v>2.139559691128144</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.7739729442872763</v>
+        <v>0.6620867664340271</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.663530205606609</v>
+        <v>4.596398498894659</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710417</v>
+        <v>3.705221264710413</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.072120594003589</v>
+        <v>-5.233931838320844</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.171192859311898</v>
+        <v>2.106468361584996</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.7315968750611412</v>
+        <v>0.6197106972078921</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.639355646263766</v>
+        <v>4.572223939551816</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893114</v>
+        <v>3.691855684893111</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.080957391419709</v>
+        <v>-5.242768635736963</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.150077342165952</v>
+        <v>2.08535284443905</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.7241547024197905</v>
+        <v>0.6122685245665414</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.617309544499457</v>
+        <v>4.550177837787508</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950188</v>
+        <v>3.715564596950184</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.172339953985167</v>
+        <v>-5.334151198302422</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.123688828184818</v>
+        <v>2.058964330457916</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6327721398543322</v>
+        <v>0.5208859620010831</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.572644518005232</v>
+        <v>4.505512811293282</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673998560171924</v>
+        <v>3.67399856017192</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.160633235998161</v>
+        <v>-5.322444480315416</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.230499773203888</v>
+        <v>2.165775275476987</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.6444788578413386</v>
+        <v>0.5325926799880895</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.681796806621704</v>
+        <v>4.614665099909754</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692296</v>
+        <v>3.682496284692295</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.060969731914499</v>
+        <v>-5.222780976231753</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.273397513568758</v>
+        <v>2.208673015841856</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.7076659410450251</v>
+        <v>0.5957797631917759</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.72274139527532</v>
+        <v>4.655609688563371</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.892708793850364</v>
+        <v>3.717443083018095</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.568555758418031</v>
+        <v>4.288378620122077</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.060969731914499</v>
+        <v>-5.273867641368104</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.273397513568758</v>
+        <v>2.178475139261088</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.7076659410450251</v>
+        <v>0.573035748458811</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.561619555404399</v>
+        <v>4.632200069197363</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240905.xlsx
+++ b/tame_output/ON/bt/strategyON_20240905.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.6%</t>
+          <t>422.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.0%</t>
+          <t>-688.4%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.4%</t>
+          <t>-158.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-162.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>85.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
     </row>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.034557818915463</v>
+        <v>-4.052666856440229</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.009533115469819</v>
+        <v>1.002289500459912</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316248</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.990184687276894</v>
+        <v>-4.008293724801661</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.027145235560682</v>
+        <v>1.019901620550776</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105967</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.012665038135779</v>
+        <v>-4.030774075660545</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.012546889355719</v>
+        <v>1.005303274345813</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.965009307574723</v>
+        <v>-3.98311834509949</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.037990938607946</v>
+        <v>1.03074732359804</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.864491149075969</v>
+        <v>-3.882600186600735</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.083090575382173</v>
+        <v>1.075846960372266</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.848585819643616</v>
+        <v>-3.866694857168382</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.076207379630986</v>
+        <v>1.068963764621079</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.803747418035218</v>
+        <v>-3.821856455559984</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.098240442884974</v>
+        <v>1.090996827875067</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.823245874277226</v>
+        <v>-3.841354911801993</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.094602000019248</v>
+        <v>1.087358385009342</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.779043037191326</v>
+        <v>-3.797152074716092</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.118162737381446</v>
+        <v>1.110919122371539</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.786602703028373</v>
+        <v>-3.804711740553139</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.113548871515875</v>
+        <v>1.106305256505968</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.6283112854891</v>
+        <v>-3.646420323013867</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.228113203714623</v>
+        <v>1.220869588704717</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.420669281854624</v>
+        <v>-3.438778319379391</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.309610709762667</v>
+        <v>1.30236709475276</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.369637189132096</v>
+        <v>-3.387746226656863</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.324971775089948</v>
+        <v>1.317728160080041</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.30441300800489</v>
+        <v>-3.322522045529657</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.368248851633535</v>
+        <v>1.361005236623629</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.266985987933757</v>
+        <v>-3.285095025458523</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.379180631961269</v>
+        <v>1.371937016951362</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.287097643968465</v>
+        <v>-3.305206681493231</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.372392761878626</v>
+        <v>1.36514914686872</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.258684380868581</v>
+        <v>-3.276793418393348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.54431583813979</v>
+        <v>1.537072223129884</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.183902119843569</v>
+        <v>-3.202011157368335</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.694341651767613</v>
+        <v>1.687098036757706</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998756</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.157818035579761</v>
+        <v>-3.175927073104527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.696483261486995</v>
+        <v>1.689239646477088</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.06994012247064</v>
+        <v>-3.088049159995407</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.729827622314422</v>
+        <v>1.722584007304516</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959858</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.061047661077357</v>
+        <v>-3.079156698602123</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.750939012598527</v>
+        <v>1.743695397588621</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.229523778047235</v>
+        <v>-3.247632815572001</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.67540361321516</v>
+        <v>1.668159998205254</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.783267585417795</v>
+        <v>-2.801376622942561</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.835175787454798</v>
+        <v>1.827932172444891</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.760546481734642</v>
+        <v>-2.778655519259408</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.834928251424963</v>
+        <v>1.827684636415057</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.889748295028685</v>
+        <v>-2.907857332553451</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.942153651958515</v>
+        <v>1.934910036948609</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.91562269350271</v>
+        <v>-2.933731731027477</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.968881715062552</v>
+        <v>1.961638100052645</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799965</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.917247192576625</v>
+        <v>-2.926677040812303</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.964907271422531</v>
+        <v>1.96113533212826</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9923273608042997</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.727558989249508</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.890295968250137</v>
+        <v>-2.899725816485815</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.985693914797868</v>
+        <v>1.981921975503597</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.007207706832019</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.746493350510881</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784109</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.911840196080925</v>
+        <v>-2.921270044316602</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.161179355810512</v>
+        <v>2.157407416516241</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.007207706832019</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.930596482655841</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714427</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.934248313885797</v>
+        <v>-2.943678162121474</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.144332803591557</v>
+        <v>2.140560864297286</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.007207706832019</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.922713177558834</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.962472549463397</v>
+        <v>-2.971902397699075</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.135097108910154</v>
+        <v>2.131325169615883</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.025184459283327</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.935553228579256</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.971913475351927</v>
+        <v>-2.981343323587605</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.18757445627659</v>
+        <v>2.183802516982318</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.147611576826719</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.065263216827139</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.017661742180871</v>
+        <v>-3.070219954756078</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.172166244090312</v>
+        <v>2.15114295906023</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.101863309997774</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.040705351275073</v>
+        <v>4.020035846244808</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.093991719781777</v>
+        <v>-3.146549932356984</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.139746065943725</v>
+        <v>2.118722780913642</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.101863309997774</v>
+        <v>1.067414134947334</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.038817164168848</v>
+        <v>4.018147659138584</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.187655664459319</v>
+        <v>-3.194601611807838</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.097100717675571</v>
+        <v>2.094322338736163</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.008199365320233</v>
+        <v>1.01936245549648</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.977439026965186</v>
+        <v>3.984136881070934</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343067</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.349224089986574</v>
+        <v>-3.356170037335093</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.030907357674821</v>
+        <v>2.028128978735413</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8814164415223537</v>
+        <v>0.8925795316986006</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.89980328289661</v>
+        <v>3.906501137002358</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.75459613538935</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.457524751856693</v>
+        <v>-3.464470699205213</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.000660499792692</v>
+        <v>1.997882120853284</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8814164415223537</v>
+        <v>0.8925795316986006</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.912876689762529</v>
+        <v>3.919574543868277</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.55067222316006</v>
+        <v>-3.557618170508579</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.955406708054285</v>
+        <v>1.952628329114877</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7585872302398209</v>
+        <v>0.7697503204160678</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.831184359775949</v>
+        <v>3.837882213881698</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.578573010269533</v>
+        <v>-3.585518957618052</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.942770434337498</v>
+        <v>1.93999205539809</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7239903060968861</v>
+        <v>0.735153396273133</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.80895024641719</v>
+        <v>3.815648100522939</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787389</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.701099112972427</v>
+        <v>-3.708045060320946</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.890524437233539</v>
+        <v>1.887746058294131</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6014642033939922</v>
+        <v>0.6126272935702392</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.732199028772653</v>
+        <v>3.738896882878401</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.931613609158015</v>
+        <v>-3.938559556506535</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.865024598349808</v>
+        <v>1.8622462194104</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3709497072084035</v>
+        <v>0.3821127973846504</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.660596290651803</v>
+        <v>3.667294144757551</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.280358694382459</v>
+        <v>-4.287304641730978</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.865838283261877</v>
+        <v>1.863059904322469</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2622017532895057</v>
+        <v>0.2733648434657526</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.735659237302312</v>
+        <v>3.74235709140806</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.434345112158599</v>
+        <v>-4.441291059507119</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.873223985297061</v>
+        <v>1.870445606357653</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2622017532895057</v>
+        <v>0.2733648434657526</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.804639506447951</v>
+        <v>3.8113373605537</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.383823208330933</v>
+        <v>-4.390769155679453</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.879483948948248</v>
+        <v>1.87670557000884</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2622017532895057</v>
+        <v>0.2733648434657526</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.790690708568072</v>
+        <v>3.797388562673821</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.636298362338658</v>
+        <v>-4.643244309687177</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.790364376400572</v>
+        <v>1.787585997461165</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2622017532895057</v>
+        <v>0.2733648434657526</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.802561197623486</v>
+        <v>3.809259051729235</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.92919411881807</v>
+        <v>-4.93614006616659</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.674416608327751</v>
+        <v>1.671638229388343</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2622017532895057</v>
+        <v>0.2733648434657526</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.80377173214243</v>
+        <v>3.810469586248178</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.115858246952878</v>
+        <v>-5.122804194301398</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.603872699301149</v>
+        <v>1.601094320361741</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2354627824649458</v>
+        <v>0.2466258726411927</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.791850091875016</v>
+        <v>3.798547945980764</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.26187893386684</v>
+        <v>-5.26882488121536</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.540542277271754</v>
+        <v>1.537763898332346</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2263796906710888</v>
+        <v>0.2375427808473358</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.781478089534891</v>
+        <v>3.788175943640639</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.353592942976425</v>
+        <v>-5.360538890324944</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.666060730326964</v>
+        <v>1.663282351387557</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2263796906710888</v>
+        <v>0.2375427808473358</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.943682146233935</v>
+        <v>3.950380000339683</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.385244602036394</v>
+        <v>-5.392190549384914</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.648246704666791</v>
+        <v>1.645468325727383</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2212112334266486</v>
+        <v>0.2323743236028956</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.935427709851085</v>
+        <v>3.942125563956833</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.467179420305277</v>
+        <v>-5.474125367653797</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.625702194927729</v>
+        <v>1.622923815988321</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2112764878395684</v>
+        <v>0.2224395780158154</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.939696280067328</v>
+        <v>3.946394134173076</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.569155542553685</v>
+        <v>-5.576101489902205</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.593837384484268</v>
+        <v>1.59105900554486</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1093003655911609</v>
+        <v>0.1204634557674078</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.887436245174186</v>
+        <v>3.894134099279934</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.459149259076463</v>
+        <v>-5.466095206424983</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.629992785119332</v>
+        <v>1.627214406179924</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1325049375084361</v>
+        <v>0.143668027684683</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.893511875568727</v>
+        <v>3.900209729674474</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818522</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.316089683335537</v>
+        <v>-5.323035630684057</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.691466626137677</v>
+        <v>1.688688247198269</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1405183640984153</v>
+        <v>0.1516814542746623</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.902569942244688</v>
+        <v>3.909267796350437</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.0146429578637</v>
+        <v>-5.021588905212219</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.819306199208948</v>
+        <v>1.81652782026954</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4419650895702526</v>
+        <v>0.4531281797464995</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.090698860410327</v>
+        <v>4.097396714516075</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.039233202098884</v>
+        <v>-5.046179149447403</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.810441279267585</v>
+        <v>1.807662900328177</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4419650895702526</v>
+        <v>0.4531281797464995</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.091670038163037</v>
+        <v>4.098367892268786</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.988194826092363</v>
+        <v>-4.995140773440883</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.831699534049948</v>
+        <v>1.82892115511054</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4419650895702526</v>
+        <v>0.4531281797464995</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.092512942542792</v>
+        <v>4.099210796648541</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.947055531225732</v>
+        <v>-4.954001478574252</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.867193350870746</v>
+        <v>1.864414971931338</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4831043844368834</v>
+        <v>0.4942674746131304</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.136234618336917</v>
+        <v>4.142932472442665</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.825752932700479</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.850420619207092</v>
+        <v>-4.857366566555612</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.722031311802137</v>
+        <v>1.719252932862729</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5797392964555234</v>
+        <v>0.5909023866317703</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.010399561672036</v>
+        <v>4.017097415777783</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.981001353737935</v>
+        <v>-4.987947301086455</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.673301062063764</v>
+        <v>1.670522683124356</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4491585619246808</v>
+        <v>0.4603216521009278</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.935553165027494</v>
+        <v>3.942251019133242</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.816505019546973</v>
+        <v>-4.823450966895493</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.723526414816231</v>
+        <v>1.720748035876823</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6136548961156427</v>
+        <v>0.6248179862918897</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.018677784618154</v>
+        <v>4.025375638723902</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.82103066007763</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.843874952231405</v>
+        <v>-4.850820899579925</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.711766152178888</v>
+        <v>1.70898777323948</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6136548961156427</v>
+        <v>0.6248179862918897</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.017865495054584</v>
+        <v>4.024563349160331</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147908</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.854260147121295</v>
+        <v>-4.861206094469814</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.717480853348005</v>
+        <v>1.714702474408597</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6032697012257534</v>
+        <v>0.6144327914020004</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.021503157245722</v>
+        <v>4.02820101135147</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.87284830584352</v>
+        <v>-4.879794253192039</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.78088259563554</v>
+        <v>1.778104216696132</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5846815425035281</v>
+        <v>0.5958446326797751</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.081187267788812</v>
+        <v>4.08788512189456</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.873146852539556</v>
+        <v>-4.880092799888075</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.777632187775424</v>
+        <v>1.774853808836016</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5843829958074922</v>
+        <v>0.5955460859837391</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.077877150589489</v>
+        <v>4.084575004695237</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108853</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.772323718849128</v>
+        <v>-4.779269666197647</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.822492336190986</v>
+        <v>1.819713957251579</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.596847211291846</v>
+        <v>0.608010301468093</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.089886574819492</v>
+        <v>4.096584428925241</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121462</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.581542358096721</v>
+        <v>-4.588488305445241</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.898934133970493</v>
+        <v>1.896155755031085</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7876285720442534</v>
+        <v>0.7987916622205004</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.20448464474948</v>
+        <v>4.211182498855228</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906075</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.474579000247299</v>
+        <v>-4.481524947595819</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.921556322847858</v>
+        <v>1.91877794390845</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8460931800040549</v>
+        <v>0.8572562701803018</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.219400255262958</v>
+        <v>4.226098109368706</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.419248412345537</v>
+        <v>-4.426194359694057</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.978655494620621</v>
+        <v>1.975877115681213</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.901423767905817</v>
+        <v>0.912586858082064</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.287565544616074</v>
+        <v>4.294263398721822</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.407194285432574</v>
+        <v>-4.414140232781094</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.977163713287244</v>
+        <v>1.974385334347836</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9134778948187798</v>
+        <v>0.9246409849950268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.288484588665289</v>
+        <v>4.295182442771037</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.448349405000795</v>
+        <v>-4.455295352349315</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.962582295644092</v>
+        <v>1.959803916704684</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8723227752505589</v>
+        <v>0.8834858654268058</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.265672147108492</v>
+        <v>4.272370001214241</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.380300842309265</v>
+        <v>-4.387246789657785</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.002652746598586</v>
+        <v>1.999874367659178</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9403713379420887</v>
+        <v>0.9515344281183357</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.319352310601293</v>
+        <v>4.326050164707041</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760311</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.611901235478766</v>
+        <v>-4.618847182827285</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.93021525950438</v>
+        <v>1.927436880564972</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9403713379420887</v>
+        <v>0.9515344281183357</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.339554980774887</v>
+        <v>4.346252834880636</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781707</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.629973743770377</v>
+        <v>-4.636919691118897</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.922986256187735</v>
+        <v>1.920207877248327</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9403713379420887</v>
+        <v>0.9515344281183357</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.339554980774887</v>
+        <v>4.346252834880636</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082832</v>
+        <v>3.670068888082836</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.805080576346823</v>
+        <v>-4.812026523695343</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.813195436750624</v>
+        <v>1.810417057811216</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9403713379420887</v>
+        <v>0.9515344281183357</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.299806894368354</v>
+        <v>4.306504748474102</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943588</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.773794555806368</v>
+        <v>-4.780740503154887</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.832732463963746</v>
+        <v>1.829954085024338</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9716573584825441</v>
+        <v>0.982820448658791</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.325601125689567</v>
+        <v>4.332298979795315</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677821</v>
+        <v>3.730590658677825</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.620769163693083</v>
+        <v>-4.627715111041603</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.993113620381964</v>
+        <v>1.990335241442556</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.124682750595828</v>
+        <v>1.135845840772075</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.516587360530441</v>
+        <v>4.52328521463619</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74129851807388</v>
+        <v>3.741298518073885</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.649076477566354</v>
+        <v>-4.656022424914873</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.169256919740948</v>
+        <v>2.16647854080154</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.124682750595828</v>
+        <v>1.135845840772075</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.704053585438734</v>
+        <v>4.710751439544482</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903166</v>
+        <v>3.69913580090317</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.815669702679876</v>
+        <v>-4.822615650028395</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.072022581049621</v>
+        <v>2.069244202110213</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9580895254823056</v>
+        <v>0.9692526156585528</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.573500601724702</v>
+        <v>4.580198455830451</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.70820270456838</v>
+        <v>3.708202704568383</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.79263390931831</v>
+        <v>-4.79957985666683</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.084913301055965</v>
+        <v>2.082134922116557</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9580895254823056</v>
+        <v>0.9692526156585528</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.57717700438642</v>
+        <v>4.583874858492169</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682201</v>
+        <v>3.740601586682205</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.763387928862613</v>
+        <v>-4.770333876211133</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.094229748361739</v>
+        <v>2.091451369422331</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9580895254823056</v>
+        <v>0.9692526156585528</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.574795059509915</v>
+        <v>4.581492913615664</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539108</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.870313476740464</v>
+        <v>-4.877259424088984</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.048752768368234</v>
+        <v>2.045974389428826</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8511639776044543</v>
+        <v>0.8623270677807015</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.50793296994084</v>
+        <v>4.514630824046588</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983735</v>
+        <v>3.689962785983738</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.015332035247713</v>
+        <v>-5.022277982596233</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.992174147108569</v>
+        <v>1.989395768169161</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7061454190972057</v>
+        <v>0.7173085092734529</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.422350636979725</v>
+        <v>4.429048491085473</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969746</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.133673801032431</v>
+        <v>-5.14061974838095</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.044768680052435</v>
+        <v>2.041990301113027</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7168314576600958</v>
+        <v>0.727994547836343</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.528693499375212</v>
+        <v>4.53539135348096</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.185084223353138</v>
+        <v>-5.192030170701658</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.02199020825009</v>
+        <v>2.019211829310682</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7168314576600958</v>
+        <v>0.727994547836343</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.526479196501151</v>
+        <v>4.533177050606898</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.704778134720066</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.26450367456089</v>
+        <v>-5.27144962190941</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.990125555841279</v>
+        <v>1.987347176901871</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7168314576600958</v>
+        <v>0.727994547836343</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.52638232457544</v>
+        <v>4.533080178681188</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581134</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.359966672478108</v>
+        <v>-5.366912619826627</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.951934250232435</v>
+        <v>1.949155871293028</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7168314576600958</v>
+        <v>0.727994547836343</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.526376218133484</v>
+        <v>4.533074072239232</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500736</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.399986670521892</v>
+        <v>-5.406932617870411</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.934022647577533</v>
+        <v>1.931244268638125</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.676811459616312</v>
+        <v>0.6879745497925591</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.500460615869824</v>
+        <v>4.507158469975572</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636271</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.455355832654085</v>
+        <v>-5.462301780002605</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.917608800472382</v>
+        <v>1.914830421532974</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.676811459616312</v>
+        <v>0.6879745497925591</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.506194433617551</v>
+        <v>4.512892287723298</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396014</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.500793612484912</v>
+        <v>-5.507739559833432</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.898972051882984</v>
+        <v>1.896193672943576</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6339664689381523</v>
+        <v>0.6451295591143995</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.480025802553588</v>
+        <v>4.486723656659336</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396423</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.412586778337334</v>
+        <v>-5.419532725685854</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.954129178392334</v>
+        <v>1.951350799452926</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6339664689381523</v>
+        <v>0.6451295591143995</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.499900195403907</v>
+        <v>4.506598049509655</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.306551783132025</v>
+        <v>-5.313497730480544</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.980243876999185</v>
+        <v>1.977465498059778</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6339664689381523</v>
+        <v>0.6451295591143995</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.483600895928634</v>
+        <v>4.490298750034383</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590407</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.12334011999893</v>
+        <v>-5.130286067347449</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.055959491716469</v>
+        <v>2.053181112777061</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6339664689381523</v>
+        <v>0.6451295591143995</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.48603184539268</v>
+        <v>4.492729699498429</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146286</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.051618672985079</v>
+        <v>-5.058564620333598</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.050439256369899</v>
+        <v>2.047660877430491</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.705687915952003</v>
+        <v>0.7168510061282501</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.49485589944888</v>
+        <v>4.501553753554628</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676844</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.029245647377373</v>
+        <v>-5.036191594725892</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.006304212534153</v>
+        <v>2.003525833594745</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7169436670649045</v>
+        <v>0.7281067572411517</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.448525096037792</v>
+        <v>4.455222950143541</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.71562763173946</v>
+        <v>3.715627631739465</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.062261943288117</v>
+        <v>-5.069207890636637</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.178295899055211</v>
+        <v>2.175517520115803</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.647506290398153</v>
+        <v>0.6586693805744002</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.592060874923097</v>
+        <v>4.598758729028845</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166406</v>
+        <v>3.713782722166411</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.050734307638509</v>
+        <v>-5.057680254987028</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.174828179143303</v>
+        <v>2.172049800203895</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.7065069485995155</v>
+        <v>0.7176700387757626</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.619382495672164</v>
+        <v>4.626080349777911</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519026</v>
+        <v>3.717170884519032</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.148075808980877</v>
+        <v>-5.155021756329397</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.139559691128144</v>
+        <v>2.136781312188737</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6620867664340271</v>
+        <v>0.6732498566102743</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.596398498894659</v>
+        <v>4.603096353000407</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710413</v>
+        <v>3.705221264710418</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.233931838320844</v>
+        <v>-5.240877785669364</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.106468361584996</v>
+        <v>2.103689982645588</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6197106972078921</v>
+        <v>0.6308737873841392</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.572223939551816</v>
+        <v>4.578921793657565</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893111</v>
+        <v>3.691855684893116</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.242768635736963</v>
+        <v>-5.249714583085483</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.08535284443905</v>
+        <v>2.082574465499642</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6122685245665414</v>
+        <v>0.6234316147427885</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.550177837787508</v>
+        <v>4.556875691893256</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715564596950184</v>
+        <v>3.715564596950189</v>
       </c>
       <c r="C2075" t="n">
         <v>4.192981234092632</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.334151198302422</v>
+        <v>-5.341097145650942</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.058964330457916</v>
+        <v>2.056185951518508</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5208859620010831</v>
+        <v>0.5320490521773302</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.505512811293282</v>
+        <v>4.512210665399031</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.67399856017192</v>
+        <v>3.673998560171925</v>
       </c>
       <c r="C2076" t="n">
         <v>4.2951094919169</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.322444480315416</v>
+        <v>-5.320607578824223</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.165775275476987</v>
+        <v>2.166510036073463</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5325926799880895</v>
+        <v>0.5525386190040491</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.614665099909754</v>
+        <v>4.62663266331933</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682496284692295</v>
+        <v>3.6824962846923</v>
       </c>
       <c r="C2077" t="n">
         <v>4.298141830648305</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.222780976231753</v>
+        <v>-5.220944074740561</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.208673015841856</v>
+        <v>2.209407776438333</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5957797631917759</v>
+        <v>0.6157257022077356</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.655609688563371</v>
+        <v>4.667577251972947</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.717443083018095</v>
+        <v>3.721413999832926</v>
       </c>
       <c r="C2078" t="n">
         <v>4.288378620122077</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.273867641368104</v>
+        <v>-5.268424463043059</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.178475139261088</v>
+        <v>2.180652410591106</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.573035748458811</v>
+        <v>0.6157257022077356</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.632200069197363</v>
+        <v>4.657814041446719</v>
       </c>
     </row>
   </sheetData>
